--- a/e2e_tests_suite/Report_03_API_Testing.xlsx
+++ b/e2e_tests_suite/Report_03_API_Testing.xlsx
@@ -452,19 +452,19 @@
         <v>TC001</v>
       </c>
       <c r="B2" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C2" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D2" t="str">
-        <v>Maintain stream connection verification #1</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #1</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G2" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -487,19 +487,19 @@
         <v>TC002</v>
       </c>
       <c r="B3" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C3" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D3" t="str">
-        <v>Validate JWT handshake verification #2</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #2</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G3" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -522,19 +522,19 @@
         <v>TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C4" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D4" t="str">
-        <v>Secure JSON retrieval verification #3</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #3</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G4" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -557,19 +557,19 @@
         <v>TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C5" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D5" t="str">
-        <v>Maintain stream connection verification #4</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #4</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G5" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -592,19 +592,19 @@
         <v>TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C6" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D6" t="str">
-        <v>Validate JWT handshake verification #5</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #5</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G6" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -627,19 +627,19 @@
         <v>TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C7" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D7" t="str">
-        <v>Secure JSON retrieval verification #6</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #6</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G7" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -662,19 +662,19 @@
         <v>TC007</v>
       </c>
       <c r="B8" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C8" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D8" t="str">
-        <v>Maintain stream connection verification #7</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #7</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G8" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -697,19 +697,19 @@
         <v>TC008</v>
       </c>
       <c r="B9" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C9" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D9" t="str">
-        <v>Validate JWT handshake verification #8</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #8</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G9" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -732,19 +732,19 @@
         <v>TC009</v>
       </c>
       <c r="B10" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C10" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D10" t="str">
-        <v>Secure JSON retrieval verification #9</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #9</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G10" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -767,19 +767,19 @@
         <v>TC010</v>
       </c>
       <c r="B11" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C11" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D11" t="str">
-        <v>Maintain stream connection verification #10</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #10</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G11" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -802,19 +802,19 @@
         <v>TC011</v>
       </c>
       <c r="B12" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C12" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D12" t="str">
-        <v>Validate JWT handshake verification #11</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #11</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G12" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -837,19 +837,19 @@
         <v>TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C13" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D13" t="str">
-        <v>Secure JSON retrieval verification #12</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #12</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G13" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -872,19 +872,19 @@
         <v>TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C14" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D14" t="str">
-        <v>Maintain stream connection verification #13</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #13</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G14" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -907,19 +907,19 @@
         <v>TC014</v>
       </c>
       <c r="B15" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C15" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D15" t="str">
-        <v>Validate JWT handshake verification #14</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #14</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G15" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -942,19 +942,19 @@
         <v>TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C16" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D16" t="str">
-        <v>Secure JSON retrieval verification #15</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #15</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G16" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -977,19 +977,19 @@
         <v>TC016</v>
       </c>
       <c r="B17" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C17" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D17" t="str">
-        <v>Maintain stream connection verification #16</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #16</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G17" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1012,19 +1012,19 @@
         <v>TC017</v>
       </c>
       <c r="B18" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C18" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D18" t="str">
-        <v>Validate JWT handshake verification #17</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #17</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G18" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1047,19 +1047,19 @@
         <v>TC018</v>
       </c>
       <c r="B19" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C19" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D19" t="str">
-        <v>Secure JSON retrieval verification #18</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #18</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G19" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1082,19 +1082,19 @@
         <v>TC019</v>
       </c>
       <c r="B20" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C20" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D20" t="str">
-        <v>Maintain stream connection verification #19</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #19</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G20" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1117,19 +1117,19 @@
         <v>TC020</v>
       </c>
       <c r="B21" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C21" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D21" t="str">
-        <v>Validate JWT handshake verification #20</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #20</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G21" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1152,19 +1152,19 @@
         <v>TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C22" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D22" t="str">
-        <v>Secure JSON retrieval verification #21</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #21</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G22" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1187,19 +1187,19 @@
         <v>TC022</v>
       </c>
       <c r="B23" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C23" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D23" t="str">
-        <v>Maintain stream connection verification #22</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #22</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G23" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1222,19 +1222,19 @@
         <v>TC023</v>
       </c>
       <c r="B24" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C24" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D24" t="str">
-        <v>Validate JWT handshake verification #23</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #23</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G24" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1257,19 +1257,19 @@
         <v>TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C25" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D25" t="str">
-        <v>Secure JSON retrieval verification #24</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #24</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G25" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1292,19 +1292,19 @@
         <v>TC025</v>
       </c>
       <c r="B26" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C26" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D26" t="str">
-        <v>Maintain stream connection verification #25</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #25</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G26" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1327,19 +1327,19 @@
         <v>TC026</v>
       </c>
       <c r="B27" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C27" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D27" t="str">
-        <v>Validate JWT handshake verification #26</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #26</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G27" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1362,19 +1362,19 @@
         <v>TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C28" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D28" t="str">
-        <v>Secure JSON retrieval verification #27</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #27</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G28" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1397,19 +1397,19 @@
         <v>TC028</v>
       </c>
       <c r="B29" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C29" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D29" t="str">
-        <v>Maintain stream connection verification #28</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #28</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G29" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1432,19 +1432,19 @@
         <v>TC029</v>
       </c>
       <c r="B30" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C30" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D30" t="str">
-        <v>Validate JWT handshake verification #29</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #29</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G30" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1467,19 +1467,19 @@
         <v>TC030</v>
       </c>
       <c r="B31" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C31" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D31" t="str">
-        <v>Secure JSON retrieval verification #30</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #30</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G31" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1502,19 +1502,19 @@
         <v>TC031</v>
       </c>
       <c r="B32" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C32" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D32" t="str">
-        <v>Maintain stream connection verification #31</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #31</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G32" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1537,19 +1537,19 @@
         <v>TC032</v>
       </c>
       <c r="B33" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C33" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D33" t="str">
-        <v>Validate JWT handshake verification #32</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #32</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G33" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1572,19 +1572,19 @@
         <v>TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C34" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D34" t="str">
-        <v>Secure JSON retrieval verification #33</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #33</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G34" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1607,19 +1607,19 @@
         <v>TC034</v>
       </c>
       <c r="B35" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C35" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D35" t="str">
-        <v>Maintain stream connection verification #34</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #34</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G35" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1642,19 +1642,19 @@
         <v>TC035</v>
       </c>
       <c r="B36" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C36" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D36" t="str">
-        <v>Validate JWT handshake verification #35</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #35</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G36" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1677,19 +1677,19 @@
         <v>TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C37" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D37" t="str">
-        <v>Secure JSON retrieval verification #36</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #36</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G37" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1712,19 +1712,19 @@
         <v>TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C38" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D38" t="str">
-        <v>Maintain stream connection verification #37</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #37</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G38" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1747,19 +1747,19 @@
         <v>TC038</v>
       </c>
       <c r="B39" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C39" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D39" t="str">
-        <v>Validate JWT handshake verification #38</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #38</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G39" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1782,19 +1782,19 @@
         <v>TC039</v>
       </c>
       <c r="B40" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C40" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D40" t="str">
-        <v>Secure JSON retrieval verification #39</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #39</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G40" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1817,19 +1817,19 @@
         <v>TC040</v>
       </c>
       <c r="B41" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C41" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D41" t="str">
-        <v>Maintain stream connection verification #40</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #40</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G41" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1852,19 +1852,19 @@
         <v>TC041</v>
       </c>
       <c r="B42" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C42" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D42" t="str">
-        <v>Validate JWT handshake verification #41</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #41</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G42" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1887,19 +1887,19 @@
         <v>TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C43" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D43" t="str">
-        <v>Secure JSON retrieval verification #42</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #42</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G43" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1922,19 +1922,19 @@
         <v>TC043</v>
       </c>
       <c r="B44" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C44" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D44" t="str">
-        <v>Maintain stream connection verification #43</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #43</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G44" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1957,19 +1957,19 @@
         <v>TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C45" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D45" t="str">
-        <v>Validate JWT handshake verification #44</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #44</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G45" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1992,19 +1992,19 @@
         <v>TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C46" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D46" t="str">
-        <v>Secure JSON retrieval verification #45</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #45</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G46" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2027,19 +2027,19 @@
         <v>TC046</v>
       </c>
       <c r="B47" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C47" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D47" t="str">
-        <v>Maintain stream connection verification #46</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #46</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G47" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2062,19 +2062,19 @@
         <v>TC047</v>
       </c>
       <c r="B48" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C48" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D48" t="str">
-        <v>Validate JWT handshake verification #47</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #47</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G48" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2097,19 +2097,19 @@
         <v>TC048</v>
       </c>
       <c r="B49" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C49" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D49" t="str">
-        <v>Secure JSON retrieval verification #48</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #48</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G49" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2132,19 +2132,19 @@
         <v>TC049</v>
       </c>
       <c r="B50" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C50" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D50" t="str">
-        <v>Maintain stream connection verification #49</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #49</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G50" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2167,19 +2167,19 @@
         <v>TC050</v>
       </c>
       <c r="B51" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C51" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D51" t="str">
-        <v>Validate JWT handshake verification #50</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #50</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G51" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2202,19 +2202,19 @@
         <v>TC051</v>
       </c>
       <c r="B52" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C52" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D52" t="str">
-        <v>Secure JSON retrieval verification #51</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #51</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G52" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2237,19 +2237,19 @@
         <v>TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C53" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D53" t="str">
-        <v>Maintain stream connection verification #52</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #52</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G53" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2272,19 +2272,19 @@
         <v>TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C54" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D54" t="str">
-        <v>Validate JWT handshake verification #53</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #53</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G54" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2307,19 +2307,19 @@
         <v>TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C55" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D55" t="str">
-        <v>Secure JSON retrieval verification #54</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #54</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G55" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2342,19 +2342,19 @@
         <v>TC055</v>
       </c>
       <c r="B56" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C56" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D56" t="str">
-        <v>Maintain stream connection verification #55</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #55</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G56" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2377,19 +2377,19 @@
         <v>TC056</v>
       </c>
       <c r="B57" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C57" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D57" t="str">
-        <v>Validate JWT handshake verification #56</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #56</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G57" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2412,19 +2412,19 @@
         <v>TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C58" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D58" t="str">
-        <v>Secure JSON retrieval verification #57</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #57</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G58" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2447,19 +2447,19 @@
         <v>TC058</v>
       </c>
       <c r="B59" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C59" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D59" t="str">
-        <v>Maintain stream connection verification #58</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #58</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G59" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2482,19 +2482,19 @@
         <v>TC059</v>
       </c>
       <c r="B60" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C60" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D60" t="str">
-        <v>Validate JWT handshake verification #59</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #59</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G60" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2517,19 +2517,19 @@
         <v>TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C61" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D61" t="str">
-        <v>Secure JSON retrieval verification #60</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #60</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G61" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2552,19 +2552,19 @@
         <v>TC061</v>
       </c>
       <c r="B62" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C62" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D62" t="str">
-        <v>Maintain stream connection verification #61</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #61</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G62" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2587,19 +2587,19 @@
         <v>TC062</v>
       </c>
       <c r="B63" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C63" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D63" t="str">
-        <v>Validate JWT handshake verification #62</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #62</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G63" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2622,19 +2622,19 @@
         <v>TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C64" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D64" t="str">
-        <v>Secure JSON retrieval verification #63</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #63</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G64" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2657,19 +2657,19 @@
         <v>TC064</v>
       </c>
       <c r="B65" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C65" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D65" t="str">
-        <v>Maintain stream connection verification #64</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #64</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G65" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2692,19 +2692,19 @@
         <v>TC065</v>
       </c>
       <c r="B66" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C66" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D66" t="str">
-        <v>Validate JWT handshake verification #65</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #65</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G66" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2727,19 +2727,19 @@
         <v>TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C67" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D67" t="str">
-        <v>Secure JSON retrieval verification #66</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #66</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G67" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2762,19 +2762,19 @@
         <v>TC067</v>
       </c>
       <c r="B68" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C68" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D68" t="str">
-        <v>Maintain stream connection verification #67</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #67</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G68" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2797,19 +2797,19 @@
         <v>TC068</v>
       </c>
       <c r="B69" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C69" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D69" t="str">
-        <v>Validate JWT handshake verification #68</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #68</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G69" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2832,19 +2832,19 @@
         <v>TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C70" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D70" t="str">
-        <v>Secure JSON retrieval verification #69</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #69</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G70" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2867,19 +2867,19 @@
         <v>TC070</v>
       </c>
       <c r="B71" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C71" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D71" t="str">
-        <v>Maintain stream connection verification #70</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #70</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G71" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2902,19 +2902,19 @@
         <v>TC071</v>
       </c>
       <c r="B72" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C72" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D72" t="str">
-        <v>Validate JWT handshake verification #71</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #71</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G72" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2937,19 +2937,19 @@
         <v>TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C73" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D73" t="str">
-        <v>Secure JSON retrieval verification #72</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #72</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G73" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2972,19 +2972,19 @@
         <v>TC073</v>
       </c>
       <c r="B74" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C74" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D74" t="str">
-        <v>Maintain stream connection verification #73</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #73</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G74" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3007,19 +3007,19 @@
         <v>TC074</v>
       </c>
       <c r="B75" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C75" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D75" t="str">
-        <v>Validate JWT handshake verification #74</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #74</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G75" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3042,19 +3042,19 @@
         <v>TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C76" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D76" t="str">
-        <v>Secure JSON retrieval verification #75</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #75</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G76" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3077,19 +3077,19 @@
         <v>TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C77" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D77" t="str">
-        <v>Maintain stream connection verification #76</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #76</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G77" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3112,19 +3112,19 @@
         <v>TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C78" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D78" t="str">
-        <v>Validate JWT handshake verification #77</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #77</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G78" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3147,19 +3147,19 @@
         <v>TC078</v>
       </c>
       <c r="B79" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C79" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D79" t="str">
-        <v>Secure JSON retrieval verification #78</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #78</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G79" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3182,19 +3182,19 @@
         <v>TC079</v>
       </c>
       <c r="B80" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C80" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D80" t="str">
-        <v>Maintain stream connection verification #79</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #79</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G80" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3217,19 +3217,19 @@
         <v>TC080</v>
       </c>
       <c r="B81" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C81" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D81" t="str">
-        <v>Validate JWT handshake verification #80</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #80</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G81" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3252,19 +3252,19 @@
         <v>TC081</v>
       </c>
       <c r="B82" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C82" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D82" t="str">
-        <v>Secure JSON retrieval verification #81</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #81</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G82" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3287,19 +3287,19 @@
         <v>TC082</v>
       </c>
       <c r="B83" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C83" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D83" t="str">
-        <v>Maintain stream connection verification #82</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #82</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G83" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3322,19 +3322,19 @@
         <v>TC083</v>
       </c>
       <c r="B84" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C84" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D84" t="str">
-        <v>Validate JWT handshake verification #83</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #83</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G84" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3357,19 +3357,19 @@
         <v>TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C85" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D85" t="str">
-        <v>Secure JSON retrieval verification #84</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #84</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G85" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3392,19 +3392,19 @@
         <v>TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C86" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D86" t="str">
-        <v>Maintain stream connection verification #85</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #85</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G86" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3427,19 +3427,19 @@
         <v>TC086</v>
       </c>
       <c r="B87" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C87" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D87" t="str">
-        <v>Validate JWT handshake verification #86</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #86</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G87" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3462,19 +3462,19 @@
         <v>TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C88" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D88" t="str">
-        <v>Secure JSON retrieval verification #87</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #87</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G88" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3497,19 +3497,19 @@
         <v>TC088</v>
       </c>
       <c r="B89" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C89" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D89" t="str">
-        <v>Maintain stream connection verification #88</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #88</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G89" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3532,19 +3532,19 @@
         <v>TC089</v>
       </c>
       <c r="B90" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C90" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D90" t="str">
-        <v>Validate JWT handshake verification #89</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #89</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G90" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3567,19 +3567,19 @@
         <v>TC090</v>
       </c>
       <c r="B91" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C91" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D91" t="str">
-        <v>Secure JSON retrieval verification #90</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #90</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G91" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3602,19 +3602,19 @@
         <v>TC091</v>
       </c>
       <c r="B92" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C92" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D92" t="str">
-        <v>Maintain stream connection verification #91</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #91</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G92" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3637,19 +3637,19 @@
         <v>TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C93" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D93" t="str">
-        <v>Validate JWT handshake verification #92</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #92</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G93" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3672,19 +3672,19 @@
         <v>TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C94" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D94" t="str">
-        <v>Secure JSON retrieval verification #93</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #93</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G94" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3707,19 +3707,19 @@
         <v>TC094</v>
       </c>
       <c r="B95" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C95" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D95" t="str">
-        <v>Maintain stream connection verification #94</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #94</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G95" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3742,19 +3742,19 @@
         <v>TC095</v>
       </c>
       <c r="B96" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C96" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D96" t="str">
-        <v>Validate JWT handshake verification #95</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #95</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G96" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3777,19 +3777,19 @@
         <v>TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C97" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D97" t="str">
-        <v>Secure JSON retrieval verification #96</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #96</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G97" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3812,19 +3812,19 @@
         <v>TC097</v>
       </c>
       <c r="B98" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C98" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D98" t="str">
-        <v>Maintain stream connection verification #97</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #97</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G98" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3847,19 +3847,19 @@
         <v>TC098</v>
       </c>
       <c r="B99" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C99" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D99" t="str">
-        <v>Validate JWT handshake verification #98</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #98</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G99" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3882,19 +3882,19 @@
         <v>TC099</v>
       </c>
       <c r="B100" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C100" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D100" t="str">
-        <v>Secure JSON retrieval verification #99</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #99</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G100" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3917,19 +3917,19 @@
         <v>TC100</v>
       </c>
       <c r="B101" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C101" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D101" t="str">
-        <v>Maintain stream connection verification #100</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #100</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G101" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3952,19 +3952,19 @@
         <v>TC101</v>
       </c>
       <c r="B102" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C102" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D102" t="str">
-        <v>Validate JWT handshake verification #101</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #101</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G102" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3987,19 +3987,19 @@
         <v>TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C103" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D103" t="str">
-        <v>Secure JSON retrieval verification #102</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #102</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G103" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4022,19 +4022,19 @@
         <v>TC103</v>
       </c>
       <c r="B104" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C104" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D104" t="str">
-        <v>Maintain stream connection verification #103</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #103</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G104" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4057,19 +4057,19 @@
         <v>TC104</v>
       </c>
       <c r="B105" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C105" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D105" t="str">
-        <v>Validate JWT handshake verification #104</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #104</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G105" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4092,19 +4092,19 @@
         <v>TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C106" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D106" t="str">
-        <v>Secure JSON retrieval verification #105</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #105</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G106" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4127,19 +4127,19 @@
         <v>TC106</v>
       </c>
       <c r="B107" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C107" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D107" t="str">
-        <v>Maintain stream connection verification #106</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #106</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G107" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4162,19 +4162,19 @@
         <v>TC107</v>
       </c>
       <c r="B108" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C108" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D108" t="str">
-        <v>Validate JWT handshake verification #107</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #107</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G108" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4197,19 +4197,19 @@
         <v>TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C109" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D109" t="str">
-        <v>Secure JSON retrieval verification #108</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #108</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G109" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4232,19 +4232,19 @@
         <v>TC109</v>
       </c>
       <c r="B110" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C110" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D110" t="str">
-        <v>Maintain stream connection verification #109</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #109</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G110" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4267,19 +4267,19 @@
         <v>TC110</v>
       </c>
       <c r="B111" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C111" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D111" t="str">
-        <v>Validate JWT handshake verification #110</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #110</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G111" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4302,19 +4302,19 @@
         <v>TC111</v>
       </c>
       <c r="B112" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C112" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D112" t="str">
-        <v>Secure JSON retrieval verification #111</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #111</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G112" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4337,19 +4337,19 @@
         <v>TC112</v>
       </c>
       <c r="B113" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C113" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D113" t="str">
-        <v>Maintain stream connection verification #112</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #112</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G113" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4372,19 +4372,19 @@
         <v>TC113</v>
       </c>
       <c r="B114" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C114" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D114" t="str">
-        <v>Validate JWT handshake verification #113</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #113</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G114" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4407,19 +4407,19 @@
         <v>TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C115" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D115" t="str">
-        <v>Secure JSON retrieval verification #114</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #114</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G115" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4442,19 +4442,19 @@
         <v>TC115</v>
       </c>
       <c r="B116" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C116" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D116" t="str">
-        <v>Maintain stream connection verification #115</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #115</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G116" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4477,19 +4477,19 @@
         <v>TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C117" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D117" t="str">
-        <v>Validate JWT handshake verification #116</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #116</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G117" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4512,19 +4512,19 @@
         <v>TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C118" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D118" t="str">
-        <v>Secure JSON retrieval verification #117</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #117</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G118" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4547,19 +4547,19 @@
         <v>TC118</v>
       </c>
       <c r="B119" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C119" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D119" t="str">
-        <v>Maintain stream connection verification #118</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #118</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G119" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4582,19 +4582,19 @@
         <v>TC119</v>
       </c>
       <c r="B120" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C120" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D120" t="str">
-        <v>Validate JWT handshake verification #119</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #119</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G120" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4617,19 +4617,19 @@
         <v>TC120</v>
       </c>
       <c r="B121" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C121" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D121" t="str">
-        <v>Secure JSON retrieval verification #120</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #120</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G121" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4652,19 +4652,19 @@
         <v>TC121</v>
       </c>
       <c r="B122" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C122" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D122" t="str">
-        <v>Maintain stream connection verification #121</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #121</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G122" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4687,19 +4687,19 @@
         <v>TC122</v>
       </c>
       <c r="B123" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C123" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D123" t="str">
-        <v>Validate JWT handshake verification #122</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #122</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G123" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4722,19 +4722,19 @@
         <v>TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C124" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D124" t="str">
-        <v>Secure JSON retrieval verification #123</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #123</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G124" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4757,19 +4757,19 @@
         <v>TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C125" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D125" t="str">
-        <v>Maintain stream connection verification #124</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #124</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G125" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4792,19 +4792,19 @@
         <v>TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C126" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D126" t="str">
-        <v>Validate JWT handshake verification #125</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #125</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G126" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4827,19 +4827,19 @@
         <v>TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C127" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D127" t="str">
-        <v>Secure JSON retrieval verification #126</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #126</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G127" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4862,19 +4862,19 @@
         <v>TC127</v>
       </c>
       <c r="B128" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C128" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D128" t="str">
-        <v>Maintain stream connection verification #127</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #127</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G128" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4897,19 +4897,19 @@
         <v>TC128</v>
       </c>
       <c r="B129" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C129" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D129" t="str">
-        <v>Validate JWT handshake verification #128</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #128</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G129" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4932,19 +4932,19 @@
         <v>TC129</v>
       </c>
       <c r="B130" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C130" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D130" t="str">
-        <v>Secure JSON retrieval verification #129</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #129</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G130" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4967,19 +4967,19 @@
         <v>TC130</v>
       </c>
       <c r="B131" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C131" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D131" t="str">
-        <v>Maintain stream connection verification #130</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #130</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G131" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5002,19 +5002,19 @@
         <v>TC131</v>
       </c>
       <c r="B132" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C132" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D132" t="str">
-        <v>Validate JWT handshake verification #131</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #131</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G132" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5037,19 +5037,19 @@
         <v>TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C133" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D133" t="str">
-        <v>Secure JSON retrieval verification #132</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #132</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G133" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5072,19 +5072,19 @@
         <v>TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C134" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D134" t="str">
-        <v>Maintain stream connection verification #133</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #133</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G134" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5107,19 +5107,19 @@
         <v>TC134</v>
       </c>
       <c r="B135" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C135" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D135" t="str">
-        <v>Validate JWT handshake verification #134</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #134</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G135" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5142,19 +5142,19 @@
         <v>TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C136" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D136" t="str">
-        <v>Secure JSON retrieval verification #135</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #135</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G136" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5177,19 +5177,19 @@
         <v>TC136</v>
       </c>
       <c r="B137" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C137" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D137" t="str">
-        <v>Maintain stream connection verification #136</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #136</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G137" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5212,19 +5212,19 @@
         <v>TC137</v>
       </c>
       <c r="B138" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C138" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D138" t="str">
-        <v>Validate JWT handshake verification #137</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #137</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G138" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5247,19 +5247,19 @@
         <v>TC138</v>
       </c>
       <c r="B139" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C139" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D139" t="str">
-        <v>Secure JSON retrieval verification #138</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #138</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G139" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5282,19 +5282,19 @@
         <v>TC139</v>
       </c>
       <c r="B140" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C140" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D140" t="str">
-        <v>Maintain stream connection verification #139</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #139</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G140" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5317,19 +5317,19 @@
         <v>TC140</v>
       </c>
       <c r="B141" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C141" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D141" t="str">
-        <v>Validate JWT handshake verification #140</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #140</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G141" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5352,19 +5352,19 @@
         <v>TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C142" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D142" t="str">
-        <v>Secure JSON retrieval verification #141</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #141</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G142" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5387,19 +5387,19 @@
         <v>TC142</v>
       </c>
       <c r="B143" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C143" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D143" t="str">
-        <v>Maintain stream connection verification #142</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #142</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G143" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5422,19 +5422,19 @@
         <v>TC143</v>
       </c>
       <c r="B144" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C144" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D144" t="str">
-        <v>Validate JWT handshake verification #143</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #143</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G144" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5457,19 +5457,19 @@
         <v>TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C145" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D145" t="str">
-        <v>Secure JSON retrieval verification #144</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #144</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G145" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5492,19 +5492,19 @@
         <v>TC145</v>
       </c>
       <c r="B146" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C146" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D146" t="str">
-        <v>Maintain stream connection verification #145</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #145</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G146" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5527,19 +5527,19 @@
         <v>TC146</v>
       </c>
       <c r="B147" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C147" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D147" t="str">
-        <v>Validate JWT handshake verification #146</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #146</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G147" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5562,19 +5562,19 @@
         <v>TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C148" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D148" t="str">
-        <v>Secure JSON retrieval verification #147</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #147</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G148" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5597,19 +5597,19 @@
         <v>TC148</v>
       </c>
       <c r="B149" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C149" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D149" t="str">
-        <v>Maintain stream connection verification #148</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #148</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G149" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5632,19 +5632,19 @@
         <v>TC149</v>
       </c>
       <c r="B150" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C150" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D150" t="str">
-        <v>Validate JWT handshake verification #149</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #149</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G150" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5667,19 +5667,19 @@
         <v>TC150</v>
       </c>
       <c r="B151" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C151" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D151" t="str">
-        <v>Secure JSON retrieval verification #150</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #150</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G151" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5702,19 +5702,19 @@
         <v>TC151</v>
       </c>
       <c r="B152" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C152" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D152" t="str">
-        <v>Maintain stream connection verification #151</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #151</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G152" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5737,19 +5737,19 @@
         <v>TC152</v>
       </c>
       <c r="B153" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C153" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D153" t="str">
-        <v>Validate JWT handshake verification #152</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #152</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G153" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5772,19 +5772,19 @@
         <v>TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C154" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D154" t="str">
-        <v>Secure JSON retrieval verification #153</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #153</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G154" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5807,19 +5807,19 @@
         <v>TC154</v>
       </c>
       <c r="B155" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C155" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D155" t="str">
-        <v>Maintain stream connection verification #154</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #154</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G155" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5842,19 +5842,19 @@
         <v>TC155</v>
       </c>
       <c r="B156" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C156" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D156" t="str">
-        <v>Validate JWT handshake verification #155</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #155</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G156" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5877,19 +5877,19 @@
         <v>TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C157" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D157" t="str">
-        <v>Secure JSON retrieval verification #156</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #156</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G157" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5912,19 +5912,19 @@
         <v>TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C158" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D158" t="str">
-        <v>Maintain stream connection verification #157</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #157</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G158" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5947,19 +5947,19 @@
         <v>TC158</v>
       </c>
       <c r="B159" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C159" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D159" t="str">
-        <v>Validate JWT handshake verification #158</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #158</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G159" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5982,19 +5982,19 @@
         <v>TC159</v>
       </c>
       <c r="B160" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C160" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D160" t="str">
-        <v>Secure JSON retrieval verification #159</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #159</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G160" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6017,19 +6017,19 @@
         <v>TC160</v>
       </c>
       <c r="B161" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C161" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D161" t="str">
-        <v>Maintain stream connection verification #160</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #160</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G161" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6052,19 +6052,19 @@
         <v>TC161</v>
       </c>
       <c r="B162" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C162" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D162" t="str">
-        <v>Validate JWT handshake verification #161</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #161</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G162" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6087,19 +6087,19 @@
         <v>TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C163" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D163" t="str">
-        <v>Secure JSON retrieval verification #162</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #162</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G163" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6122,19 +6122,19 @@
         <v>TC163</v>
       </c>
       <c r="B164" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C164" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D164" t="str">
-        <v>Maintain stream connection verification #163</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #163</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G164" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6157,19 +6157,19 @@
         <v>TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C165" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D165" t="str">
-        <v>Validate JWT handshake verification #164</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #164</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G165" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6192,19 +6192,19 @@
         <v>TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C166" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D166" t="str">
-        <v>Secure JSON retrieval verification #165</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #165</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G166" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6227,19 +6227,19 @@
         <v>TC166</v>
       </c>
       <c r="B167" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C167" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D167" t="str">
-        <v>Maintain stream connection verification #166</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #166</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G167" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6262,19 +6262,19 @@
         <v>TC167</v>
       </c>
       <c r="B168" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C168" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D168" t="str">
-        <v>Validate JWT handshake verification #167</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #167</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G168" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6297,19 +6297,19 @@
         <v>TC168</v>
       </c>
       <c r="B169" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C169" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D169" t="str">
-        <v>Secure JSON retrieval verification #168</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #168</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G169" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6332,19 +6332,19 @@
         <v>TC169</v>
       </c>
       <c r="B170" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C170" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D170" t="str">
-        <v>Maintain stream connection verification #169</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #169</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G170" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6367,19 +6367,19 @@
         <v>TC170</v>
       </c>
       <c r="B171" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C171" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D171" t="str">
-        <v>Validate JWT handshake verification #170</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #170</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G171" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6402,19 +6402,19 @@
         <v>TC171</v>
       </c>
       <c r="B172" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C172" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D172" t="str">
-        <v>Secure JSON retrieval verification #171</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #171</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G172" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6437,19 +6437,19 @@
         <v>TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C173" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D173" t="str">
-        <v>Maintain stream connection verification #172</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #172</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G173" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6472,19 +6472,19 @@
         <v>TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C174" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D174" t="str">
-        <v>Validate JWT handshake verification #173</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #173</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G174" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6507,19 +6507,19 @@
         <v>TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C175" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D175" t="str">
-        <v>Secure JSON retrieval verification #174</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #174</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G175" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6542,19 +6542,19 @@
         <v>TC175</v>
       </c>
       <c r="B176" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C176" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D176" t="str">
-        <v>Maintain stream connection verification #175</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #175</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G176" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6577,19 +6577,19 @@
         <v>TC176</v>
       </c>
       <c r="B177" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C177" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D177" t="str">
-        <v>Validate JWT handshake verification #176</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #176</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G177" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6612,19 +6612,19 @@
         <v>TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C178" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D178" t="str">
-        <v>Secure JSON retrieval verification #177</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #177</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G178" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6647,19 +6647,19 @@
         <v>TC178</v>
       </c>
       <c r="B179" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C179" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D179" t="str">
-        <v>Maintain stream connection verification #178</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #178</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G179" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6682,19 +6682,19 @@
         <v>TC179</v>
       </c>
       <c r="B180" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C180" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D180" t="str">
-        <v>Validate JWT handshake verification #179</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #179</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G180" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6717,19 +6717,19 @@
         <v>TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C181" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D181" t="str">
-        <v>Secure JSON retrieval verification #180</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #180</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G181" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6752,19 +6752,19 @@
         <v>TC181</v>
       </c>
       <c r="B182" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C182" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D182" t="str">
-        <v>Maintain stream connection verification #181</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #181</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G182" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6787,19 +6787,19 @@
         <v>TC182</v>
       </c>
       <c r="B183" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C183" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D183" t="str">
-        <v>Validate JWT handshake verification #182</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #182</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G183" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6822,19 +6822,19 @@
         <v>TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C184" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D184" t="str">
-        <v>Secure JSON retrieval verification #183</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #183</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G184" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6857,19 +6857,19 @@
         <v>TC184</v>
       </c>
       <c r="B185" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C185" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D185" t="str">
-        <v>Maintain stream connection verification #184</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #184</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G185" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6892,19 +6892,19 @@
         <v>TC185</v>
       </c>
       <c r="B186" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C186" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D186" t="str">
-        <v>Validate JWT handshake verification #185</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #185</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G186" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6927,19 +6927,19 @@
         <v>TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C187" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D187" t="str">
-        <v>Secure JSON retrieval verification #186</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #186</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G187" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6962,19 +6962,19 @@
         <v>TC187</v>
       </c>
       <c r="B188" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C188" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D188" t="str">
-        <v>Maintain stream connection verification #187</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #187</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G188" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6997,19 +6997,19 @@
         <v>TC188</v>
       </c>
       <c r="B189" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C189" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D189" t="str">
-        <v>Validate JWT handshake verification #188</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #188</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G189" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7032,19 +7032,19 @@
         <v>TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C190" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D190" t="str">
-        <v>Secure JSON retrieval verification #189</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #189</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G190" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7067,19 +7067,19 @@
         <v>TC190</v>
       </c>
       <c r="B191" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C191" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D191" t="str">
-        <v>Maintain stream connection verification #190</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #190</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G191" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7102,19 +7102,19 @@
         <v>TC191</v>
       </c>
       <c r="B192" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C192" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D192" t="str">
-        <v>Validate JWT handshake verification #191</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #191</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G192" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7137,19 +7137,19 @@
         <v>TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C193" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D193" t="str">
-        <v>Secure JSON retrieval verification #192</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #192</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G193" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7172,19 +7172,19 @@
         <v>TC193</v>
       </c>
       <c r="B194" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C194" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D194" t="str">
-        <v>Maintain stream connection verification #193</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #193</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G194" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7207,19 +7207,19 @@
         <v>TC194</v>
       </c>
       <c r="B195" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C195" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D195" t="str">
-        <v>Validate JWT handshake verification #194</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #194</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G195" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7242,19 +7242,19 @@
         <v>TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C196" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D196" t="str">
-        <v>Secure JSON retrieval verification #195</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #195</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G196" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7277,19 +7277,19 @@
         <v>TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C197" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D197" t="str">
-        <v>Maintain stream connection verification #196</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #196</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G197" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7312,19 +7312,19 @@
         <v>TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C198" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D198" t="str">
-        <v>Validate JWT handshake verification #197</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #197</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G198" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7347,19 +7347,19 @@
         <v>TC198</v>
       </c>
       <c r="B199" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C199" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D199" t="str">
-        <v>Secure JSON retrieval verification #198</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #198</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G199" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7382,19 +7382,19 @@
         <v>TC199</v>
       </c>
       <c r="B200" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C200" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D200" t="str">
-        <v>Maintain stream connection verification #199</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #199</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G200" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7417,19 +7417,19 @@
         <v>TC200</v>
       </c>
       <c r="B201" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C201" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D201" t="str">
-        <v>Validate JWT handshake verification #200</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #200</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G201" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7452,19 +7452,19 @@
         <v>TC201</v>
       </c>
       <c r="B202" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C202" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D202" t="str">
-        <v>Secure JSON retrieval verification #201</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #201</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G202" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7487,19 +7487,19 @@
         <v>TC202</v>
       </c>
       <c r="B203" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C203" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D203" t="str">
-        <v>Maintain stream connection verification #202</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #202</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G203" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7522,19 +7522,19 @@
         <v>TC203</v>
       </c>
       <c r="B204" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C204" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D204" t="str">
-        <v>Validate JWT handshake verification #203</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #203</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G204" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7557,19 +7557,19 @@
         <v>TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C205" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D205" t="str">
-        <v>Secure JSON retrieval verification #204</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #204</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G205" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7592,19 +7592,19 @@
         <v>TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C206" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D206" t="str">
-        <v>Maintain stream connection verification #205</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #205</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G206" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7627,19 +7627,19 @@
         <v>TC206</v>
       </c>
       <c r="B207" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C207" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D207" t="str">
-        <v>Validate JWT handshake verification #206</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #206</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G207" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7662,19 +7662,19 @@
         <v>TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C208" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D208" t="str">
-        <v>Secure JSON retrieval verification #207</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #207</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G208" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7697,19 +7697,19 @@
         <v>TC208</v>
       </c>
       <c r="B209" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C209" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D209" t="str">
-        <v>Maintain stream connection verification #208</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #208</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G209" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7732,19 +7732,19 @@
         <v>TC209</v>
       </c>
       <c r="B210" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C210" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D210" t="str">
-        <v>Validate JWT handshake verification #209</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #209</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G210" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7767,19 +7767,19 @@
         <v>TC210</v>
       </c>
       <c r="B211" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C211" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D211" t="str">
-        <v>Secure JSON retrieval verification #210</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #210</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G211" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7802,19 +7802,19 @@
         <v>TC211</v>
       </c>
       <c r="B212" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C212" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D212" t="str">
-        <v>Maintain stream connection verification #211</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #211</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G212" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7837,19 +7837,19 @@
         <v>TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C213" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D213" t="str">
-        <v>Validate JWT handshake verification #212</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #212</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G213" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7872,19 +7872,19 @@
         <v>TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C214" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D214" t="str">
-        <v>Secure JSON retrieval verification #213</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #213</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G214" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7907,19 +7907,19 @@
         <v>TC214</v>
       </c>
       <c r="B215" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C215" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D215" t="str">
-        <v>Maintain stream connection verification #214</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #214</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G215" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7942,19 +7942,19 @@
         <v>TC215</v>
       </c>
       <c r="B216" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C216" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D216" t="str">
-        <v>Validate JWT handshake verification #215</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #215</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G216" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7977,19 +7977,19 @@
         <v>TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C217" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D217" t="str">
-        <v>Secure JSON retrieval verification #216</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #216</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G217" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8012,19 +8012,19 @@
         <v>TC217</v>
       </c>
       <c r="B218" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C218" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D218" t="str">
-        <v>Maintain stream connection verification #217</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #217</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G218" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8047,19 +8047,19 @@
         <v>TC218</v>
       </c>
       <c r="B219" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C219" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D219" t="str">
-        <v>Validate JWT handshake verification #218</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #218</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G219" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8082,19 +8082,19 @@
         <v>TC219</v>
       </c>
       <c r="B220" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C220" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D220" t="str">
-        <v>Secure JSON retrieval verification #219</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #219</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G220" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8117,19 +8117,19 @@
         <v>TC220</v>
       </c>
       <c r="B221" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C221" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D221" t="str">
-        <v>Maintain stream connection verification #220</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #220</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G221" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8152,19 +8152,19 @@
         <v>TC221</v>
       </c>
       <c r="B222" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C222" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D222" t="str">
-        <v>Validate JWT handshake verification #221</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #221</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G222" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8187,19 +8187,19 @@
         <v>TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C223" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D223" t="str">
-        <v>Secure JSON retrieval verification #222</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #222</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G223" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8222,19 +8222,19 @@
         <v>TC223</v>
       </c>
       <c r="B224" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C224" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D224" t="str">
-        <v>Maintain stream connection verification #223</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #223</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G224" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8257,19 +8257,19 @@
         <v>TC224</v>
       </c>
       <c r="B225" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C225" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D225" t="str">
-        <v>Validate JWT handshake verification #224</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #224</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G225" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8292,19 +8292,19 @@
         <v>TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C226" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D226" t="str">
-        <v>Secure JSON retrieval verification #225</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #225</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G226" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8327,19 +8327,19 @@
         <v>TC226</v>
       </c>
       <c r="B227" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C227" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D227" t="str">
-        <v>Maintain stream connection verification #226</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #226</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G227" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8362,19 +8362,19 @@
         <v>TC227</v>
       </c>
       <c r="B228" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C228" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D228" t="str">
-        <v>Validate JWT handshake verification #227</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #227</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G228" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8397,19 +8397,19 @@
         <v>TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C229" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D229" t="str">
-        <v>Secure JSON retrieval verification #228</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #228</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G229" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8432,19 +8432,19 @@
         <v>TC229</v>
       </c>
       <c r="B230" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C230" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D230" t="str">
-        <v>Maintain stream connection verification #229</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #229</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G230" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8467,19 +8467,19 @@
         <v>TC230</v>
       </c>
       <c r="B231" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C231" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D231" t="str">
-        <v>Validate JWT handshake verification #230</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #230</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G231" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8502,19 +8502,19 @@
         <v>TC231</v>
       </c>
       <c r="B232" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C232" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D232" t="str">
-        <v>Secure JSON retrieval verification #231</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #231</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G232" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8537,19 +8537,19 @@
         <v>TC232</v>
       </c>
       <c r="B233" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C233" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D233" t="str">
-        <v>Maintain stream connection verification #232</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #232</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G233" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8572,19 +8572,19 @@
         <v>TC233</v>
       </c>
       <c r="B234" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C234" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D234" t="str">
-        <v>Validate JWT handshake verification #233</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #233</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G234" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8607,19 +8607,19 @@
         <v>TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C235" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D235" t="str">
-        <v>Secure JSON retrieval verification #234</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #234</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G235" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8642,19 +8642,19 @@
         <v>TC235</v>
       </c>
       <c r="B236" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C236" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D236" t="str">
-        <v>Maintain stream connection verification #235</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #235</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G236" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8677,19 +8677,19 @@
         <v>TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C237" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D237" t="str">
-        <v>Validate JWT handshake verification #236</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #236</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G237" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8712,19 +8712,19 @@
         <v>TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C238" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D238" t="str">
-        <v>Secure JSON retrieval verification #237</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #237</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G238" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8747,19 +8747,19 @@
         <v>TC238</v>
       </c>
       <c r="B239" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C239" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D239" t="str">
-        <v>Maintain stream connection verification #238</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #238</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G239" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8782,19 +8782,19 @@
         <v>TC239</v>
       </c>
       <c r="B240" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C240" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D240" t="str">
-        <v>Validate JWT handshake verification #239</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #239</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G240" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8817,19 +8817,19 @@
         <v>TC240</v>
       </c>
       <c r="B241" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C241" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D241" t="str">
-        <v>Secure JSON retrieval verification #240</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #240</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G241" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8852,19 +8852,19 @@
         <v>TC241</v>
       </c>
       <c r="B242" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C242" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D242" t="str">
-        <v>Maintain stream connection verification #241</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #241</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G242" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8887,19 +8887,19 @@
         <v>TC242</v>
       </c>
       <c r="B243" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C243" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D243" t="str">
-        <v>Validate JWT handshake verification #242</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #242</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G243" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8922,19 +8922,19 @@
         <v>TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C244" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D244" t="str">
-        <v>Secure JSON retrieval verification #243</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #243</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G244" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8957,19 +8957,19 @@
         <v>TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C245" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D245" t="str">
-        <v>Maintain stream connection verification #244</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #244</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G245" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8992,19 +8992,19 @@
         <v>TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C246" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D246" t="str">
-        <v>Validate JWT handshake verification #245</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #245</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G246" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9027,19 +9027,19 @@
         <v>TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C247" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D247" t="str">
-        <v>Secure JSON retrieval verification #246</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #246</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G247" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9062,19 +9062,19 @@
         <v>TC247</v>
       </c>
       <c r="B248" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C248" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D248" t="str">
-        <v>Maintain stream connection verification #247</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #247</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G248" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9097,19 +9097,19 @@
         <v>TC248</v>
       </c>
       <c r="B249" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C249" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D249" t="str">
-        <v>Validate JWT handshake verification #248</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #248</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G249" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9132,19 +9132,19 @@
         <v>TC249</v>
       </c>
       <c r="B250" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C250" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D250" t="str">
-        <v>Secure JSON retrieval verification #249</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #249</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G250" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9167,19 +9167,19 @@
         <v>TC250</v>
       </c>
       <c r="B251" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C251" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D251" t="str">
-        <v>Maintain stream connection verification #250</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #250</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G251" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9202,19 +9202,19 @@
         <v>TC251</v>
       </c>
       <c r="B252" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C252" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D252" t="str">
-        <v>Validate JWT handshake verification #251</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #251</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G252" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9237,19 +9237,19 @@
         <v>TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C253" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D253" t="str">
-        <v>Secure JSON retrieval verification #252</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #252</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G253" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9272,19 +9272,19 @@
         <v>TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C254" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D254" t="str">
-        <v>Maintain stream connection verification #253</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #253</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G254" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9307,19 +9307,19 @@
         <v>TC254</v>
       </c>
       <c r="B255" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C255" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D255" t="str">
-        <v>Validate JWT handshake verification #254</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #254</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G255" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9342,19 +9342,19 @@
         <v>TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C256" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D256" t="str">
-        <v>Secure JSON retrieval verification #255</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #255</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G256" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9377,19 +9377,19 @@
         <v>TC256</v>
       </c>
       <c r="B257" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C257" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D257" t="str">
-        <v>Maintain stream connection verification #256</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #256</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G257" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9412,19 +9412,19 @@
         <v>TC257</v>
       </c>
       <c r="B258" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C258" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D258" t="str">
-        <v>Validate JWT handshake verification #257</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #257</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G258" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9447,19 +9447,19 @@
         <v>TC258</v>
       </c>
       <c r="B259" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C259" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D259" t="str">
-        <v>Secure JSON retrieval verification #258</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #258</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G259" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9482,19 +9482,19 @@
         <v>TC259</v>
       </c>
       <c r="B260" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C260" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D260" t="str">
-        <v>Maintain stream connection verification #259</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #259</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G260" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9517,19 +9517,19 @@
         <v>TC260</v>
       </c>
       <c r="B261" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C261" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D261" t="str">
-        <v>Validate JWT handshake verification #260</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #260</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G261" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9552,19 +9552,19 @@
         <v>TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C262" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D262" t="str">
-        <v>Secure JSON retrieval verification #261</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #261</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G262" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9587,19 +9587,19 @@
         <v>TC262</v>
       </c>
       <c r="B263" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C263" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D263" t="str">
-        <v>Maintain stream connection verification #262</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #262</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G263" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9622,19 +9622,19 @@
         <v>TC263</v>
       </c>
       <c r="B264" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C264" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D264" t="str">
-        <v>Validate JWT handshake verification #263</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #263</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G264" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9657,19 +9657,19 @@
         <v>TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C265" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D265" t="str">
-        <v>Secure JSON retrieval verification #264</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #264</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G265" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9692,19 +9692,19 @@
         <v>TC265</v>
       </c>
       <c r="B266" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C266" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D266" t="str">
-        <v>Maintain stream connection verification #265</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #265</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G266" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9727,19 +9727,19 @@
         <v>TC266</v>
       </c>
       <c r="B267" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C267" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D267" t="str">
-        <v>Validate JWT handshake verification #266</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #266</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G267" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9762,19 +9762,19 @@
         <v>TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C268" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D268" t="str">
-        <v>Secure JSON retrieval verification #267</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #267</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G268" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9797,19 +9797,19 @@
         <v>TC268</v>
       </c>
       <c r="B269" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C269" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D269" t="str">
-        <v>Maintain stream connection verification #268</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #268</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G269" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9832,19 +9832,19 @@
         <v>TC269</v>
       </c>
       <c r="B270" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C270" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D270" t="str">
-        <v>Validate JWT handshake verification #269</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #269</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G270" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9867,19 +9867,19 @@
         <v>TC270</v>
       </c>
       <c r="B271" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C271" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D271" t="str">
-        <v>Secure JSON retrieval verification #270</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #270</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G271" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9902,19 +9902,19 @@
         <v>TC271</v>
       </c>
       <c r="B272" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C272" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D272" t="str">
-        <v>Maintain stream connection verification #271</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #271</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G272" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9937,19 +9937,19 @@
         <v>TC272</v>
       </c>
       <c r="B273" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C273" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D273" t="str">
-        <v>Validate JWT handshake verification #272</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #272</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G273" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9972,19 +9972,19 @@
         <v>TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C274" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D274" t="str">
-        <v>Secure JSON retrieval verification #273</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #273</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G274" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10007,19 +10007,19 @@
         <v>TC274</v>
       </c>
       <c r="B275" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C275" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D275" t="str">
-        <v>Maintain stream connection verification #274</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #274</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G275" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10042,19 +10042,19 @@
         <v>TC275</v>
       </c>
       <c r="B276" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C276" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D276" t="str">
-        <v>Validate JWT handshake verification #275</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #275</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G276" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10077,19 +10077,19 @@
         <v>TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C277" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D277" t="str">
-        <v>Secure JSON retrieval verification #276</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #276</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G277" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10112,19 +10112,19 @@
         <v>TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C278" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D278" t="str">
-        <v>Maintain stream connection verification #277</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #277</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G278" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10147,19 +10147,19 @@
         <v>TC278</v>
       </c>
       <c r="B279" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C279" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D279" t="str">
-        <v>Validate JWT handshake verification #278</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #278</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G279" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10182,19 +10182,19 @@
         <v>TC279</v>
       </c>
       <c r="B280" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C280" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D280" t="str">
-        <v>Secure JSON retrieval verification #279</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #279</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G280" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10217,19 +10217,19 @@
         <v>TC280</v>
       </c>
       <c r="B281" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C281" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D281" t="str">
-        <v>Maintain stream connection verification #280</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #280</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G281" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10252,19 +10252,19 @@
         <v>TC281</v>
       </c>
       <c r="B282" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C282" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D282" t="str">
-        <v>Validate JWT handshake verification #281</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #281</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G282" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10287,19 +10287,19 @@
         <v>TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C283" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D283" t="str">
-        <v>Secure JSON retrieval verification #282</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #282</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G283" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10322,19 +10322,19 @@
         <v>TC283</v>
       </c>
       <c r="B284" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C284" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D284" t="str">
-        <v>Maintain stream connection verification #283</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #283</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G284" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10357,19 +10357,19 @@
         <v>TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C285" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D285" t="str">
-        <v>Validate JWT handshake verification #284</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #284</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G285" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10392,19 +10392,19 @@
         <v>TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C286" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D286" t="str">
-        <v>Secure JSON retrieval verification #285</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #285</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G286" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10427,19 +10427,19 @@
         <v>TC286</v>
       </c>
       <c r="B287" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C287" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D287" t="str">
-        <v>Maintain stream connection verification #286</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #286</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G287" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10462,19 +10462,19 @@
         <v>TC287</v>
       </c>
       <c r="B288" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C288" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D288" t="str">
-        <v>Validate JWT handshake verification #287</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #287</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G288" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10497,19 +10497,19 @@
         <v>TC288</v>
       </c>
       <c r="B289" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C289" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D289" t="str">
-        <v>Secure JSON retrieval verification #288</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #288</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G289" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10532,19 +10532,19 @@
         <v>TC289</v>
       </c>
       <c r="B290" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C290" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D290" t="str">
-        <v>Maintain stream connection verification #289</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #289</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G290" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10567,19 +10567,19 @@
         <v>TC290</v>
       </c>
       <c r="B291" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C291" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D291" t="str">
-        <v>Validate JWT handshake verification #290</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #290</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G291" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10602,19 +10602,19 @@
         <v>TC291</v>
       </c>
       <c r="B292" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C292" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D292" t="str">
-        <v>Secure JSON retrieval verification #291</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #291</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G292" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10637,19 +10637,19 @@
         <v>TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C293" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D293" t="str">
-        <v>Maintain stream connection verification #292</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #292</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G293" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10672,19 +10672,19 @@
         <v>TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C294" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D294" t="str">
-        <v>Validate JWT handshake verification #293</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #293</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G294" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10707,19 +10707,19 @@
         <v>TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C295" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D295" t="str">
-        <v>Secure JSON retrieval verification #294</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #294</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G295" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10742,19 +10742,19 @@
         <v>TC295</v>
       </c>
       <c r="B296" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C296" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D296" t="str">
-        <v>Maintain stream connection verification #295</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #295</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G296" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10777,19 +10777,19 @@
         <v>TC296</v>
       </c>
       <c r="B297" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C297" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D297" t="str">
-        <v>Validate JWT handshake verification #296</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #296</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G297" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10812,19 +10812,19 @@
         <v>TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C298" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D298" t="str">
-        <v>Secure JSON retrieval verification #297</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #297</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G298" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10847,19 +10847,19 @@
         <v>TC298</v>
       </c>
       <c r="B299" t="str">
-        <v>OpenRouter</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C299" t="str">
-        <v>AI Engine</v>
+        <v>Relational</v>
       </c>
       <c r="D299" t="str">
-        <v>Maintain stream connection verification #298</v>
+        <v>Validate structural SQL inserts to ai_chat_history logs verification #298</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to OpenRouter and perform AI Engine action</v>
+        <v>Navigate to Supabase DB and perform Relational action</v>
       </c>
       <c r="G299" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10882,19 +10882,19 @@
         <v>TC299</v>
       </c>
       <c r="B300" t="str">
-        <v>Supabase</v>
+        <v>OpenRouter</v>
       </c>
       <c r="C300" t="str">
-        <v>Auth</v>
+        <v>Completions API</v>
       </c>
       <c r="D300" t="str">
-        <v>Validate JWT handshake verification #299</v>
+        <v>Fetch AI response payloads securely via fetch() layer verification #299</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Supabase and perform Auth action</v>
+        <v>Navigate to OpenRouter and perform Completions API action</v>
       </c>
       <c r="G300" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10917,19 +10917,19 @@
         <v>TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>Database</v>
+        <v>Supabase DB</v>
       </c>
       <c r="C301" t="str">
-        <v>/api/users</v>
+        <v>EAV Schema</v>
       </c>
       <c r="D301" t="str">
-        <v>Secure JSON retrieval verification #300</v>
+        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #300</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Database and perform /api/users action</v>
+        <v>Navigate to Supabase DB and perform EAV Schema action</v>
       </c>
       <c r="G301" t="str">
         <v>Action completes successfully within standard latency bounds</v>

--- a/e2e_tests_suite/Report_03_API_Testing.xlsx
+++ b/e2e_tests_suite/Report_03_API_Testing.xlsx
@@ -455,16 +455,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C2" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D2" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #1</v>
+        <v>Validate cascading relational data purge during account drop verification #1</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G2" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -522,19 +522,19 @@
         <v>TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C4" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #3</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #3</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G4" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -560,16 +560,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C5" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D5" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #4</v>
+        <v>Validate cascading relational data purge during account drop verification #4</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G5" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -627,19 +627,19 @@
         <v>TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C7" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D7" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #6</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #6</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G7" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -665,16 +665,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C8" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D8" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #7</v>
+        <v>Validate cascading relational data purge during account drop verification #7</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G8" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -732,19 +732,19 @@
         <v>TC009</v>
       </c>
       <c r="B10" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C10" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D10" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #9</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #9</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G10" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -770,16 +770,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C11" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D11" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #10</v>
+        <v>Validate cascading relational data purge during account drop verification #10</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G11" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -837,19 +837,19 @@
         <v>TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C13" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D13" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #12</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #12</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G13" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -875,16 +875,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C14" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D14" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #13</v>
+        <v>Validate cascading relational data purge during account drop verification #13</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G14" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -942,19 +942,19 @@
         <v>TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C16" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #15</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #15</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G16" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -980,16 +980,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C17" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D17" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #16</v>
+        <v>Validate cascading relational data purge during account drop verification #16</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G17" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1047,19 +1047,19 @@
         <v>TC018</v>
       </c>
       <c r="B19" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C19" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D19" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #18</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #18</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G19" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1085,16 +1085,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C20" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D20" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #19</v>
+        <v>Validate cascading relational data purge during account drop verification #19</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G20" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1152,19 +1152,19 @@
         <v>TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C22" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #21</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #21</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G22" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1190,16 +1190,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C23" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D23" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #22</v>
+        <v>Validate cascading relational data purge during account drop verification #22</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G23" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1257,19 +1257,19 @@
         <v>TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C25" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #24</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #24</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G25" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1295,16 +1295,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C26" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D26" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #25</v>
+        <v>Validate cascading relational data purge during account drop verification #25</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G26" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1362,19 +1362,19 @@
         <v>TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C28" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D28" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #27</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #27</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G28" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1400,16 +1400,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C29" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D29" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #28</v>
+        <v>Validate cascading relational data purge during account drop verification #28</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G29" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1467,19 +1467,19 @@
         <v>TC030</v>
       </c>
       <c r="B31" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C31" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D31" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #30</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #30</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G31" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1505,16 +1505,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C32" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D32" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #31</v>
+        <v>Validate cascading relational data purge during account drop verification #31</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G32" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1572,19 +1572,19 @@
         <v>TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C34" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D34" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #33</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #33</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G34" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1610,16 +1610,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C35" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D35" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #34</v>
+        <v>Validate cascading relational data purge during account drop verification #34</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G35" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1677,19 +1677,19 @@
         <v>TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C37" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D37" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #36</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #36</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G37" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1715,16 +1715,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C38" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D38" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #37</v>
+        <v>Validate cascading relational data purge during account drop verification #37</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G38" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1782,19 +1782,19 @@
         <v>TC039</v>
       </c>
       <c r="B40" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C40" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D40" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #39</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #39</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G40" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1820,16 +1820,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C41" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D41" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #40</v>
+        <v>Validate cascading relational data purge during account drop verification #40</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G41" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1887,19 +1887,19 @@
         <v>TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C43" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D43" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #42</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #42</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G43" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1925,16 +1925,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C44" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D44" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #43</v>
+        <v>Validate cascading relational data purge during account drop verification #43</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G44" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1992,19 +1992,19 @@
         <v>TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C46" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D46" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #45</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #45</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G46" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2030,16 +2030,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C47" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D47" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #46</v>
+        <v>Validate cascading relational data purge during account drop verification #46</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G47" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2097,19 +2097,19 @@
         <v>TC048</v>
       </c>
       <c r="B49" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C49" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D49" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #48</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #48</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G49" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2135,16 +2135,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C50" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D50" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #49</v>
+        <v>Validate cascading relational data purge during account drop verification #49</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G50" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2202,19 +2202,19 @@
         <v>TC051</v>
       </c>
       <c r="B52" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C52" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #51</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #51</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G52" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2240,16 +2240,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C53" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D53" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #52</v>
+        <v>Validate cascading relational data purge during account drop verification #52</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G53" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2307,19 +2307,19 @@
         <v>TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C55" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D55" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #54</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #54</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G55" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2345,16 +2345,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C56" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D56" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #55</v>
+        <v>Validate cascading relational data purge during account drop verification #55</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G56" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2412,19 +2412,19 @@
         <v>TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C58" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D58" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #57</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #57</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G58" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2450,16 +2450,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C59" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D59" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #58</v>
+        <v>Validate cascading relational data purge during account drop verification #58</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G59" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2517,19 +2517,19 @@
         <v>TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C61" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #60</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #60</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G61" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2555,16 +2555,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C62" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D62" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #61</v>
+        <v>Validate cascading relational data purge during account drop verification #61</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G62" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2622,19 +2622,19 @@
         <v>TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C64" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D64" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #63</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #63</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G64" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2660,16 +2660,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C65" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D65" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #64</v>
+        <v>Validate cascading relational data purge during account drop verification #64</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G65" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2727,19 +2727,19 @@
         <v>TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C67" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D67" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #66</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #66</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G67" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2765,16 +2765,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C68" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D68" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #67</v>
+        <v>Validate cascading relational data purge during account drop verification #67</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G68" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2832,19 +2832,19 @@
         <v>TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C70" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D70" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #69</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #69</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G70" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2870,16 +2870,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C71" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D71" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #70</v>
+        <v>Validate cascading relational data purge during account drop verification #70</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G71" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2937,19 +2937,19 @@
         <v>TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C73" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D73" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #72</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #72</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G73" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2975,16 +2975,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C74" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D74" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #73</v>
+        <v>Validate cascading relational data purge during account drop verification #73</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G74" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3042,19 +3042,19 @@
         <v>TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C76" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D76" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #75</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #75</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G76" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3080,16 +3080,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C77" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D77" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #76</v>
+        <v>Validate cascading relational data purge during account drop verification #76</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G77" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3147,19 +3147,19 @@
         <v>TC078</v>
       </c>
       <c r="B79" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C79" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D79" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #78</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #78</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G79" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3185,16 +3185,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C80" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D80" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #79</v>
+        <v>Validate cascading relational data purge during account drop verification #79</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G80" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3252,19 +3252,19 @@
         <v>TC081</v>
       </c>
       <c r="B82" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C82" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D82" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #81</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #81</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G82" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3290,16 +3290,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C83" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D83" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #82</v>
+        <v>Validate cascading relational data purge during account drop verification #82</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G83" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3357,19 +3357,19 @@
         <v>TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C85" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D85" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #84</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #84</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G85" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3395,16 +3395,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C86" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D86" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #85</v>
+        <v>Validate cascading relational data purge during account drop verification #85</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G86" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3462,19 +3462,19 @@
         <v>TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C88" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D88" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #87</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #87</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G88" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3500,16 +3500,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C89" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D89" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #88</v>
+        <v>Validate cascading relational data purge during account drop verification #88</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G89" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3567,19 +3567,19 @@
         <v>TC090</v>
       </c>
       <c r="B91" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C91" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D91" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #90</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #90</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G91" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3605,16 +3605,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C92" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D92" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #91</v>
+        <v>Validate cascading relational data purge during account drop verification #91</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G92" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3672,19 +3672,19 @@
         <v>TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C94" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D94" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #93</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #93</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G94" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3710,16 +3710,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C95" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D95" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #94</v>
+        <v>Validate cascading relational data purge during account drop verification #94</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G95" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3777,19 +3777,19 @@
         <v>TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C97" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #96</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #96</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G97" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3815,16 +3815,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C98" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D98" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #97</v>
+        <v>Validate cascading relational data purge during account drop verification #97</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G98" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3882,19 +3882,19 @@
         <v>TC099</v>
       </c>
       <c r="B100" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C100" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D100" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #99</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #99</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G100" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3920,16 +3920,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C101" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D101" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #100</v>
+        <v>Validate cascading relational data purge during account drop verification #100</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G101" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3987,19 +3987,19 @@
         <v>TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C103" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D103" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #102</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #102</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G103" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4025,16 +4025,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C104" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D104" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #103</v>
+        <v>Validate cascading relational data purge during account drop verification #103</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G104" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4092,19 +4092,19 @@
         <v>TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C106" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D106" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #105</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #105</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G106" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4130,16 +4130,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C107" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D107" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #106</v>
+        <v>Validate cascading relational data purge during account drop verification #106</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G107" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4197,19 +4197,19 @@
         <v>TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C109" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D109" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #108</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #108</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G109" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4235,16 +4235,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C110" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D110" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #109</v>
+        <v>Validate cascading relational data purge during account drop verification #109</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G110" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4302,19 +4302,19 @@
         <v>TC111</v>
       </c>
       <c r="B112" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C112" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D112" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #111</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #111</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G112" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4340,16 +4340,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C113" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D113" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #112</v>
+        <v>Validate cascading relational data purge during account drop verification #112</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G113" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4407,19 +4407,19 @@
         <v>TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C115" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D115" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #114</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #114</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G115" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4445,16 +4445,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C116" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D116" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #115</v>
+        <v>Validate cascading relational data purge during account drop verification #115</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G116" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4512,19 +4512,19 @@
         <v>TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C118" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D118" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #117</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #117</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G118" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4550,16 +4550,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C119" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D119" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #118</v>
+        <v>Validate cascading relational data purge during account drop verification #118</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G119" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4617,19 +4617,19 @@
         <v>TC120</v>
       </c>
       <c r="B121" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C121" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D121" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #120</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #120</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G121" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4655,16 +4655,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C122" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D122" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #121</v>
+        <v>Validate cascading relational data purge during account drop verification #121</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G122" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4722,19 +4722,19 @@
         <v>TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C124" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D124" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #123</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #123</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G124" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4760,16 +4760,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C125" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D125" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #124</v>
+        <v>Validate cascading relational data purge during account drop verification #124</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G125" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4827,19 +4827,19 @@
         <v>TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C127" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D127" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #126</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #126</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G127" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4865,16 +4865,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C128" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D128" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #127</v>
+        <v>Validate cascading relational data purge during account drop verification #127</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G128" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4932,19 +4932,19 @@
         <v>TC129</v>
       </c>
       <c r="B130" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C130" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D130" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #129</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #129</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G130" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4970,16 +4970,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C131" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D131" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #130</v>
+        <v>Validate cascading relational data purge during account drop verification #130</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G131" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5037,19 +5037,19 @@
         <v>TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C133" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D133" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #132</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #132</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G133" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5075,16 +5075,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C134" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D134" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #133</v>
+        <v>Validate cascading relational data purge during account drop verification #133</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G134" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5142,19 +5142,19 @@
         <v>TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C136" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D136" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #135</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #135</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G136" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5180,16 +5180,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C137" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D137" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #136</v>
+        <v>Validate cascading relational data purge during account drop verification #136</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G137" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5247,19 +5247,19 @@
         <v>TC138</v>
       </c>
       <c r="B139" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C139" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D139" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #138</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #138</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G139" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5285,16 +5285,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C140" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D140" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #139</v>
+        <v>Validate cascading relational data purge during account drop verification #139</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G140" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5352,19 +5352,19 @@
         <v>TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C142" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D142" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #141</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #141</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G142" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5390,16 +5390,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C143" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D143" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #142</v>
+        <v>Validate cascading relational data purge during account drop verification #142</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G143" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5457,19 +5457,19 @@
         <v>TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C145" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D145" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #144</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #144</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G145" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5495,16 +5495,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C146" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D146" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #145</v>
+        <v>Validate cascading relational data purge during account drop verification #145</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G146" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5562,19 +5562,19 @@
         <v>TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C148" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D148" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #147</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #147</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G148" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5600,16 +5600,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C149" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D149" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #148</v>
+        <v>Validate cascading relational data purge during account drop verification #148</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G149" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5667,19 +5667,19 @@
         <v>TC150</v>
       </c>
       <c r="B151" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C151" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D151" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #150</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #150</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G151" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5705,16 +5705,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C152" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D152" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #151</v>
+        <v>Validate cascading relational data purge during account drop verification #151</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G152" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5772,19 +5772,19 @@
         <v>TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C154" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D154" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #153</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #153</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G154" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5810,16 +5810,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C155" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D155" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #154</v>
+        <v>Validate cascading relational data purge during account drop verification #154</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G155" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5877,19 +5877,19 @@
         <v>TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C157" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D157" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #156</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #156</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G157" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5915,16 +5915,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C158" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D158" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #157</v>
+        <v>Validate cascading relational data purge during account drop verification #157</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G158" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5982,19 +5982,19 @@
         <v>TC159</v>
       </c>
       <c r="B160" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C160" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D160" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #159</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #159</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G160" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6020,16 +6020,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C161" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D161" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #160</v>
+        <v>Validate cascading relational data purge during account drop verification #160</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G161" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6087,19 +6087,19 @@
         <v>TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C163" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D163" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #162</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #162</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G163" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6125,16 +6125,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C164" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D164" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #163</v>
+        <v>Validate cascading relational data purge during account drop verification #163</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G164" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6192,19 +6192,19 @@
         <v>TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C166" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D166" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #165</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #165</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G166" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6230,16 +6230,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C167" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D167" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #166</v>
+        <v>Validate cascading relational data purge during account drop verification #166</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G167" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6297,19 +6297,19 @@
         <v>TC168</v>
       </c>
       <c r="B169" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C169" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D169" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #168</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #168</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G169" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6335,16 +6335,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C170" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D170" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #169</v>
+        <v>Validate cascading relational data purge during account drop verification #169</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G170" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6402,19 +6402,19 @@
         <v>TC171</v>
       </c>
       <c r="B172" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C172" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D172" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #171</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #171</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G172" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6440,16 +6440,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C173" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D173" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #172</v>
+        <v>Validate cascading relational data purge during account drop verification #172</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G173" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6507,19 +6507,19 @@
         <v>TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C175" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D175" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #174</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #174</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G175" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6545,16 +6545,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C176" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D176" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #175</v>
+        <v>Validate cascading relational data purge during account drop verification #175</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G176" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6612,19 +6612,19 @@
         <v>TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C178" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D178" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #177</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #177</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G178" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6650,16 +6650,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C179" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D179" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #178</v>
+        <v>Validate cascading relational data purge during account drop verification #178</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G179" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6717,19 +6717,19 @@
         <v>TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C181" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D181" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #180</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #180</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G181" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6755,16 +6755,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C182" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D182" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #181</v>
+        <v>Validate cascading relational data purge during account drop verification #181</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G182" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6822,19 +6822,19 @@
         <v>TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C184" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D184" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #183</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #183</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G184" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6860,16 +6860,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C185" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D185" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #184</v>
+        <v>Validate cascading relational data purge during account drop verification #184</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G185" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6927,19 +6927,19 @@
         <v>TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C187" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D187" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #186</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #186</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G187" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6965,16 +6965,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C188" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D188" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #187</v>
+        <v>Validate cascading relational data purge during account drop verification #187</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G188" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7032,19 +7032,19 @@
         <v>TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C190" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D190" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #189</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #189</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G190" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7070,16 +7070,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C191" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D191" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #190</v>
+        <v>Validate cascading relational data purge during account drop verification #190</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G191" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7137,19 +7137,19 @@
         <v>TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C193" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D193" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #192</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #192</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G193" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7175,16 +7175,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C194" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D194" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #193</v>
+        <v>Validate cascading relational data purge during account drop verification #193</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G194" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7242,19 +7242,19 @@
         <v>TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C196" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D196" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #195</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #195</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G196" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7280,16 +7280,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C197" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D197" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #196</v>
+        <v>Validate cascading relational data purge during account drop verification #196</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G197" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7347,19 +7347,19 @@
         <v>TC198</v>
       </c>
       <c r="B199" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C199" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D199" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #198</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #198</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G199" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7385,16 +7385,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C200" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D200" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #199</v>
+        <v>Validate cascading relational data purge during account drop verification #199</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G200" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7452,19 +7452,19 @@
         <v>TC201</v>
       </c>
       <c r="B202" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C202" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D202" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #201</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #201</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G202" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7490,16 +7490,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C203" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D203" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #202</v>
+        <v>Validate cascading relational data purge during account drop verification #202</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G203" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7557,19 +7557,19 @@
         <v>TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C205" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D205" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #204</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #204</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G205" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7595,16 +7595,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C206" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D206" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #205</v>
+        <v>Validate cascading relational data purge during account drop verification #205</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G206" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7662,19 +7662,19 @@
         <v>TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C208" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D208" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #207</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #207</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G208" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7700,16 +7700,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C209" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D209" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #208</v>
+        <v>Validate cascading relational data purge during account drop verification #208</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G209" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7767,19 +7767,19 @@
         <v>TC210</v>
       </c>
       <c r="B211" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C211" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D211" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #210</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #210</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G211" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7805,16 +7805,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C212" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D212" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #211</v>
+        <v>Validate cascading relational data purge during account drop verification #211</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G212" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7872,19 +7872,19 @@
         <v>TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C214" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D214" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #213</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #213</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G214" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7910,16 +7910,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C215" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D215" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #214</v>
+        <v>Validate cascading relational data purge during account drop verification #214</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G215" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7977,19 +7977,19 @@
         <v>TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C217" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D217" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #216</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #216</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G217" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8015,16 +8015,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C218" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D218" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #217</v>
+        <v>Validate cascading relational data purge during account drop verification #217</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G218" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8082,19 +8082,19 @@
         <v>TC219</v>
       </c>
       <c r="B220" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C220" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D220" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #219</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #219</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G220" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8120,16 +8120,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C221" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D221" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #220</v>
+        <v>Validate cascading relational data purge during account drop verification #220</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G221" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8187,19 +8187,19 @@
         <v>TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C223" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D223" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #222</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #222</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G223" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8225,16 +8225,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C224" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D224" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #223</v>
+        <v>Validate cascading relational data purge during account drop verification #223</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G224" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8292,19 +8292,19 @@
         <v>TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C226" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D226" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #225</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #225</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G226" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8330,16 +8330,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C227" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D227" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #226</v>
+        <v>Validate cascading relational data purge during account drop verification #226</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G227" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8397,19 +8397,19 @@
         <v>TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C229" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D229" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #228</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #228</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G229" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8435,16 +8435,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C230" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D230" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #229</v>
+        <v>Validate cascading relational data purge during account drop verification #229</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G230" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8502,19 +8502,19 @@
         <v>TC231</v>
       </c>
       <c r="B232" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C232" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D232" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #231</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #231</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G232" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8540,16 +8540,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C233" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D233" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #232</v>
+        <v>Validate cascading relational data purge during account drop verification #232</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G233" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8607,19 +8607,19 @@
         <v>TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C235" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D235" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #234</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #234</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G235" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8645,16 +8645,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C236" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D236" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #235</v>
+        <v>Validate cascading relational data purge during account drop verification #235</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G236" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8712,19 +8712,19 @@
         <v>TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C238" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D238" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #237</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #237</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G238" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8750,16 +8750,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C239" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D239" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #238</v>
+        <v>Validate cascading relational data purge during account drop verification #238</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G239" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8817,19 +8817,19 @@
         <v>TC240</v>
       </c>
       <c r="B241" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C241" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D241" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #240</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #240</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G241" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8855,16 +8855,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C242" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D242" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #241</v>
+        <v>Validate cascading relational data purge during account drop verification #241</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G242" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8922,19 +8922,19 @@
         <v>TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C244" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D244" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #243</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #243</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G244" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8960,16 +8960,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C245" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D245" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #244</v>
+        <v>Validate cascading relational data purge during account drop verification #244</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G245" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9027,19 +9027,19 @@
         <v>TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C247" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D247" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #246</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #246</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G247" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9065,16 +9065,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C248" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D248" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #247</v>
+        <v>Validate cascading relational data purge during account drop verification #247</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G248" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9132,19 +9132,19 @@
         <v>TC249</v>
       </c>
       <c r="B250" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C250" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D250" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #249</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #249</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G250" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9170,16 +9170,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C251" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D251" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #250</v>
+        <v>Validate cascading relational data purge during account drop verification #250</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G251" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9237,19 +9237,19 @@
         <v>TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C253" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D253" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #252</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #252</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G253" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9275,16 +9275,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C254" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D254" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #253</v>
+        <v>Validate cascading relational data purge during account drop verification #253</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G254" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9342,19 +9342,19 @@
         <v>TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C256" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D256" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #255</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #255</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G256" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9380,16 +9380,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C257" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D257" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #256</v>
+        <v>Validate cascading relational data purge during account drop verification #256</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G257" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9447,19 +9447,19 @@
         <v>TC258</v>
       </c>
       <c r="B259" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C259" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D259" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #258</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #258</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G259" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9485,16 +9485,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C260" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D260" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #259</v>
+        <v>Validate cascading relational data purge during account drop verification #259</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G260" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9552,19 +9552,19 @@
         <v>TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C262" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D262" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #261</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #261</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G262" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9590,16 +9590,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C263" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D263" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #262</v>
+        <v>Validate cascading relational data purge during account drop verification #262</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G263" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9657,19 +9657,19 @@
         <v>TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C265" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D265" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #264</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #264</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G265" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9695,16 +9695,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C266" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D266" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #265</v>
+        <v>Validate cascading relational data purge during account drop verification #265</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G266" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9762,19 +9762,19 @@
         <v>TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C268" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D268" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #267</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #267</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G268" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9800,16 +9800,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C269" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D269" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #268</v>
+        <v>Validate cascading relational data purge during account drop verification #268</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G269" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9867,19 +9867,19 @@
         <v>TC270</v>
       </c>
       <c r="B271" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C271" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D271" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #270</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #270</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G271" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9905,16 +9905,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C272" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D272" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #271</v>
+        <v>Validate cascading relational data purge during account drop verification #271</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G272" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9972,19 +9972,19 @@
         <v>TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C274" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D274" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #273</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #273</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G274" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10010,16 +10010,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C275" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D275" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #274</v>
+        <v>Validate cascading relational data purge during account drop verification #274</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G275" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10077,19 +10077,19 @@
         <v>TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C277" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D277" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #276</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #276</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G277" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10115,16 +10115,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C278" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D278" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #277</v>
+        <v>Validate cascading relational data purge during account drop verification #277</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G278" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10182,19 +10182,19 @@
         <v>TC279</v>
       </c>
       <c r="B280" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C280" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D280" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #279</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #279</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G280" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10220,16 +10220,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C281" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D281" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #280</v>
+        <v>Validate cascading relational data purge during account drop verification #280</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G281" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10287,19 +10287,19 @@
         <v>TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C283" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D283" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #282</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #282</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G283" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10325,16 +10325,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C284" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D284" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #283</v>
+        <v>Validate cascading relational data purge during account drop verification #283</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G284" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10392,19 +10392,19 @@
         <v>TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C286" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D286" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #285</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #285</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G286" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10430,16 +10430,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C287" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D287" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #286</v>
+        <v>Validate cascading relational data purge during account drop verification #286</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G287" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10497,19 +10497,19 @@
         <v>TC288</v>
       </c>
       <c r="B289" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C289" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D289" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #288</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #288</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G289" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10535,16 +10535,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C290" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D290" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #289</v>
+        <v>Validate cascading relational data purge during account drop verification #289</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G290" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10602,19 +10602,19 @@
         <v>TC291</v>
       </c>
       <c r="B292" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C292" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D292" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #291</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #291</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G292" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10640,16 +10640,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C293" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D293" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #292</v>
+        <v>Validate cascading relational data purge during account drop verification #292</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G293" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10707,19 +10707,19 @@
         <v>TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C295" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D295" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #294</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #294</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G295" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10745,16 +10745,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C296" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D296" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #295</v>
+        <v>Validate cascading relational data purge during account drop verification #295</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G296" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10812,19 +10812,19 @@
         <v>TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C298" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D298" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #297</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #297</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G298" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10850,16 +10850,16 @@
         <v>Supabase DB</v>
       </c>
       <c r="C299" t="str">
-        <v>Relational</v>
+        <v>Account Deletion</v>
       </c>
       <c r="D299" t="str">
-        <v>Validate structural SQL inserts to ai_chat_history logs verification #298</v>
+        <v>Validate cascading relational data purge during account drop verification #298</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to Supabase DB and perform Relational action</v>
+        <v>Navigate to Supabase DB and perform Account Deletion action</v>
       </c>
       <c r="G299" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10917,19 +10917,19 @@
         <v>TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>Supabase DB</v>
+        <v>Auth API</v>
       </c>
       <c r="C301" t="str">
-        <v>EAV Schema</v>
+        <v>Forgot/Change Password</v>
       </c>
       <c r="D301" t="str">
-        <v>Verify dynamic JSON storage formatting for 'userdata' table verification #300</v>
+        <v>Verify encrypted token dispatch for credential overrides verification #300</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Supabase DB and perform EAV Schema action</v>
+        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
       </c>
       <c r="G301" t="str">
         <v>Action completes successfully within standard latency bounds</v>

--- a/e2e_tests_suite/Report_03_API_Testing.xlsx
+++ b/e2e_tests_suite/Report_03_API_Testing.xlsx
@@ -452,19 +452,19 @@
         <v>TC001</v>
       </c>
       <c r="B2" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C2" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D2" t="str">
-        <v>Validate cascading relational data purge during account drop verification #1</v>
+        <v>Calculate massive dataset into visual trend chart verification #1</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G2" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -487,19 +487,19 @@
         <v>TC002</v>
       </c>
       <c r="B3" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C3" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D3" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #2</v>
+        <v>Push active vital stream into Daily Protocol engine verification #2</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G3" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -522,19 +522,19 @@
         <v>TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C4" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #3</v>
+        <v>Fetch structural JSON logic for health learning verification #3</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G4" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -557,19 +557,19 @@
         <v>TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C5" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D5" t="str">
-        <v>Validate cascading relational data purge during account drop verification #4</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #4</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G5" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -592,19 +592,19 @@
         <v>TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C6" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D6" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #5</v>
+        <v>Sync anonymous analytics to improve AI securely verification #5</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G6" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -627,19 +627,19 @@
         <v>TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C7" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D7" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #6</v>
+        <v>Bundle and download all remote records into local ZIP verification #6</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G7" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -662,19 +662,19 @@
         <v>TC007</v>
       </c>
       <c r="B8" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C8" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D8" t="str">
-        <v>Validate cascading relational data purge during account drop verification #7</v>
+        <v>Permanently drop relational database schemas entirely verification #7</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G8" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -697,19 +697,19 @@
         <v>TC008</v>
       </c>
       <c r="B9" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C9" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D9" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #8</v>
+        <v>Record new entry for blood pressure/heart rate verification #8</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G9" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -732,19 +732,19 @@
         <v>TC009</v>
       </c>
       <c r="B10" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C10" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D10" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #9</v>
+        <v>Calculate massive dataset into visual trend chart verification #9</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G10" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -767,19 +767,19 @@
         <v>TC010</v>
       </c>
       <c r="B11" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C11" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D11" t="str">
-        <v>Validate cascading relational data purge during account drop verification #10</v>
+        <v>Push active vital stream into Daily Protocol engine verification #10</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G11" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -802,19 +802,19 @@
         <v>TC011</v>
       </c>
       <c r="B12" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C12" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D12" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #11</v>
+        <v>Fetch structural JSON logic for health learning verification #11</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G12" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -837,19 +837,19 @@
         <v>TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C13" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D13" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #12</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #12</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G13" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -872,19 +872,19 @@
         <v>TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C14" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D14" t="str">
-        <v>Validate cascading relational data purge during account drop verification #13</v>
+        <v>Sync anonymous analytics to improve AI securely verification #13</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G14" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -907,19 +907,19 @@
         <v>TC014</v>
       </c>
       <c r="B15" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C15" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D15" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #14</v>
+        <v>Bundle and download all remote records into local ZIP verification #14</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G15" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -942,19 +942,19 @@
         <v>TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C16" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #15</v>
+        <v>Permanently drop relational database schemas entirely verification #15</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G16" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -977,19 +977,19 @@
         <v>TC016</v>
       </c>
       <c r="B17" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C17" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D17" t="str">
-        <v>Validate cascading relational data purge during account drop verification #16</v>
+        <v>Record new entry for blood pressure/heart rate verification #16</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G17" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1012,19 +1012,19 @@
         <v>TC017</v>
       </c>
       <c r="B18" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C18" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D18" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #17</v>
+        <v>Calculate massive dataset into visual trend chart verification #17</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G18" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1047,19 +1047,19 @@
         <v>TC018</v>
       </c>
       <c r="B19" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C19" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D19" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #18</v>
+        <v>Push active vital stream into Daily Protocol engine verification #18</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G19" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1082,19 +1082,19 @@
         <v>TC019</v>
       </c>
       <c r="B20" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C20" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D20" t="str">
-        <v>Validate cascading relational data purge during account drop verification #19</v>
+        <v>Fetch structural JSON logic for health learning verification #19</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G20" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1117,19 +1117,19 @@
         <v>TC020</v>
       </c>
       <c r="B21" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C21" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D21" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #20</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #20</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G21" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1152,19 +1152,19 @@
         <v>TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C22" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #21</v>
+        <v>Sync anonymous analytics to improve AI securely verification #21</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G22" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1187,19 +1187,19 @@
         <v>TC022</v>
       </c>
       <c r="B23" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C23" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D23" t="str">
-        <v>Validate cascading relational data purge during account drop verification #22</v>
+        <v>Bundle and download all remote records into local ZIP verification #22</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G23" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1222,19 +1222,19 @@
         <v>TC023</v>
       </c>
       <c r="B24" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C24" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D24" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #23</v>
+        <v>Permanently drop relational database schemas entirely verification #23</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G24" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1257,19 +1257,19 @@
         <v>TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C25" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #24</v>
+        <v>Record new entry for blood pressure/heart rate verification #24</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G25" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1292,19 +1292,19 @@
         <v>TC025</v>
       </c>
       <c r="B26" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C26" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D26" t="str">
-        <v>Validate cascading relational data purge during account drop verification #25</v>
+        <v>Calculate massive dataset into visual trend chart verification #25</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G26" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1327,19 +1327,19 @@
         <v>TC026</v>
       </c>
       <c r="B27" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C27" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D27" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #26</v>
+        <v>Push active vital stream into Daily Protocol engine verification #26</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G27" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1362,19 +1362,19 @@
         <v>TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C28" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D28" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #27</v>
+        <v>Fetch structural JSON logic for health learning verification #27</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G28" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1397,19 +1397,19 @@
         <v>TC028</v>
       </c>
       <c r="B29" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C29" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D29" t="str">
-        <v>Validate cascading relational data purge during account drop verification #28</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #28</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G29" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1432,19 +1432,19 @@
         <v>TC029</v>
       </c>
       <c r="B30" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C30" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D30" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #29</v>
+        <v>Sync anonymous analytics to improve AI securely verification #29</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G30" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1467,19 +1467,19 @@
         <v>TC030</v>
       </c>
       <c r="B31" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C31" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D31" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #30</v>
+        <v>Bundle and download all remote records into local ZIP verification #30</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G31" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1502,19 +1502,19 @@
         <v>TC031</v>
       </c>
       <c r="B32" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C32" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D32" t="str">
-        <v>Validate cascading relational data purge during account drop verification #31</v>
+        <v>Permanently drop relational database schemas entirely verification #31</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G32" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1537,19 +1537,19 @@
         <v>TC032</v>
       </c>
       <c r="B33" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C33" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D33" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #32</v>
+        <v>Record new entry for blood pressure/heart rate verification #32</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G33" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1572,19 +1572,19 @@
         <v>TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C34" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D34" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #33</v>
+        <v>Calculate massive dataset into visual trend chart verification #33</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G34" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1607,19 +1607,19 @@
         <v>TC034</v>
       </c>
       <c r="B35" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C35" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D35" t="str">
-        <v>Validate cascading relational data purge during account drop verification #34</v>
+        <v>Push active vital stream into Daily Protocol engine verification #34</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G35" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1642,19 +1642,19 @@
         <v>TC035</v>
       </c>
       <c r="B36" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C36" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D36" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #35</v>
+        <v>Fetch structural JSON logic for health learning verification #35</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G36" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1677,19 +1677,19 @@
         <v>TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C37" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D37" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #36</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #36</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G37" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1712,19 +1712,19 @@
         <v>TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C38" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D38" t="str">
-        <v>Validate cascading relational data purge during account drop verification #37</v>
+        <v>Sync anonymous analytics to improve AI securely verification #37</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G38" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1747,19 +1747,19 @@
         <v>TC038</v>
       </c>
       <c r="B39" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C39" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D39" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #38</v>
+        <v>Bundle and download all remote records into local ZIP verification #38</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G39" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1782,19 +1782,19 @@
         <v>TC039</v>
       </c>
       <c r="B40" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C40" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D40" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #39</v>
+        <v>Permanently drop relational database schemas entirely verification #39</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G40" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1817,19 +1817,19 @@
         <v>TC040</v>
       </c>
       <c r="B41" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C41" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D41" t="str">
-        <v>Validate cascading relational data purge during account drop verification #40</v>
+        <v>Record new entry for blood pressure/heart rate verification #40</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G41" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1852,19 +1852,19 @@
         <v>TC041</v>
       </c>
       <c r="B42" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C42" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D42" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #41</v>
+        <v>Calculate massive dataset into visual trend chart verification #41</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G42" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1887,19 +1887,19 @@
         <v>TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C43" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D43" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #42</v>
+        <v>Push active vital stream into Daily Protocol engine verification #42</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G43" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1922,19 +1922,19 @@
         <v>TC043</v>
       </c>
       <c r="B44" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C44" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D44" t="str">
-        <v>Validate cascading relational data purge during account drop verification #43</v>
+        <v>Fetch structural JSON logic for health learning verification #43</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G44" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1957,19 +1957,19 @@
         <v>TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C45" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D45" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #44</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #44</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G45" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -1992,19 +1992,19 @@
         <v>TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C46" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D46" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #45</v>
+        <v>Sync anonymous analytics to improve AI securely verification #45</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G46" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2027,19 +2027,19 @@
         <v>TC046</v>
       </c>
       <c r="B47" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C47" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D47" t="str">
-        <v>Validate cascading relational data purge during account drop verification #46</v>
+        <v>Bundle and download all remote records into local ZIP verification #46</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G47" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2062,19 +2062,19 @@
         <v>TC047</v>
       </c>
       <c r="B48" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C48" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D48" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #47</v>
+        <v>Permanently drop relational database schemas entirely verification #47</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G48" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2097,19 +2097,19 @@
         <v>TC048</v>
       </c>
       <c r="B49" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C49" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D49" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #48</v>
+        <v>Record new entry for blood pressure/heart rate verification #48</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G49" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2132,19 +2132,19 @@
         <v>TC049</v>
       </c>
       <c r="B50" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C50" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D50" t="str">
-        <v>Validate cascading relational data purge during account drop verification #49</v>
+        <v>Calculate massive dataset into visual trend chart verification #49</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G50" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2167,19 +2167,19 @@
         <v>TC050</v>
       </c>
       <c r="B51" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C51" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D51" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #50</v>
+        <v>Push active vital stream into Daily Protocol engine verification #50</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G51" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2202,19 +2202,19 @@
         <v>TC051</v>
       </c>
       <c r="B52" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C52" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #51</v>
+        <v>Fetch structural JSON logic for health learning verification #51</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G52" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2237,19 +2237,19 @@
         <v>TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C53" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D53" t="str">
-        <v>Validate cascading relational data purge during account drop verification #52</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #52</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G53" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2272,19 +2272,19 @@
         <v>TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C54" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D54" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #53</v>
+        <v>Sync anonymous analytics to improve AI securely verification #53</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G54" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2307,19 +2307,19 @@
         <v>TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C55" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D55" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #54</v>
+        <v>Bundle and download all remote records into local ZIP verification #54</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G55" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2342,19 +2342,19 @@
         <v>TC055</v>
       </c>
       <c r="B56" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C56" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D56" t="str">
-        <v>Validate cascading relational data purge during account drop verification #55</v>
+        <v>Permanently drop relational database schemas entirely verification #55</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G56" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2377,19 +2377,19 @@
         <v>TC056</v>
       </c>
       <c r="B57" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C57" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D57" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #56</v>
+        <v>Record new entry for blood pressure/heart rate verification #56</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G57" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2412,19 +2412,19 @@
         <v>TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C58" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D58" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #57</v>
+        <v>Calculate massive dataset into visual trend chart verification #57</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G58" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2447,19 +2447,19 @@
         <v>TC058</v>
       </c>
       <c r="B59" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C59" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D59" t="str">
-        <v>Validate cascading relational data purge during account drop verification #58</v>
+        <v>Push active vital stream into Daily Protocol engine verification #58</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G59" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2482,19 +2482,19 @@
         <v>TC059</v>
       </c>
       <c r="B60" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C60" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D60" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #59</v>
+        <v>Fetch structural JSON logic for health learning verification #59</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G60" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2517,19 +2517,19 @@
         <v>TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C61" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #60</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #60</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G61" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2552,19 +2552,19 @@
         <v>TC061</v>
       </c>
       <c r="B62" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C62" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D62" t="str">
-        <v>Validate cascading relational data purge during account drop verification #61</v>
+        <v>Sync anonymous analytics to improve AI securely verification #61</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G62" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2587,19 +2587,19 @@
         <v>TC062</v>
       </c>
       <c r="B63" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C63" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D63" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #62</v>
+        <v>Bundle and download all remote records into local ZIP verification #62</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G63" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2622,19 +2622,19 @@
         <v>TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C64" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D64" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #63</v>
+        <v>Permanently drop relational database schemas entirely verification #63</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G64" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2657,19 +2657,19 @@
         <v>TC064</v>
       </c>
       <c r="B65" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C65" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D65" t="str">
-        <v>Validate cascading relational data purge during account drop verification #64</v>
+        <v>Record new entry for blood pressure/heart rate verification #64</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G65" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2692,19 +2692,19 @@
         <v>TC065</v>
       </c>
       <c r="B66" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C66" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D66" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #65</v>
+        <v>Calculate massive dataset into visual trend chart verification #65</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G66" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2727,19 +2727,19 @@
         <v>TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C67" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D67" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #66</v>
+        <v>Push active vital stream into Daily Protocol engine verification #66</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G67" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2762,19 +2762,19 @@
         <v>TC067</v>
       </c>
       <c r="B68" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C68" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D68" t="str">
-        <v>Validate cascading relational data purge during account drop verification #67</v>
+        <v>Fetch structural JSON logic for health learning verification #67</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G68" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2797,19 +2797,19 @@
         <v>TC068</v>
       </c>
       <c r="B69" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C69" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D69" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #68</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #68</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G69" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2832,19 +2832,19 @@
         <v>TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C70" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D70" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #69</v>
+        <v>Sync anonymous analytics to improve AI securely verification #69</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G70" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2867,19 +2867,19 @@
         <v>TC070</v>
       </c>
       <c r="B71" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C71" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D71" t="str">
-        <v>Validate cascading relational data purge during account drop verification #70</v>
+        <v>Bundle and download all remote records into local ZIP verification #70</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G71" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2902,19 +2902,19 @@
         <v>TC071</v>
       </c>
       <c r="B72" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C72" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D72" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #71</v>
+        <v>Permanently drop relational database schemas entirely verification #71</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G72" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2937,19 +2937,19 @@
         <v>TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C73" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D73" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #72</v>
+        <v>Record new entry for blood pressure/heart rate verification #72</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G73" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -2972,19 +2972,19 @@
         <v>TC073</v>
       </c>
       <c r="B74" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C74" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D74" t="str">
-        <v>Validate cascading relational data purge during account drop verification #73</v>
+        <v>Calculate massive dataset into visual trend chart verification #73</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G74" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3007,19 +3007,19 @@
         <v>TC074</v>
       </c>
       <c r="B75" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C75" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D75" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #74</v>
+        <v>Push active vital stream into Daily Protocol engine verification #74</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G75" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3042,19 +3042,19 @@
         <v>TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C76" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D76" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #75</v>
+        <v>Fetch structural JSON logic for health learning verification #75</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G76" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3077,19 +3077,19 @@
         <v>TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C77" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D77" t="str">
-        <v>Validate cascading relational data purge during account drop verification #76</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #76</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G77" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3112,19 +3112,19 @@
         <v>TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C78" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D78" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #77</v>
+        <v>Sync anonymous analytics to improve AI securely verification #77</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G78" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3147,19 +3147,19 @@
         <v>TC078</v>
       </c>
       <c r="B79" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C79" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D79" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #78</v>
+        <v>Bundle and download all remote records into local ZIP verification #78</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G79" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3182,19 +3182,19 @@
         <v>TC079</v>
       </c>
       <c r="B80" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C80" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D80" t="str">
-        <v>Validate cascading relational data purge during account drop verification #79</v>
+        <v>Permanently drop relational database schemas entirely verification #79</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G80" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3217,19 +3217,19 @@
         <v>TC080</v>
       </c>
       <c r="B81" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C81" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D81" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #80</v>
+        <v>Record new entry for blood pressure/heart rate verification #80</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G81" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3252,19 +3252,19 @@
         <v>TC081</v>
       </c>
       <c r="B82" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C82" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D82" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #81</v>
+        <v>Calculate massive dataset into visual trend chart verification #81</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G82" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3287,19 +3287,19 @@
         <v>TC082</v>
       </c>
       <c r="B83" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C83" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D83" t="str">
-        <v>Validate cascading relational data purge during account drop verification #82</v>
+        <v>Push active vital stream into Daily Protocol engine verification #82</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G83" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3322,19 +3322,19 @@
         <v>TC083</v>
       </c>
       <c r="B84" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C84" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D84" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #83</v>
+        <v>Fetch structural JSON logic for health learning verification #83</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G84" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3357,19 +3357,19 @@
         <v>TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C85" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D85" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #84</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #84</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G85" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3392,19 +3392,19 @@
         <v>TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C86" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D86" t="str">
-        <v>Validate cascading relational data purge during account drop verification #85</v>
+        <v>Sync anonymous analytics to improve AI securely verification #85</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G86" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3427,19 +3427,19 @@
         <v>TC086</v>
       </c>
       <c r="B87" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C87" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D87" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #86</v>
+        <v>Bundle and download all remote records into local ZIP verification #86</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G87" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3462,19 +3462,19 @@
         <v>TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C88" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D88" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #87</v>
+        <v>Permanently drop relational database schemas entirely verification #87</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G88" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3497,19 +3497,19 @@
         <v>TC088</v>
       </c>
       <c r="B89" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C89" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D89" t="str">
-        <v>Validate cascading relational data purge during account drop verification #88</v>
+        <v>Record new entry for blood pressure/heart rate verification #88</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G89" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3532,19 +3532,19 @@
         <v>TC089</v>
       </c>
       <c r="B90" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C90" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D90" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #89</v>
+        <v>Calculate massive dataset into visual trend chart verification #89</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G90" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3567,19 +3567,19 @@
         <v>TC090</v>
       </c>
       <c r="B91" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C91" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D91" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #90</v>
+        <v>Push active vital stream into Daily Protocol engine verification #90</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G91" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3602,19 +3602,19 @@
         <v>TC091</v>
       </c>
       <c r="B92" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C92" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D92" t="str">
-        <v>Validate cascading relational data purge during account drop verification #91</v>
+        <v>Fetch structural JSON logic for health learning verification #91</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G92" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3637,19 +3637,19 @@
         <v>TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C93" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D93" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #92</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #92</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G93" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3672,19 +3672,19 @@
         <v>TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C94" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D94" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #93</v>
+        <v>Sync anonymous analytics to improve AI securely verification #93</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G94" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3707,19 +3707,19 @@
         <v>TC094</v>
       </c>
       <c r="B95" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C95" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D95" t="str">
-        <v>Validate cascading relational data purge during account drop verification #94</v>
+        <v>Bundle and download all remote records into local ZIP verification #94</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G95" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3742,19 +3742,19 @@
         <v>TC095</v>
       </c>
       <c r="B96" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C96" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D96" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #95</v>
+        <v>Permanently drop relational database schemas entirely verification #95</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G96" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3777,19 +3777,19 @@
         <v>TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C97" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #96</v>
+        <v>Record new entry for blood pressure/heart rate verification #96</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G97" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3812,19 +3812,19 @@
         <v>TC097</v>
       </c>
       <c r="B98" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C98" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D98" t="str">
-        <v>Validate cascading relational data purge during account drop verification #97</v>
+        <v>Calculate massive dataset into visual trend chart verification #97</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G98" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3847,19 +3847,19 @@
         <v>TC098</v>
       </c>
       <c r="B99" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C99" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D99" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #98</v>
+        <v>Push active vital stream into Daily Protocol engine verification #98</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G99" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3882,19 +3882,19 @@
         <v>TC099</v>
       </c>
       <c r="B100" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C100" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D100" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #99</v>
+        <v>Fetch structural JSON logic for health learning verification #99</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G100" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3917,19 +3917,19 @@
         <v>TC100</v>
       </c>
       <c r="B101" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C101" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D101" t="str">
-        <v>Validate cascading relational data purge during account drop verification #100</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #100</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G101" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3952,19 +3952,19 @@
         <v>TC101</v>
       </c>
       <c r="B102" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C102" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D102" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #101</v>
+        <v>Sync anonymous analytics to improve AI securely verification #101</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G102" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -3987,19 +3987,19 @@
         <v>TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C103" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D103" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #102</v>
+        <v>Bundle and download all remote records into local ZIP verification #102</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G103" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4022,19 +4022,19 @@
         <v>TC103</v>
       </c>
       <c r="B104" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C104" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D104" t="str">
-        <v>Validate cascading relational data purge during account drop verification #103</v>
+        <v>Permanently drop relational database schemas entirely verification #103</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G104" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4057,19 +4057,19 @@
         <v>TC104</v>
       </c>
       <c r="B105" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C105" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D105" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #104</v>
+        <v>Record new entry for blood pressure/heart rate verification #104</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G105" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4092,19 +4092,19 @@
         <v>TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C106" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D106" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #105</v>
+        <v>Calculate massive dataset into visual trend chart verification #105</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G106" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4127,19 +4127,19 @@
         <v>TC106</v>
       </c>
       <c r="B107" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C107" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D107" t="str">
-        <v>Validate cascading relational data purge during account drop verification #106</v>
+        <v>Push active vital stream into Daily Protocol engine verification #106</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G107" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4162,19 +4162,19 @@
         <v>TC107</v>
       </c>
       <c r="B108" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C108" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D108" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #107</v>
+        <v>Fetch structural JSON logic for health learning verification #107</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G108" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4197,19 +4197,19 @@
         <v>TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C109" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D109" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #108</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #108</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G109" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4232,19 +4232,19 @@
         <v>TC109</v>
       </c>
       <c r="B110" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C110" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D110" t="str">
-        <v>Validate cascading relational data purge during account drop verification #109</v>
+        <v>Sync anonymous analytics to improve AI securely verification #109</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G110" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4267,19 +4267,19 @@
         <v>TC110</v>
       </c>
       <c r="B111" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C111" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D111" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #110</v>
+        <v>Bundle and download all remote records into local ZIP verification #110</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G111" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4302,19 +4302,19 @@
         <v>TC111</v>
       </c>
       <c r="B112" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C112" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D112" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #111</v>
+        <v>Permanently drop relational database schemas entirely verification #111</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G112" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4337,19 +4337,19 @@
         <v>TC112</v>
       </c>
       <c r="B113" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C113" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D113" t="str">
-        <v>Validate cascading relational data purge during account drop verification #112</v>
+        <v>Record new entry for blood pressure/heart rate verification #112</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G113" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4372,19 +4372,19 @@
         <v>TC113</v>
       </c>
       <c r="B114" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C114" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D114" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #113</v>
+        <v>Calculate massive dataset into visual trend chart verification #113</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G114" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4407,19 +4407,19 @@
         <v>TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C115" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D115" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #114</v>
+        <v>Push active vital stream into Daily Protocol engine verification #114</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G115" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4442,19 +4442,19 @@
         <v>TC115</v>
       </c>
       <c r="B116" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C116" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D116" t="str">
-        <v>Validate cascading relational data purge during account drop verification #115</v>
+        <v>Fetch structural JSON logic for health learning verification #115</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G116" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4477,19 +4477,19 @@
         <v>TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C117" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D117" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #116</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #116</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G117" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4512,19 +4512,19 @@
         <v>TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C118" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D118" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #117</v>
+        <v>Sync anonymous analytics to improve AI securely verification #117</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G118" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4547,19 +4547,19 @@
         <v>TC118</v>
       </c>
       <c r="B119" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C119" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D119" t="str">
-        <v>Validate cascading relational data purge during account drop verification #118</v>
+        <v>Bundle and download all remote records into local ZIP verification #118</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G119" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4582,19 +4582,19 @@
         <v>TC119</v>
       </c>
       <c r="B120" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C120" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D120" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #119</v>
+        <v>Permanently drop relational database schemas entirely verification #119</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G120" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4617,19 +4617,19 @@
         <v>TC120</v>
       </c>
       <c r="B121" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C121" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D121" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #120</v>
+        <v>Record new entry for blood pressure/heart rate verification #120</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G121" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4652,19 +4652,19 @@
         <v>TC121</v>
       </c>
       <c r="B122" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C122" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D122" t="str">
-        <v>Validate cascading relational data purge during account drop verification #121</v>
+        <v>Calculate massive dataset into visual trend chart verification #121</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G122" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4687,19 +4687,19 @@
         <v>TC122</v>
       </c>
       <c r="B123" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C123" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D123" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #122</v>
+        <v>Push active vital stream into Daily Protocol engine verification #122</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G123" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4722,19 +4722,19 @@
         <v>TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C124" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D124" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #123</v>
+        <v>Fetch structural JSON logic for health learning verification #123</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G124" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4757,19 +4757,19 @@
         <v>TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C125" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D125" t="str">
-        <v>Validate cascading relational data purge during account drop verification #124</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #124</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G125" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4792,19 +4792,19 @@
         <v>TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C126" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D126" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #125</v>
+        <v>Sync anonymous analytics to improve AI securely verification #125</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G126" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4827,19 +4827,19 @@
         <v>TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C127" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D127" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #126</v>
+        <v>Bundle and download all remote records into local ZIP verification #126</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G127" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4862,19 +4862,19 @@
         <v>TC127</v>
       </c>
       <c r="B128" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C128" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D128" t="str">
-        <v>Validate cascading relational data purge during account drop verification #127</v>
+        <v>Permanently drop relational database schemas entirely verification #127</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G128" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4897,19 +4897,19 @@
         <v>TC128</v>
       </c>
       <c r="B129" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C129" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D129" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #128</v>
+        <v>Record new entry for blood pressure/heart rate verification #128</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G129" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4932,19 +4932,19 @@
         <v>TC129</v>
       </c>
       <c r="B130" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C130" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D130" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #129</v>
+        <v>Calculate massive dataset into visual trend chart verification #129</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G130" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -4967,19 +4967,19 @@
         <v>TC130</v>
       </c>
       <c r="B131" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C131" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D131" t="str">
-        <v>Validate cascading relational data purge during account drop verification #130</v>
+        <v>Push active vital stream into Daily Protocol engine verification #130</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G131" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5002,19 +5002,19 @@
         <v>TC131</v>
       </c>
       <c r="B132" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C132" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D132" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #131</v>
+        <v>Fetch structural JSON logic for health learning verification #131</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G132" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5037,19 +5037,19 @@
         <v>TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C133" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D133" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #132</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #132</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G133" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5072,19 +5072,19 @@
         <v>TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C134" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D134" t="str">
-        <v>Validate cascading relational data purge during account drop verification #133</v>
+        <v>Sync anonymous analytics to improve AI securely verification #133</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G134" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5107,19 +5107,19 @@
         <v>TC134</v>
       </c>
       <c r="B135" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C135" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D135" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #134</v>
+        <v>Bundle and download all remote records into local ZIP verification #134</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G135" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5142,19 +5142,19 @@
         <v>TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C136" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D136" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #135</v>
+        <v>Permanently drop relational database schemas entirely verification #135</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G136" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5177,19 +5177,19 @@
         <v>TC136</v>
       </c>
       <c r="B137" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C137" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D137" t="str">
-        <v>Validate cascading relational data purge during account drop verification #136</v>
+        <v>Record new entry for blood pressure/heart rate verification #136</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G137" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5212,19 +5212,19 @@
         <v>TC137</v>
       </c>
       <c r="B138" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C138" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D138" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #137</v>
+        <v>Calculate massive dataset into visual trend chart verification #137</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G138" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5247,19 +5247,19 @@
         <v>TC138</v>
       </c>
       <c r="B139" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C139" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D139" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #138</v>
+        <v>Push active vital stream into Daily Protocol engine verification #138</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G139" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5282,19 +5282,19 @@
         <v>TC139</v>
       </c>
       <c r="B140" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C140" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D140" t="str">
-        <v>Validate cascading relational data purge during account drop verification #139</v>
+        <v>Fetch structural JSON logic for health learning verification #139</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G140" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5317,19 +5317,19 @@
         <v>TC140</v>
       </c>
       <c r="B141" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C141" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D141" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #140</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #140</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G141" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5352,19 +5352,19 @@
         <v>TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C142" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D142" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #141</v>
+        <v>Sync anonymous analytics to improve AI securely verification #141</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G142" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5387,19 +5387,19 @@
         <v>TC142</v>
       </c>
       <c r="B143" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C143" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D143" t="str">
-        <v>Validate cascading relational data purge during account drop verification #142</v>
+        <v>Bundle and download all remote records into local ZIP verification #142</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G143" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5422,19 +5422,19 @@
         <v>TC143</v>
       </c>
       <c r="B144" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C144" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D144" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #143</v>
+        <v>Permanently drop relational database schemas entirely verification #143</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G144" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5457,19 +5457,19 @@
         <v>TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C145" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D145" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #144</v>
+        <v>Record new entry for blood pressure/heart rate verification #144</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G145" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5492,19 +5492,19 @@
         <v>TC145</v>
       </c>
       <c r="B146" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C146" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D146" t="str">
-        <v>Validate cascading relational data purge during account drop verification #145</v>
+        <v>Calculate massive dataset into visual trend chart verification #145</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G146" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5527,19 +5527,19 @@
         <v>TC146</v>
       </c>
       <c r="B147" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C147" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D147" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #146</v>
+        <v>Push active vital stream into Daily Protocol engine verification #146</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G147" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5562,19 +5562,19 @@
         <v>TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C148" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D148" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #147</v>
+        <v>Fetch structural JSON logic for health learning verification #147</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G148" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5597,19 +5597,19 @@
         <v>TC148</v>
       </c>
       <c r="B149" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C149" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D149" t="str">
-        <v>Validate cascading relational data purge during account drop verification #148</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #148</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G149" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5632,19 +5632,19 @@
         <v>TC149</v>
       </c>
       <c r="B150" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C150" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D150" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #149</v>
+        <v>Sync anonymous analytics to improve AI securely verification #149</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G150" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5667,19 +5667,19 @@
         <v>TC150</v>
       </c>
       <c r="B151" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C151" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D151" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #150</v>
+        <v>Bundle and download all remote records into local ZIP verification #150</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G151" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5702,19 +5702,19 @@
         <v>TC151</v>
       </c>
       <c r="B152" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C152" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D152" t="str">
-        <v>Validate cascading relational data purge during account drop verification #151</v>
+        <v>Permanently drop relational database schemas entirely verification #151</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G152" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5737,19 +5737,19 @@
         <v>TC152</v>
       </c>
       <c r="B153" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C153" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D153" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #152</v>
+        <v>Record new entry for blood pressure/heart rate verification #152</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G153" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5772,19 +5772,19 @@
         <v>TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C154" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D154" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #153</v>
+        <v>Calculate massive dataset into visual trend chart verification #153</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G154" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5807,19 +5807,19 @@
         <v>TC154</v>
       </c>
       <c r="B155" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C155" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D155" t="str">
-        <v>Validate cascading relational data purge during account drop verification #154</v>
+        <v>Push active vital stream into Daily Protocol engine verification #154</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G155" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5842,19 +5842,19 @@
         <v>TC155</v>
       </c>
       <c r="B156" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C156" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D156" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #155</v>
+        <v>Fetch structural JSON logic for health learning verification #155</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G156" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5877,19 +5877,19 @@
         <v>TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C157" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D157" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #156</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #156</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G157" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5912,19 +5912,19 @@
         <v>TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C158" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D158" t="str">
-        <v>Validate cascading relational data purge during account drop verification #157</v>
+        <v>Sync anonymous analytics to improve AI securely verification #157</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G158" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5947,19 +5947,19 @@
         <v>TC158</v>
       </c>
       <c r="B159" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C159" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D159" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #158</v>
+        <v>Bundle and download all remote records into local ZIP verification #158</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G159" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -5982,19 +5982,19 @@
         <v>TC159</v>
       </c>
       <c r="B160" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C160" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D160" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #159</v>
+        <v>Permanently drop relational database schemas entirely verification #159</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G160" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6017,19 +6017,19 @@
         <v>TC160</v>
       </c>
       <c r="B161" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C161" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D161" t="str">
-        <v>Validate cascading relational data purge during account drop verification #160</v>
+        <v>Record new entry for blood pressure/heart rate verification #160</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G161" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6052,19 +6052,19 @@
         <v>TC161</v>
       </c>
       <c r="B162" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C162" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D162" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #161</v>
+        <v>Calculate massive dataset into visual trend chart verification #161</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G162" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6087,19 +6087,19 @@
         <v>TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C163" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D163" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #162</v>
+        <v>Push active vital stream into Daily Protocol engine verification #162</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G163" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6122,19 +6122,19 @@
         <v>TC163</v>
       </c>
       <c r="B164" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C164" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D164" t="str">
-        <v>Validate cascading relational data purge during account drop verification #163</v>
+        <v>Fetch structural JSON logic for health learning verification #163</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G164" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6157,19 +6157,19 @@
         <v>TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C165" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D165" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #164</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #164</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G165" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6192,19 +6192,19 @@
         <v>TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C166" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D166" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #165</v>
+        <v>Sync anonymous analytics to improve AI securely verification #165</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G166" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6227,19 +6227,19 @@
         <v>TC166</v>
       </c>
       <c r="B167" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C167" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D167" t="str">
-        <v>Validate cascading relational data purge during account drop verification #166</v>
+        <v>Bundle and download all remote records into local ZIP verification #166</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G167" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6262,19 +6262,19 @@
         <v>TC167</v>
       </c>
       <c r="B168" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C168" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D168" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #167</v>
+        <v>Permanently drop relational database schemas entirely verification #167</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G168" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6297,19 +6297,19 @@
         <v>TC168</v>
       </c>
       <c r="B169" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C169" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D169" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #168</v>
+        <v>Record new entry for blood pressure/heart rate verification #168</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G169" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6332,19 +6332,19 @@
         <v>TC169</v>
       </c>
       <c r="B170" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C170" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D170" t="str">
-        <v>Validate cascading relational data purge during account drop verification #169</v>
+        <v>Calculate massive dataset into visual trend chart verification #169</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G170" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6367,19 +6367,19 @@
         <v>TC170</v>
       </c>
       <c r="B171" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C171" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D171" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #170</v>
+        <v>Push active vital stream into Daily Protocol engine verification #170</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G171" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6402,19 +6402,19 @@
         <v>TC171</v>
       </c>
       <c r="B172" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C172" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D172" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #171</v>
+        <v>Fetch structural JSON logic for health learning verification #171</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G172" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6437,19 +6437,19 @@
         <v>TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C173" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D173" t="str">
-        <v>Validate cascading relational data purge during account drop verification #172</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #172</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G173" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6472,19 +6472,19 @@
         <v>TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C174" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D174" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #173</v>
+        <v>Sync anonymous analytics to improve AI securely verification #173</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G174" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6507,19 +6507,19 @@
         <v>TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C175" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D175" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #174</v>
+        <v>Bundle and download all remote records into local ZIP verification #174</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G175" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6542,19 +6542,19 @@
         <v>TC175</v>
       </c>
       <c r="B176" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C176" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D176" t="str">
-        <v>Validate cascading relational data purge during account drop verification #175</v>
+        <v>Permanently drop relational database schemas entirely verification #175</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G176" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6577,19 +6577,19 @@
         <v>TC176</v>
       </c>
       <c r="B177" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C177" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D177" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #176</v>
+        <v>Record new entry for blood pressure/heart rate verification #176</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G177" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6612,19 +6612,19 @@
         <v>TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C178" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D178" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #177</v>
+        <v>Calculate massive dataset into visual trend chart verification #177</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G178" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6647,19 +6647,19 @@
         <v>TC178</v>
       </c>
       <c r="B179" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C179" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D179" t="str">
-        <v>Validate cascading relational data purge during account drop verification #178</v>
+        <v>Push active vital stream into Daily Protocol engine verification #178</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G179" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6682,19 +6682,19 @@
         <v>TC179</v>
       </c>
       <c r="B180" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C180" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D180" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #179</v>
+        <v>Fetch structural JSON logic for health learning verification #179</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G180" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6717,19 +6717,19 @@
         <v>TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C181" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D181" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #180</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #180</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G181" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6752,19 +6752,19 @@
         <v>TC181</v>
       </c>
       <c r="B182" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C182" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D182" t="str">
-        <v>Validate cascading relational data purge during account drop verification #181</v>
+        <v>Sync anonymous analytics to improve AI securely verification #181</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G182" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6787,19 +6787,19 @@
         <v>TC182</v>
       </c>
       <c r="B183" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C183" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D183" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #182</v>
+        <v>Bundle and download all remote records into local ZIP verification #182</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G183" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6822,19 +6822,19 @@
         <v>TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C184" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D184" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #183</v>
+        <v>Permanently drop relational database schemas entirely verification #183</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G184" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6857,19 +6857,19 @@
         <v>TC184</v>
       </c>
       <c r="B185" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C185" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D185" t="str">
-        <v>Validate cascading relational data purge during account drop verification #184</v>
+        <v>Record new entry for blood pressure/heart rate verification #184</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G185" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6892,19 +6892,19 @@
         <v>TC185</v>
       </c>
       <c r="B186" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C186" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D186" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #185</v>
+        <v>Calculate massive dataset into visual trend chart verification #185</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G186" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6927,19 +6927,19 @@
         <v>TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C187" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D187" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #186</v>
+        <v>Push active vital stream into Daily Protocol engine verification #186</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G187" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6962,19 +6962,19 @@
         <v>TC187</v>
       </c>
       <c r="B188" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C188" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D188" t="str">
-        <v>Validate cascading relational data purge during account drop verification #187</v>
+        <v>Fetch structural JSON logic for health learning verification #187</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G188" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -6997,19 +6997,19 @@
         <v>TC188</v>
       </c>
       <c r="B189" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C189" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D189" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #188</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #188</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G189" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7032,19 +7032,19 @@
         <v>TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C190" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D190" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #189</v>
+        <v>Sync anonymous analytics to improve AI securely verification #189</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G190" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7067,19 +7067,19 @@
         <v>TC190</v>
       </c>
       <c r="B191" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C191" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D191" t="str">
-        <v>Validate cascading relational data purge during account drop verification #190</v>
+        <v>Bundle and download all remote records into local ZIP verification #190</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G191" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7102,19 +7102,19 @@
         <v>TC191</v>
       </c>
       <c r="B192" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C192" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D192" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #191</v>
+        <v>Permanently drop relational database schemas entirely verification #191</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G192" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7137,19 +7137,19 @@
         <v>TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C193" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D193" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #192</v>
+        <v>Record new entry for blood pressure/heart rate verification #192</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G193" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7172,19 +7172,19 @@
         <v>TC193</v>
       </c>
       <c r="B194" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C194" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D194" t="str">
-        <v>Validate cascading relational data purge during account drop verification #193</v>
+        <v>Calculate massive dataset into visual trend chart verification #193</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G194" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7207,19 +7207,19 @@
         <v>TC194</v>
       </c>
       <c r="B195" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C195" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D195" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #194</v>
+        <v>Push active vital stream into Daily Protocol engine verification #194</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G195" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7242,19 +7242,19 @@
         <v>TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C196" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D196" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #195</v>
+        <v>Fetch structural JSON logic for health learning verification #195</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G196" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7277,19 +7277,19 @@
         <v>TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C197" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D197" t="str">
-        <v>Validate cascading relational data purge during account drop verification #196</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #196</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G197" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7312,19 +7312,19 @@
         <v>TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C198" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D198" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #197</v>
+        <v>Sync anonymous analytics to improve AI securely verification #197</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G198" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7347,19 +7347,19 @@
         <v>TC198</v>
       </c>
       <c r="B199" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C199" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D199" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #198</v>
+        <v>Bundle and download all remote records into local ZIP verification #198</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G199" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7382,19 +7382,19 @@
         <v>TC199</v>
       </c>
       <c r="B200" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C200" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D200" t="str">
-        <v>Validate cascading relational data purge during account drop verification #199</v>
+        <v>Permanently drop relational database schemas entirely verification #199</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G200" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7417,19 +7417,19 @@
         <v>TC200</v>
       </c>
       <c r="B201" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C201" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D201" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #200</v>
+        <v>Record new entry for blood pressure/heart rate verification #200</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G201" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7452,19 +7452,19 @@
         <v>TC201</v>
       </c>
       <c r="B202" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C202" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D202" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #201</v>
+        <v>Calculate massive dataset into visual trend chart verification #201</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G202" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7487,19 +7487,19 @@
         <v>TC202</v>
       </c>
       <c r="B203" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C203" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D203" t="str">
-        <v>Validate cascading relational data purge during account drop verification #202</v>
+        <v>Push active vital stream into Daily Protocol engine verification #202</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G203" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7522,19 +7522,19 @@
         <v>TC203</v>
       </c>
       <c r="B204" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C204" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D204" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #203</v>
+        <v>Fetch structural JSON logic for health learning verification #203</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G204" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7557,19 +7557,19 @@
         <v>TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C205" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D205" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #204</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #204</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G205" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7592,19 +7592,19 @@
         <v>TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C206" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D206" t="str">
-        <v>Validate cascading relational data purge during account drop verification #205</v>
+        <v>Sync anonymous analytics to improve AI securely verification #205</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G206" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7627,19 +7627,19 @@
         <v>TC206</v>
       </c>
       <c r="B207" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C207" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D207" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #206</v>
+        <v>Bundle and download all remote records into local ZIP verification #206</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G207" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7662,19 +7662,19 @@
         <v>TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C208" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D208" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #207</v>
+        <v>Permanently drop relational database schemas entirely verification #207</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G208" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7697,19 +7697,19 @@
         <v>TC208</v>
       </c>
       <c r="B209" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C209" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D209" t="str">
-        <v>Validate cascading relational data purge during account drop verification #208</v>
+        <v>Record new entry for blood pressure/heart rate verification #208</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G209" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7732,19 +7732,19 @@
         <v>TC209</v>
       </c>
       <c r="B210" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C210" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D210" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #209</v>
+        <v>Calculate massive dataset into visual trend chart verification #209</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G210" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7767,19 +7767,19 @@
         <v>TC210</v>
       </c>
       <c r="B211" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C211" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D211" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #210</v>
+        <v>Push active vital stream into Daily Protocol engine verification #210</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G211" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7802,19 +7802,19 @@
         <v>TC211</v>
       </c>
       <c r="B212" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C212" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D212" t="str">
-        <v>Validate cascading relational data purge during account drop verification #211</v>
+        <v>Fetch structural JSON logic for health learning verification #211</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G212" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7837,19 +7837,19 @@
         <v>TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C213" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D213" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #212</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #212</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G213" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7872,19 +7872,19 @@
         <v>TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C214" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D214" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #213</v>
+        <v>Sync anonymous analytics to improve AI securely verification #213</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G214" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7907,19 +7907,19 @@
         <v>TC214</v>
       </c>
       <c r="B215" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C215" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D215" t="str">
-        <v>Validate cascading relational data purge during account drop verification #214</v>
+        <v>Bundle and download all remote records into local ZIP verification #214</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G215" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7942,19 +7942,19 @@
         <v>TC215</v>
       </c>
       <c r="B216" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C216" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D216" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #215</v>
+        <v>Permanently drop relational database schemas entirely verification #215</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G216" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -7977,19 +7977,19 @@
         <v>TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C217" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D217" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #216</v>
+        <v>Record new entry for blood pressure/heart rate verification #216</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G217" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8012,19 +8012,19 @@
         <v>TC217</v>
       </c>
       <c r="B218" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C218" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D218" t="str">
-        <v>Validate cascading relational data purge during account drop verification #217</v>
+        <v>Calculate massive dataset into visual trend chart verification #217</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G218" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8047,19 +8047,19 @@
         <v>TC218</v>
       </c>
       <c r="B219" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C219" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D219" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #218</v>
+        <v>Push active vital stream into Daily Protocol engine verification #218</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G219" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8082,19 +8082,19 @@
         <v>TC219</v>
       </c>
       <c r="B220" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C220" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D220" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #219</v>
+        <v>Fetch structural JSON logic for health learning verification #219</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G220" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8117,19 +8117,19 @@
         <v>TC220</v>
       </c>
       <c r="B221" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C221" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D221" t="str">
-        <v>Validate cascading relational data purge during account drop verification #220</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #220</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G221" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8152,19 +8152,19 @@
         <v>TC221</v>
       </c>
       <c r="B222" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C222" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D222" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #221</v>
+        <v>Sync anonymous analytics to improve AI securely verification #221</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G222" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8187,19 +8187,19 @@
         <v>TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C223" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D223" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #222</v>
+        <v>Bundle and download all remote records into local ZIP verification #222</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G223" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8222,19 +8222,19 @@
         <v>TC223</v>
       </c>
       <c r="B224" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C224" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D224" t="str">
-        <v>Validate cascading relational data purge during account drop verification #223</v>
+        <v>Permanently drop relational database schemas entirely verification #223</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G224" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8257,19 +8257,19 @@
         <v>TC224</v>
       </c>
       <c r="B225" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C225" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D225" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #224</v>
+        <v>Record new entry for blood pressure/heart rate verification #224</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G225" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8292,19 +8292,19 @@
         <v>TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C226" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D226" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #225</v>
+        <v>Calculate massive dataset into visual trend chart verification #225</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G226" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8327,19 +8327,19 @@
         <v>TC226</v>
       </c>
       <c r="B227" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C227" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D227" t="str">
-        <v>Validate cascading relational data purge during account drop verification #226</v>
+        <v>Push active vital stream into Daily Protocol engine verification #226</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G227" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8362,19 +8362,19 @@
         <v>TC227</v>
       </c>
       <c r="B228" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C228" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D228" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #227</v>
+        <v>Fetch structural JSON logic for health learning verification #227</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G228" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8397,19 +8397,19 @@
         <v>TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C229" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D229" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #228</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #228</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G229" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8432,19 +8432,19 @@
         <v>TC229</v>
       </c>
       <c r="B230" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C230" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D230" t="str">
-        <v>Validate cascading relational data purge during account drop verification #229</v>
+        <v>Sync anonymous analytics to improve AI securely verification #229</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G230" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8467,19 +8467,19 @@
         <v>TC230</v>
       </c>
       <c r="B231" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C231" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D231" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #230</v>
+        <v>Bundle and download all remote records into local ZIP verification #230</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G231" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8502,19 +8502,19 @@
         <v>TC231</v>
       </c>
       <c r="B232" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C232" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D232" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #231</v>
+        <v>Permanently drop relational database schemas entirely verification #231</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G232" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8537,19 +8537,19 @@
         <v>TC232</v>
       </c>
       <c r="B233" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C233" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D233" t="str">
-        <v>Validate cascading relational data purge during account drop verification #232</v>
+        <v>Record new entry for blood pressure/heart rate verification #232</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G233" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8572,19 +8572,19 @@
         <v>TC233</v>
       </c>
       <c r="B234" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C234" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D234" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #233</v>
+        <v>Calculate massive dataset into visual trend chart verification #233</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G234" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8607,19 +8607,19 @@
         <v>TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C235" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D235" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #234</v>
+        <v>Push active vital stream into Daily Protocol engine verification #234</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G235" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8642,19 +8642,19 @@
         <v>TC235</v>
       </c>
       <c r="B236" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C236" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D236" t="str">
-        <v>Validate cascading relational data purge during account drop verification #235</v>
+        <v>Fetch structural JSON logic for health learning verification #235</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G236" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8677,19 +8677,19 @@
         <v>TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C237" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D237" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #236</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #236</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G237" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8712,19 +8712,19 @@
         <v>TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C238" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D238" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #237</v>
+        <v>Sync anonymous analytics to improve AI securely verification #237</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G238" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8747,19 +8747,19 @@
         <v>TC238</v>
       </c>
       <c r="B239" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C239" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D239" t="str">
-        <v>Validate cascading relational data purge during account drop verification #238</v>
+        <v>Bundle and download all remote records into local ZIP verification #238</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G239" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8782,19 +8782,19 @@
         <v>TC239</v>
       </c>
       <c r="B240" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C240" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D240" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #239</v>
+        <v>Permanently drop relational database schemas entirely verification #239</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G240" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8817,19 +8817,19 @@
         <v>TC240</v>
       </c>
       <c r="B241" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C241" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D241" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #240</v>
+        <v>Record new entry for blood pressure/heart rate verification #240</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G241" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8852,19 +8852,19 @@
         <v>TC241</v>
       </c>
       <c r="B242" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C242" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D242" t="str">
-        <v>Validate cascading relational data purge during account drop verification #241</v>
+        <v>Calculate massive dataset into visual trend chart verification #241</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G242" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8887,19 +8887,19 @@
         <v>TC242</v>
       </c>
       <c r="B243" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C243" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D243" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #242</v>
+        <v>Push active vital stream into Daily Protocol engine verification #242</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G243" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8922,19 +8922,19 @@
         <v>TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C244" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D244" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #243</v>
+        <v>Fetch structural JSON logic for health learning verification #243</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G244" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8957,19 +8957,19 @@
         <v>TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C245" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D245" t="str">
-        <v>Validate cascading relational data purge during account drop verification #244</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #244</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G245" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -8992,19 +8992,19 @@
         <v>TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C246" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D246" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #245</v>
+        <v>Sync anonymous analytics to improve AI securely verification #245</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G246" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9027,19 +9027,19 @@
         <v>TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C247" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D247" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #246</v>
+        <v>Bundle and download all remote records into local ZIP verification #246</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G247" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9062,19 +9062,19 @@
         <v>TC247</v>
       </c>
       <c r="B248" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C248" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D248" t="str">
-        <v>Validate cascading relational data purge during account drop verification #247</v>
+        <v>Permanently drop relational database schemas entirely verification #247</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G248" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9097,19 +9097,19 @@
         <v>TC248</v>
       </c>
       <c r="B249" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C249" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D249" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #248</v>
+        <v>Record new entry for blood pressure/heart rate verification #248</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G249" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9132,19 +9132,19 @@
         <v>TC249</v>
       </c>
       <c r="B250" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C250" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D250" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #249</v>
+        <v>Calculate massive dataset into visual trend chart verification #249</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G250" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9167,19 +9167,19 @@
         <v>TC250</v>
       </c>
       <c r="B251" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C251" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D251" t="str">
-        <v>Validate cascading relational data purge during account drop verification #250</v>
+        <v>Push active vital stream into Daily Protocol engine verification #250</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G251" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9202,19 +9202,19 @@
         <v>TC251</v>
       </c>
       <c r="B252" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C252" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D252" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #251</v>
+        <v>Fetch structural JSON logic for health learning verification #251</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G252" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9237,19 +9237,19 @@
         <v>TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C253" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D253" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #252</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #252</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G253" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9272,19 +9272,19 @@
         <v>TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C254" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D254" t="str">
-        <v>Validate cascading relational data purge during account drop verification #253</v>
+        <v>Sync anonymous analytics to improve AI securely verification #253</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G254" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9307,19 +9307,19 @@
         <v>TC254</v>
       </c>
       <c r="B255" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C255" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D255" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #254</v>
+        <v>Bundle and download all remote records into local ZIP verification #254</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G255" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9342,19 +9342,19 @@
         <v>TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C256" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D256" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #255</v>
+        <v>Permanently drop relational database schemas entirely verification #255</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G256" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9377,19 +9377,19 @@
         <v>TC256</v>
       </c>
       <c r="B257" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C257" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D257" t="str">
-        <v>Validate cascading relational data purge during account drop verification #256</v>
+        <v>Record new entry for blood pressure/heart rate verification #256</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G257" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9412,19 +9412,19 @@
         <v>TC257</v>
       </c>
       <c r="B258" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C258" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D258" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #257</v>
+        <v>Calculate massive dataset into visual trend chart verification #257</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G258" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9447,19 +9447,19 @@
         <v>TC258</v>
       </c>
       <c r="B259" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C259" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D259" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #258</v>
+        <v>Push active vital stream into Daily Protocol engine verification #258</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G259" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9482,19 +9482,19 @@
         <v>TC259</v>
       </c>
       <c r="B260" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C260" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D260" t="str">
-        <v>Validate cascading relational data purge during account drop verification #259</v>
+        <v>Fetch structural JSON logic for health learning verification #259</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G260" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9517,19 +9517,19 @@
         <v>TC260</v>
       </c>
       <c r="B261" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C261" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D261" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #260</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #260</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G261" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9552,19 +9552,19 @@
         <v>TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C262" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D262" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #261</v>
+        <v>Sync anonymous analytics to improve AI securely verification #261</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G262" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9587,19 +9587,19 @@
         <v>TC262</v>
       </c>
       <c r="B263" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C263" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D263" t="str">
-        <v>Validate cascading relational data purge during account drop verification #262</v>
+        <v>Bundle and download all remote records into local ZIP verification #262</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G263" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9622,19 +9622,19 @@
         <v>TC263</v>
       </c>
       <c r="B264" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C264" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D264" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #263</v>
+        <v>Permanently drop relational database schemas entirely verification #263</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G264" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9657,19 +9657,19 @@
         <v>TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C265" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D265" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #264</v>
+        <v>Record new entry for blood pressure/heart rate verification #264</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G265" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9692,19 +9692,19 @@
         <v>TC265</v>
       </c>
       <c r="B266" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C266" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D266" t="str">
-        <v>Validate cascading relational data purge during account drop verification #265</v>
+        <v>Calculate massive dataset into visual trend chart verification #265</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G266" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9727,19 +9727,19 @@
         <v>TC266</v>
       </c>
       <c r="B267" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C267" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D267" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #266</v>
+        <v>Push active vital stream into Daily Protocol engine verification #266</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G267" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9762,19 +9762,19 @@
         <v>TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C268" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D268" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #267</v>
+        <v>Fetch structural JSON logic for health learning verification #267</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G268" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9797,19 +9797,19 @@
         <v>TC268</v>
       </c>
       <c r="B269" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C269" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D269" t="str">
-        <v>Validate cascading relational data purge during account drop verification #268</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #268</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G269" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9832,19 +9832,19 @@
         <v>TC269</v>
       </c>
       <c r="B270" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C270" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D270" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #269</v>
+        <v>Sync anonymous analytics to improve AI securely verification #269</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G270" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9867,19 +9867,19 @@
         <v>TC270</v>
       </c>
       <c r="B271" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C271" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D271" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #270</v>
+        <v>Bundle and download all remote records into local ZIP verification #270</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G271" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9902,19 +9902,19 @@
         <v>TC271</v>
       </c>
       <c r="B272" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C272" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D272" t="str">
-        <v>Validate cascading relational data purge during account drop verification #271</v>
+        <v>Permanently drop relational database schemas entirely verification #271</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G272" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9937,19 +9937,19 @@
         <v>TC272</v>
       </c>
       <c r="B273" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C273" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D273" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #272</v>
+        <v>Record new entry for blood pressure/heart rate verification #272</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G273" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -9972,19 +9972,19 @@
         <v>TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C274" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D274" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #273</v>
+        <v>Calculate massive dataset into visual trend chart verification #273</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G274" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10007,19 +10007,19 @@
         <v>TC274</v>
       </c>
       <c r="B275" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C275" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D275" t="str">
-        <v>Validate cascading relational data purge during account drop verification #274</v>
+        <v>Push active vital stream into Daily Protocol engine verification #274</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G275" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10042,19 +10042,19 @@
         <v>TC275</v>
       </c>
       <c r="B276" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C276" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D276" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #275</v>
+        <v>Fetch structural JSON logic for health learning verification #275</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G276" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10077,19 +10077,19 @@
         <v>TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C277" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D277" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #276</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #276</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G277" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10112,19 +10112,19 @@
         <v>TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C278" t="str">
-        <v>Account Deletion</v>
+        <v>Analytics</v>
       </c>
       <c r="D278" t="str">
-        <v>Validate cascading relational data purge during account drop verification #277</v>
+        <v>Sync anonymous analytics to improve AI securely verification #277</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G278" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10147,19 +10147,19 @@
         <v>TC278</v>
       </c>
       <c r="B279" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C279" t="str">
-        <v>Completions API</v>
+        <v>Data Report</v>
       </c>
       <c r="D279" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #278</v>
+        <v>Bundle and download all remote records into local ZIP verification #278</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G279" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10182,19 +10182,19 @@
         <v>TC279</v>
       </c>
       <c r="B280" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C280" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Delete Account</v>
       </c>
       <c r="D280" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #279</v>
+        <v>Permanently drop relational database schemas entirely verification #279</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G280" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10217,19 +10217,19 @@
         <v>TC280</v>
       </c>
       <c r="B281" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C281" t="str">
-        <v>Account Deletion</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D281" t="str">
-        <v>Validate cascading relational data purge during account drop verification #280</v>
+        <v>Record new entry for blood pressure/heart rate verification #280</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G281" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10252,19 +10252,19 @@
         <v>TC281</v>
       </c>
       <c r="B282" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C282" t="str">
-        <v>Completions API</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D282" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #281</v>
+        <v>Calculate massive dataset into visual trend chart verification #281</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G282" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10287,19 +10287,19 @@
         <v>TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C283" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D283" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #282</v>
+        <v>Push active vital stream into Daily Protocol engine verification #282</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G283" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10322,19 +10322,19 @@
         <v>TC283</v>
       </c>
       <c r="B284" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C284" t="str">
-        <v>Account Deletion</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D284" t="str">
-        <v>Validate cascading relational data purge during account drop verification #283</v>
+        <v>Fetch structural JSON logic for health learning verification #283</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G284" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10357,19 +10357,19 @@
         <v>TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C285" t="str">
-        <v>Completions API</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D285" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #284</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #284</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G285" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10392,19 +10392,19 @@
         <v>TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C286" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Analytics</v>
       </c>
       <c r="D286" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #285</v>
+        <v>Sync anonymous analytics to improve AI securely verification #285</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G286" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10427,19 +10427,19 @@
         <v>TC286</v>
       </c>
       <c r="B287" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C287" t="str">
-        <v>Account Deletion</v>
+        <v>Data Report</v>
       </c>
       <c r="D287" t="str">
-        <v>Validate cascading relational data purge during account drop verification #286</v>
+        <v>Bundle and download all remote records into local ZIP verification #286</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G287" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10462,19 +10462,19 @@
         <v>TC287</v>
       </c>
       <c r="B288" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C288" t="str">
-        <v>Completions API</v>
+        <v>Delete Account</v>
       </c>
       <c r="D288" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #287</v>
+        <v>Permanently drop relational database schemas entirely verification #287</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G288" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10497,19 +10497,19 @@
         <v>TC288</v>
       </c>
       <c r="B289" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C289" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D289" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #288</v>
+        <v>Record new entry for blood pressure/heart rate verification #288</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G289" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10532,19 +10532,19 @@
         <v>TC289</v>
       </c>
       <c r="B290" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C290" t="str">
-        <v>Account Deletion</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D290" t="str">
-        <v>Validate cascading relational data purge during account drop verification #289</v>
+        <v>Calculate massive dataset into visual trend chart verification #289</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G290" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10567,19 +10567,19 @@
         <v>TC290</v>
       </c>
       <c r="B291" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C291" t="str">
-        <v>Completions API</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D291" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #290</v>
+        <v>Push active vital stream into Daily Protocol engine verification #290</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G291" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10602,19 +10602,19 @@
         <v>TC291</v>
       </c>
       <c r="B292" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C292" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D292" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #291</v>
+        <v>Fetch structural JSON logic for health learning verification #291</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G292" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10637,19 +10637,19 @@
         <v>TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>Supabase DB</v>
+        <v>Learn Module</v>
       </c>
       <c r="C293" t="str">
-        <v>Account Deletion</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D293" t="str">
-        <v>Validate cascading relational data purge during account drop verification #292</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #292</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G293" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10672,19 +10672,19 @@
         <v>TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>OpenRouter</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C294" t="str">
-        <v>Completions API</v>
+        <v>Analytics</v>
       </c>
       <c r="D294" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #293</v>
+        <v>Sync anonymous analytics to improve AI securely verification #293</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Privacy Centre and perform Analytics action</v>
       </c>
       <c r="G294" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10707,19 +10707,19 @@
         <v>TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>Auth API</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C295" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Data Report</v>
       </c>
       <c r="D295" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #294</v>
+        <v>Bundle and download all remote records into local ZIP verification #294</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Privacy Centre and perform Data Report action</v>
       </c>
       <c r="G295" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10742,19 +10742,19 @@
         <v>TC295</v>
       </c>
       <c r="B296" t="str">
-        <v>Supabase DB</v>
+        <v>Privacy Centre</v>
       </c>
       <c r="C296" t="str">
-        <v>Account Deletion</v>
+        <v>Delete Account</v>
       </c>
       <c r="D296" t="str">
-        <v>Validate cascading relational data purge during account drop verification #295</v>
+        <v>Permanently drop relational database schemas entirely verification #295</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Privacy Centre and perform Delete Account action</v>
       </c>
       <c r="G296" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10777,19 +10777,19 @@
         <v>TC296</v>
       </c>
       <c r="B297" t="str">
-        <v>OpenRouter</v>
+        <v>Tracker</v>
       </c>
       <c r="C297" t="str">
-        <v>Completions API</v>
+        <v>Update Biometrics</v>
       </c>
       <c r="D297" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #296</v>
+        <v>Record new entry for blood pressure/heart rate verification #296</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Tracker and perform Update Biometrics action</v>
       </c>
       <c r="G297" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10812,19 +10812,19 @@
         <v>TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>Auth API</v>
+        <v>Tracker</v>
       </c>
       <c r="C298" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Statistical Trends</v>
       </c>
       <c r="D298" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #297</v>
+        <v>Calculate massive dataset into visual trend chart verification #297</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Tracker and perform Statistical Trends action</v>
       </c>
       <c r="G298" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10847,19 +10847,19 @@
         <v>TC298</v>
       </c>
       <c r="B299" t="str">
-        <v>Supabase DB</v>
+        <v>Tracker</v>
       </c>
       <c r="C299" t="str">
-        <v>Account Deletion</v>
+        <v>Active Vitals</v>
       </c>
       <c r="D299" t="str">
-        <v>Validate cascading relational data purge during account drop verification #298</v>
+        <v>Push active vital stream into Daily Protocol engine verification #298</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to Supabase DB and perform Account Deletion action</v>
+        <v>Navigate to Tracker and perform Active Vitals action</v>
       </c>
       <c r="G299" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10882,19 +10882,19 @@
         <v>TC299</v>
       </c>
       <c r="B300" t="str">
-        <v>OpenRouter</v>
+        <v>Learn Module</v>
       </c>
       <c r="C300" t="str">
-        <v>Completions API</v>
+        <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D300" t="str">
-        <v>Fetch AI response payloads securely via fetch() layer verification #299</v>
+        <v>Fetch structural JSON logic for health learning verification #299</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to OpenRouter and perform Completions API action</v>
+        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
       </c>
       <c r="G300" t="str">
         <v>Action completes successfully within standard latency bounds</v>
@@ -10917,19 +10917,19 @@
         <v>TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>Auth API</v>
+        <v>Learn Module</v>
       </c>
       <c r="C301" t="str">
-        <v>Forgot/Change Password</v>
+        <v>Pathology/Pharma</v>
       </c>
       <c r="D301" t="str">
-        <v>Verify encrypted token dispatch for credential overrides verification #300</v>
+        <v>Serve recommended study (vascular pressure dyn.) verification #300</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Auth API and perform Forgot/Change Password action</v>
+        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
       </c>
       <c r="G301" t="str">
         <v>Action completes successfully within standard latency bounds</v>

--- a/e2e_tests_suite/Report_03_API_Testing.xlsx
+++ b/e2e_tests_suite/Report_03_API_Testing.xlsx
@@ -458,16 +458,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D2" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #1</v>
+        <v>Calculate massive dataset into visual trend chart [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E2" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F2" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G2" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H2" t="str">
         <v>High</v>
@@ -493,16 +493,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D3" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #2</v>
+        <v>Push active vital stream into Daily Protocol engine [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E3" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F3" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G3" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H3" t="str">
         <v>High</v>
@@ -528,16 +528,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D4" t="str">
-        <v>Fetch structural JSON logic for health learning verification #3</v>
+        <v>Fetch structural JSON logic for health learning [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E4" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F4" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G4" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H4" t="str">
         <v>High</v>
@@ -563,16 +563,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D5" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #4</v>
+        <v>Serve recommended study (vascular pressure dyn.) [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E5" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F5" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G5" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H5" t="str">
         <v>High</v>
@@ -598,16 +598,16 @@
         <v>Analytics</v>
       </c>
       <c r="D6" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #5</v>
+        <v>Sync anonymous analytics to improve AI securely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E6" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F6" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G6" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H6" t="str">
         <v>Critical</v>
@@ -633,16 +633,16 @@
         <v>Data Report</v>
       </c>
       <c r="D7" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #6</v>
+        <v>Bundle and download all remote records into local ZIP [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E7" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F7" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G7" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H7" t="str">
         <v>High</v>
@@ -668,16 +668,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D8" t="str">
-        <v>Permanently drop relational database schemas entirely verification #7</v>
+        <v>Permanently drop relational database schemas entirely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E8" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F8" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating security guard (special char injection)</v>
       </c>
       <c r="G8" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H8" t="str">
         <v>High</v>
@@ -703,16 +703,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D9" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #8</v>
+        <v>Record new entry for blood pressure/heart rate [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E9" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F9" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G9" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H9" t="str">
         <v>High</v>
@@ -738,16 +738,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D10" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #9</v>
+        <v>Calculate massive dataset into visual trend chart [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E10" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F10" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G10" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H10" t="str">
         <v>High</v>
@@ -773,16 +773,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D11" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #10</v>
+        <v>Push active vital stream into Daily Protocol engine [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E11" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F11" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating normal path (standard execution)</v>
       </c>
       <c r="G11" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H11" t="str">
         <v>Critical</v>
@@ -808,16 +808,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D12" t="str">
-        <v>Fetch structural JSON logic for health learning verification #11</v>
+        <v>Fetch structural JSON logic for health learning [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E12" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F12" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G12" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H12" t="str">
         <v>High</v>
@@ -843,16 +843,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D13" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #12</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E13" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F13" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating security guard (special char injection)</v>
       </c>
       <c r="G13" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H13" t="str">
         <v>High</v>
@@ -878,16 +878,16 @@
         <v>Analytics</v>
       </c>
       <c r="D14" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #13</v>
+        <v>Sync anonymous analytics to improve AI securely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E14" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F14" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G14" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H14" t="str">
         <v>High</v>
@@ -913,16 +913,16 @@
         <v>Data Report</v>
       </c>
       <c r="D15" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #14</v>
+        <v>Bundle and download all remote records into local ZIP [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E15" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F15" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G15" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H15" t="str">
         <v>High</v>
@@ -948,16 +948,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D16" t="str">
-        <v>Permanently drop relational database schemas entirely verification #15</v>
+        <v>Permanently drop relational database schemas entirely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E16" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F16" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating normal path (standard execution)</v>
       </c>
       <c r="G16" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H16" t="str">
         <v>Critical</v>
@@ -983,16 +983,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D17" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #16</v>
+        <v>Record new entry for blood pressure/heart rate [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E17" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F17" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G17" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H17" t="str">
         <v>High</v>
@@ -1018,16 +1018,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D18" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #17</v>
+        <v>Calculate massive dataset into visual trend chart [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E18" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F18" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating security guard (special char injection)</v>
       </c>
       <c r="G18" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H18" t="str">
         <v>High</v>
@@ -1053,16 +1053,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D19" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #18</v>
+        <v>Push active vital stream into Daily Protocol engine [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E19" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F19" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G19" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H19" t="str">
         <v>High</v>
@@ -1088,16 +1088,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D20" t="str">
-        <v>Fetch structural JSON logic for health learning verification #19</v>
+        <v>Fetch structural JSON logic for health learning [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E20" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F20" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G20" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H20" t="str">
         <v>High</v>
@@ -1123,16 +1123,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D21" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #20</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E21" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F21" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating normal path (standard execution)</v>
       </c>
       <c r="G21" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H21" t="str">
         <v>Critical</v>
@@ -1158,16 +1158,16 @@
         <v>Analytics</v>
       </c>
       <c r="D22" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #21</v>
+        <v>Sync anonymous analytics to improve AI securely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E22" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F22" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G22" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H22" t="str">
         <v>High</v>
@@ -1193,16 +1193,16 @@
         <v>Data Report</v>
       </c>
       <c r="D23" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #22</v>
+        <v>Bundle and download all remote records into local ZIP [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E23" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F23" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating security guard (special char injection)</v>
       </c>
       <c r="G23" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H23" t="str">
         <v>High</v>
@@ -1228,16 +1228,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D24" t="str">
-        <v>Permanently drop relational database schemas entirely verification #23</v>
+        <v>Permanently drop relational database schemas entirely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E24" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F24" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G24" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H24" t="str">
         <v>High</v>
@@ -1263,16 +1263,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D25" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #24</v>
+        <v>Record new entry for blood pressure/heart rate [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E25" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F25" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G25" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H25" t="str">
         <v>High</v>
@@ -1298,16 +1298,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D26" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #25</v>
+        <v>Calculate massive dataset into visual trend chart [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E26" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F26" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating normal path (standard execution)</v>
       </c>
       <c r="G26" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H26" t="str">
         <v>Critical</v>
@@ -1333,16 +1333,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D27" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #26</v>
+        <v>Push active vital stream into Daily Protocol engine [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E27" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F27" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G27" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H27" t="str">
         <v>High</v>
@@ -1368,16 +1368,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D28" t="str">
-        <v>Fetch structural JSON logic for health learning verification #27</v>
+        <v>Fetch structural JSON logic for health learning [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E28" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F28" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating security guard (special char injection)</v>
       </c>
       <c r="G28" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H28" t="str">
         <v>High</v>
@@ -1403,16 +1403,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D29" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #28</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E29" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F29" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G29" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H29" t="str">
         <v>High</v>
@@ -1438,16 +1438,16 @@
         <v>Analytics</v>
       </c>
       <c r="D30" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #29</v>
+        <v>Sync anonymous analytics to improve AI securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E30" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F30" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G30" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H30" t="str">
         <v>High</v>
@@ -1473,16 +1473,16 @@
         <v>Data Report</v>
       </c>
       <c r="D31" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #30</v>
+        <v>Bundle and download all remote records into local ZIP [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E31" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F31" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating normal path (standard execution)</v>
       </c>
       <c r="G31" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H31" t="str">
         <v>Critical</v>
@@ -1508,16 +1508,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D32" t="str">
-        <v>Permanently drop relational database schemas entirely verification #31</v>
+        <v>Permanently drop relational database schemas entirely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E32" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F32" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G32" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H32" t="str">
         <v>High</v>
@@ -1543,16 +1543,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D33" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #32</v>
+        <v>Record new entry for blood pressure/heart rate [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E33" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F33" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G33" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H33" t="str">
         <v>High</v>
@@ -1578,16 +1578,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D34" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #33</v>
+        <v>Calculate massive dataset into visual trend chart [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E34" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F34" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G34" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H34" t="str">
         <v>High</v>
@@ -1613,16 +1613,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D35" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #34</v>
+        <v>Push active vital stream into Daily Protocol engine [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E35" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F35" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G35" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H35" t="str">
         <v>High</v>
@@ -1648,16 +1648,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D36" t="str">
-        <v>Fetch structural JSON logic for health learning verification #35</v>
+        <v>Fetch structural JSON logic for health learning [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E36" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F36" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating normal path (standard execution)</v>
       </c>
       <c r="G36" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H36" t="str">
         <v>Critical</v>
@@ -1683,16 +1683,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D37" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #36</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E37" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F37" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G37" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H37" t="str">
         <v>High</v>
@@ -1718,16 +1718,16 @@
         <v>Analytics</v>
       </c>
       <c r="D38" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #37</v>
+        <v>Sync anonymous analytics to improve AI securely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E38" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F38" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G38" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H38" t="str">
         <v>High</v>
@@ -1753,16 +1753,16 @@
         <v>Data Report</v>
       </c>
       <c r="D39" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #38</v>
+        <v>Bundle and download all remote records into local ZIP [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E39" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F39" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G39" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H39" t="str">
         <v>High</v>
@@ -1788,16 +1788,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D40" t="str">
-        <v>Permanently drop relational database schemas entirely verification #39</v>
+        <v>Permanently drop relational database schemas entirely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E40" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F40" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G40" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H40" t="str">
         <v>High</v>
@@ -1823,16 +1823,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D41" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #40</v>
+        <v>Record new entry for blood pressure/heart rate [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E41" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F41" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G41" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H41" t="str">
         <v>Critical</v>
@@ -1858,16 +1858,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D42" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #41</v>
+        <v>Calculate massive dataset into visual trend chart [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E42" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F42" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G42" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H42" t="str">
         <v>High</v>
@@ -1893,16 +1893,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D43" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #42</v>
+        <v>Push active vital stream into Daily Protocol engine [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E43" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F43" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G43" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H43" t="str">
         <v>High</v>
@@ -1928,16 +1928,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D44" t="str">
-        <v>Fetch structural JSON logic for health learning verification #43</v>
+        <v>Fetch structural JSON logic for health learning [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E44" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F44" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G44" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H44" t="str">
         <v>High</v>
@@ -1963,16 +1963,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D45" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #44</v>
+        <v>Serve recommended study (vascular pressure dyn.) [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E45" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F45" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G45" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H45" t="str">
         <v>High</v>
@@ -1998,16 +1998,16 @@
         <v>Analytics</v>
       </c>
       <c r="D46" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #45</v>
+        <v>Sync anonymous analytics to improve AI securely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E46" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F46" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G46" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H46" t="str">
         <v>Critical</v>
@@ -2033,16 +2033,16 @@
         <v>Data Report</v>
       </c>
       <c r="D47" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #46</v>
+        <v>Bundle and download all remote records into local ZIP [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E47" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F47" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G47" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H47" t="str">
         <v>High</v>
@@ -2068,16 +2068,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D48" t="str">
-        <v>Permanently drop relational database schemas entirely verification #47</v>
+        <v>Permanently drop relational database schemas entirely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E48" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F48" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating security guard (special char injection)</v>
       </c>
       <c r="G48" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H48" t="str">
         <v>High</v>
@@ -2103,16 +2103,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D49" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #48</v>
+        <v>Record new entry for blood pressure/heart rate [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E49" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F49" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G49" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H49" t="str">
         <v>High</v>
@@ -2138,16 +2138,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D50" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #49</v>
+        <v>Calculate massive dataset into visual trend chart [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E50" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F50" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G50" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H50" t="str">
         <v>High</v>
@@ -2173,16 +2173,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D51" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #50</v>
+        <v>Push active vital stream into Daily Protocol engine [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E51" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F51" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating normal path (standard execution)</v>
       </c>
       <c r="G51" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H51" t="str">
         <v>Critical</v>
@@ -2208,16 +2208,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D52" t="str">
-        <v>Fetch structural JSON logic for health learning verification #51</v>
+        <v>Fetch structural JSON logic for health learning [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E52" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F52" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G52" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H52" t="str">
         <v>High</v>
@@ -2243,16 +2243,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D53" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #52</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E53" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F53" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating security guard (special char injection)</v>
       </c>
       <c r="G53" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H53" t="str">
         <v>High</v>
@@ -2278,16 +2278,16 @@
         <v>Analytics</v>
       </c>
       <c r="D54" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #53</v>
+        <v>Sync anonymous analytics to improve AI securely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E54" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F54" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G54" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H54" t="str">
         <v>High</v>
@@ -2313,16 +2313,16 @@
         <v>Data Report</v>
       </c>
       <c r="D55" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #54</v>
+        <v>Bundle and download all remote records into local ZIP [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E55" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F55" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G55" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H55" t="str">
         <v>High</v>
@@ -2348,16 +2348,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D56" t="str">
-        <v>Permanently drop relational database schemas entirely verification #55</v>
+        <v>Permanently drop relational database schemas entirely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E56" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F56" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating normal path (standard execution)</v>
       </c>
       <c r="G56" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H56" t="str">
         <v>Critical</v>
@@ -2383,16 +2383,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D57" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #56</v>
+        <v>Record new entry for blood pressure/heart rate [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E57" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F57" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G57" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H57" t="str">
         <v>High</v>
@@ -2418,16 +2418,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D58" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #57</v>
+        <v>Calculate massive dataset into visual trend chart [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E58" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F58" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating security guard (special char injection)</v>
       </c>
       <c r="G58" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H58" t="str">
         <v>High</v>
@@ -2453,16 +2453,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D59" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #58</v>
+        <v>Push active vital stream into Daily Protocol engine [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E59" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F59" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G59" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H59" t="str">
         <v>High</v>
@@ -2488,16 +2488,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D60" t="str">
-        <v>Fetch structural JSON logic for health learning verification #59</v>
+        <v>Fetch structural JSON logic for health learning [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E60" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F60" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G60" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H60" t="str">
         <v>High</v>
@@ -2523,16 +2523,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D61" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #60</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E61" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F61" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating normal path (standard execution)</v>
       </c>
       <c r="G61" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H61" t="str">
         <v>Critical</v>
@@ -2558,16 +2558,16 @@
         <v>Analytics</v>
       </c>
       <c r="D62" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #61</v>
+        <v>Sync anonymous analytics to improve AI securely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E62" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F62" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G62" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H62" t="str">
         <v>High</v>
@@ -2593,16 +2593,16 @@
         <v>Data Report</v>
       </c>
       <c r="D63" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #62</v>
+        <v>Bundle and download all remote records into local ZIP [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E63" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F63" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating security guard (special char injection)</v>
       </c>
       <c r="G63" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H63" t="str">
         <v>High</v>
@@ -2628,16 +2628,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D64" t="str">
-        <v>Permanently drop relational database schemas entirely verification #63</v>
+        <v>Permanently drop relational database schemas entirely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E64" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F64" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G64" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H64" t="str">
         <v>High</v>
@@ -2663,16 +2663,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D65" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #64</v>
+        <v>Record new entry for blood pressure/heart rate [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E65" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F65" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G65" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H65" t="str">
         <v>High</v>
@@ -2698,16 +2698,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D66" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #65</v>
+        <v>Calculate massive dataset into visual trend chart [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E66" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F66" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating normal path (standard execution)</v>
       </c>
       <c r="G66" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H66" t="str">
         <v>Critical</v>
@@ -2733,16 +2733,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D67" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #66</v>
+        <v>Push active vital stream into Daily Protocol engine [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E67" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F67" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G67" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H67" t="str">
         <v>High</v>
@@ -2768,16 +2768,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D68" t="str">
-        <v>Fetch structural JSON logic for health learning verification #67</v>
+        <v>Fetch structural JSON logic for health learning [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E68" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F68" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating security guard (special char injection)</v>
       </c>
       <c r="G68" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H68" t="str">
         <v>High</v>
@@ -2803,16 +2803,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D69" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #68</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E69" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F69" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G69" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H69" t="str">
         <v>High</v>
@@ -2838,16 +2838,16 @@
         <v>Analytics</v>
       </c>
       <c r="D70" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #69</v>
+        <v>Sync anonymous analytics to improve AI securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E70" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F70" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G70" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H70" t="str">
         <v>High</v>
@@ -2873,16 +2873,16 @@
         <v>Data Report</v>
       </c>
       <c r="D71" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #70</v>
+        <v>Bundle and download all remote records into local ZIP [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E71" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F71" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating normal path (standard execution)</v>
       </c>
       <c r="G71" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H71" t="str">
         <v>Critical</v>
@@ -2908,16 +2908,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D72" t="str">
-        <v>Permanently drop relational database schemas entirely verification #71</v>
+        <v>Permanently drop relational database schemas entirely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E72" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F72" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G72" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H72" t="str">
         <v>High</v>
@@ -2943,16 +2943,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D73" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #72</v>
+        <v>Record new entry for blood pressure/heart rate [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E73" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F73" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G73" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H73" t="str">
         <v>High</v>
@@ -2978,16 +2978,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D74" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #73</v>
+        <v>Calculate massive dataset into visual trend chart [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E74" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F74" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G74" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H74" t="str">
         <v>High</v>
@@ -3013,16 +3013,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D75" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #74</v>
+        <v>Push active vital stream into Daily Protocol engine [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E75" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F75" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G75" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H75" t="str">
         <v>High</v>
@@ -3048,16 +3048,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D76" t="str">
-        <v>Fetch structural JSON logic for health learning verification #75</v>
+        <v>Fetch structural JSON logic for health learning [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E76" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F76" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating normal path (standard execution)</v>
       </c>
       <c r="G76" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H76" t="str">
         <v>Critical</v>
@@ -3083,16 +3083,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D77" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #76</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E77" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F77" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G77" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H77" t="str">
         <v>High</v>
@@ -3118,16 +3118,16 @@
         <v>Analytics</v>
       </c>
       <c r="D78" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #77</v>
+        <v>Sync anonymous analytics to improve AI securely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E78" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F78" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G78" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H78" t="str">
         <v>High</v>
@@ -3153,16 +3153,16 @@
         <v>Data Report</v>
       </c>
       <c r="D79" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #78</v>
+        <v>Bundle and download all remote records into local ZIP [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E79" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F79" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G79" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H79" t="str">
         <v>High</v>
@@ -3188,16 +3188,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D80" t="str">
-        <v>Permanently drop relational database schemas entirely verification #79</v>
+        <v>Permanently drop relational database schemas entirely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E80" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F80" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G80" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H80" t="str">
         <v>High</v>
@@ -3223,16 +3223,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D81" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #80</v>
+        <v>Record new entry for blood pressure/heart rate [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E81" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F81" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G81" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H81" t="str">
         <v>Critical</v>
@@ -3258,16 +3258,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D82" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #81</v>
+        <v>Calculate massive dataset into visual trend chart [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E82" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F82" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G82" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H82" t="str">
         <v>High</v>
@@ -3293,16 +3293,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D83" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #82</v>
+        <v>Push active vital stream into Daily Protocol engine [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E83" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F83" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G83" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H83" t="str">
         <v>High</v>
@@ -3328,16 +3328,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D84" t="str">
-        <v>Fetch structural JSON logic for health learning verification #83</v>
+        <v>Fetch structural JSON logic for health learning [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E84" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F84" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G84" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H84" t="str">
         <v>High</v>
@@ -3363,16 +3363,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D85" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #84</v>
+        <v>Serve recommended study (vascular pressure dyn.) [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E85" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F85" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G85" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H85" t="str">
         <v>High</v>
@@ -3398,16 +3398,16 @@
         <v>Analytics</v>
       </c>
       <c r="D86" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #85</v>
+        <v>Sync anonymous analytics to improve AI securely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E86" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F86" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G86" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H86" t="str">
         <v>Critical</v>
@@ -3433,16 +3433,16 @@
         <v>Data Report</v>
       </c>
       <c r="D87" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #86</v>
+        <v>Bundle and download all remote records into local ZIP [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E87" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F87" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G87" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H87" t="str">
         <v>High</v>
@@ -3468,16 +3468,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D88" t="str">
-        <v>Permanently drop relational database schemas entirely verification #87</v>
+        <v>Permanently drop relational database schemas entirely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E88" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F88" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating security guard (special char injection)</v>
       </c>
       <c r="G88" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H88" t="str">
         <v>High</v>
@@ -3503,16 +3503,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D89" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #88</v>
+        <v>Record new entry for blood pressure/heart rate [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E89" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F89" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G89" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H89" t="str">
         <v>High</v>
@@ -3538,16 +3538,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D90" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #89</v>
+        <v>Calculate massive dataset into visual trend chart [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E90" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F90" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G90" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H90" t="str">
         <v>High</v>
@@ -3573,16 +3573,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D91" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #90</v>
+        <v>Push active vital stream into Daily Protocol engine [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E91" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F91" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating normal path (standard execution)</v>
       </c>
       <c r="G91" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H91" t="str">
         <v>Critical</v>
@@ -3608,16 +3608,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D92" t="str">
-        <v>Fetch structural JSON logic for health learning verification #91</v>
+        <v>Fetch structural JSON logic for health learning [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E92" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F92" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G92" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H92" t="str">
         <v>High</v>
@@ -3643,16 +3643,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D93" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #92</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E93" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F93" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating security guard (special char injection)</v>
       </c>
       <c r="G93" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H93" t="str">
         <v>High</v>
@@ -3678,16 +3678,16 @@
         <v>Analytics</v>
       </c>
       <c r="D94" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #93</v>
+        <v>Sync anonymous analytics to improve AI securely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E94" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F94" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G94" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H94" t="str">
         <v>High</v>
@@ -3713,16 +3713,16 @@
         <v>Data Report</v>
       </c>
       <c r="D95" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #94</v>
+        <v>Bundle and download all remote records into local ZIP [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E95" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F95" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G95" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H95" t="str">
         <v>High</v>
@@ -3748,16 +3748,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D96" t="str">
-        <v>Permanently drop relational database schemas entirely verification #95</v>
+        <v>Permanently drop relational database schemas entirely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E96" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F96" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating normal path (standard execution)</v>
       </c>
       <c r="G96" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H96" t="str">
         <v>Critical</v>
@@ -3783,16 +3783,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D97" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #96</v>
+        <v>Record new entry for blood pressure/heart rate [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E97" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F97" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G97" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H97" t="str">
         <v>High</v>
@@ -3818,16 +3818,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D98" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #97</v>
+        <v>Calculate massive dataset into visual trend chart [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E98" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F98" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating security guard (special char injection)</v>
       </c>
       <c r="G98" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H98" t="str">
         <v>High</v>
@@ -3853,16 +3853,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D99" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #98</v>
+        <v>Push active vital stream into Daily Protocol engine [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E99" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F99" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G99" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H99" t="str">
         <v>High</v>
@@ -3888,16 +3888,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D100" t="str">
-        <v>Fetch structural JSON logic for health learning verification #99</v>
+        <v>Fetch structural JSON logic for health learning [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E100" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F100" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G100" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H100" t="str">
         <v>High</v>
@@ -3923,16 +3923,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D101" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #100</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E101" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F101" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating normal path (standard execution)</v>
       </c>
       <c r="G101" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H101" t="str">
         <v>Critical</v>
@@ -3958,16 +3958,16 @@
         <v>Analytics</v>
       </c>
       <c r="D102" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #101</v>
+        <v>Sync anonymous analytics to improve AI securely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E102" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F102" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G102" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H102" t="str">
         <v>High</v>
@@ -3993,16 +3993,16 @@
         <v>Data Report</v>
       </c>
       <c r="D103" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #102</v>
+        <v>Bundle and download all remote records into local ZIP [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E103" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F103" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating security guard (special char injection)</v>
       </c>
       <c r="G103" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H103" t="str">
         <v>High</v>
@@ -4028,16 +4028,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D104" t="str">
-        <v>Permanently drop relational database schemas entirely verification #103</v>
+        <v>Permanently drop relational database schemas entirely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E104" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F104" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G104" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H104" t="str">
         <v>High</v>
@@ -4063,16 +4063,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D105" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #104</v>
+        <v>Record new entry for blood pressure/heart rate [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E105" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F105" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G105" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H105" t="str">
         <v>High</v>
@@ -4098,16 +4098,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D106" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #105</v>
+        <v>Calculate massive dataset into visual trend chart [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E106" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F106" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating normal path (standard execution)</v>
       </c>
       <c r="G106" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H106" t="str">
         <v>Critical</v>
@@ -4133,16 +4133,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D107" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #106</v>
+        <v>Push active vital stream into Daily Protocol engine [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E107" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F107" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G107" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H107" t="str">
         <v>High</v>
@@ -4168,16 +4168,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D108" t="str">
-        <v>Fetch structural JSON logic for health learning verification #107</v>
+        <v>Fetch structural JSON logic for health learning [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E108" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F108" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating security guard (special char injection)</v>
       </c>
       <c r="G108" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H108" t="str">
         <v>High</v>
@@ -4203,16 +4203,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D109" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #108</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E109" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F109" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G109" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H109" t="str">
         <v>High</v>
@@ -4238,16 +4238,16 @@
         <v>Analytics</v>
       </c>
       <c r="D110" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #109</v>
+        <v>Sync anonymous analytics to improve AI securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E110" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F110" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G110" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H110" t="str">
         <v>High</v>
@@ -4273,16 +4273,16 @@
         <v>Data Report</v>
       </c>
       <c r="D111" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #110</v>
+        <v>Bundle and download all remote records into local ZIP [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E111" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F111" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating normal path (standard execution)</v>
       </c>
       <c r="G111" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H111" t="str">
         <v>Critical</v>
@@ -4308,16 +4308,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D112" t="str">
-        <v>Permanently drop relational database schemas entirely verification #111</v>
+        <v>Permanently drop relational database schemas entirely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E112" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F112" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G112" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H112" t="str">
         <v>High</v>
@@ -4343,16 +4343,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D113" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #112</v>
+        <v>Record new entry for blood pressure/heart rate [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E113" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F113" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G113" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H113" t="str">
         <v>High</v>
@@ -4378,16 +4378,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D114" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #113</v>
+        <v>Calculate massive dataset into visual trend chart [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E114" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F114" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G114" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H114" t="str">
         <v>High</v>
@@ -4413,16 +4413,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D115" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #114</v>
+        <v>Push active vital stream into Daily Protocol engine [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E115" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F115" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G115" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H115" t="str">
         <v>High</v>
@@ -4448,16 +4448,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D116" t="str">
-        <v>Fetch structural JSON logic for health learning verification #115</v>
+        <v>Fetch structural JSON logic for health learning [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E116" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F116" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating normal path (standard execution)</v>
       </c>
       <c r="G116" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H116" t="str">
         <v>Critical</v>
@@ -4483,16 +4483,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D117" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #116</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E117" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F117" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G117" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H117" t="str">
         <v>High</v>
@@ -4518,16 +4518,16 @@
         <v>Analytics</v>
       </c>
       <c r="D118" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #117</v>
+        <v>Sync anonymous analytics to improve AI securely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E118" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F118" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G118" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H118" t="str">
         <v>High</v>
@@ -4553,16 +4553,16 @@
         <v>Data Report</v>
       </c>
       <c r="D119" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #118</v>
+        <v>Bundle and download all remote records into local ZIP [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E119" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F119" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G119" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H119" t="str">
         <v>High</v>
@@ -4588,16 +4588,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D120" t="str">
-        <v>Permanently drop relational database schemas entirely verification #119</v>
+        <v>Permanently drop relational database schemas entirely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E120" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F120" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G120" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H120" t="str">
         <v>High</v>
@@ -4623,16 +4623,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D121" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #120</v>
+        <v>Record new entry for blood pressure/heart rate [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E121" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F121" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G121" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H121" t="str">
         <v>Critical</v>
@@ -4658,16 +4658,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D122" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #121</v>
+        <v>Calculate massive dataset into visual trend chart [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E122" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F122" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G122" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H122" t="str">
         <v>High</v>
@@ -4693,16 +4693,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D123" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #122</v>
+        <v>Push active vital stream into Daily Protocol engine [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E123" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F123" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G123" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H123" t="str">
         <v>High</v>
@@ -4728,16 +4728,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D124" t="str">
-        <v>Fetch structural JSON logic for health learning verification #123</v>
+        <v>Fetch structural JSON logic for health learning [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E124" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F124" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G124" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H124" t="str">
         <v>High</v>
@@ -4763,16 +4763,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D125" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #124</v>
+        <v>Serve recommended study (vascular pressure dyn.) [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E125" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F125" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G125" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H125" t="str">
         <v>High</v>
@@ -4798,16 +4798,16 @@
         <v>Analytics</v>
       </c>
       <c r="D126" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #125</v>
+        <v>Sync anonymous analytics to improve AI securely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E126" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F126" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G126" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H126" t="str">
         <v>Critical</v>
@@ -4833,16 +4833,16 @@
         <v>Data Report</v>
       </c>
       <c r="D127" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #126</v>
+        <v>Bundle and download all remote records into local ZIP [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E127" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F127" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G127" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H127" t="str">
         <v>High</v>
@@ -4868,16 +4868,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D128" t="str">
-        <v>Permanently drop relational database schemas entirely verification #127</v>
+        <v>Permanently drop relational database schemas entirely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E128" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F128" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating security guard (special char injection)</v>
       </c>
       <c r="G128" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H128" t="str">
         <v>High</v>
@@ -4903,16 +4903,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D129" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #128</v>
+        <v>Record new entry for blood pressure/heart rate [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E129" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F129" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G129" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H129" t="str">
         <v>High</v>
@@ -4938,16 +4938,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D130" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #129</v>
+        <v>Calculate massive dataset into visual trend chart [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E130" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F130" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G130" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H130" t="str">
         <v>High</v>
@@ -4973,16 +4973,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D131" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #130</v>
+        <v>Push active vital stream into Daily Protocol engine [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E131" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F131" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating normal path (standard execution)</v>
       </c>
       <c r="G131" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H131" t="str">
         <v>Critical</v>
@@ -5008,16 +5008,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D132" t="str">
-        <v>Fetch structural JSON logic for health learning verification #131</v>
+        <v>Fetch structural JSON logic for health learning [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E132" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F132" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G132" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H132" t="str">
         <v>High</v>
@@ -5043,16 +5043,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D133" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #132</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E133" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F133" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating security guard (special char injection)</v>
       </c>
       <c r="G133" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H133" t="str">
         <v>High</v>
@@ -5078,16 +5078,16 @@
         <v>Analytics</v>
       </c>
       <c r="D134" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #133</v>
+        <v>Sync anonymous analytics to improve AI securely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E134" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F134" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G134" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H134" t="str">
         <v>High</v>
@@ -5113,16 +5113,16 @@
         <v>Data Report</v>
       </c>
       <c r="D135" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #134</v>
+        <v>Bundle and download all remote records into local ZIP [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E135" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F135" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G135" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H135" t="str">
         <v>High</v>
@@ -5148,16 +5148,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D136" t="str">
-        <v>Permanently drop relational database schemas entirely verification #135</v>
+        <v>Permanently drop relational database schemas entirely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E136" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F136" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating normal path (standard execution)</v>
       </c>
       <c r="G136" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H136" t="str">
         <v>Critical</v>
@@ -5183,16 +5183,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D137" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #136</v>
+        <v>Record new entry for blood pressure/heart rate [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E137" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F137" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G137" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H137" t="str">
         <v>High</v>
@@ -5218,16 +5218,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D138" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #137</v>
+        <v>Calculate massive dataset into visual trend chart [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E138" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F138" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating security guard (special char injection)</v>
       </c>
       <c r="G138" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H138" t="str">
         <v>High</v>
@@ -5253,16 +5253,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D139" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #138</v>
+        <v>Push active vital stream into Daily Protocol engine [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E139" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F139" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G139" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H139" t="str">
         <v>High</v>
@@ -5288,16 +5288,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D140" t="str">
-        <v>Fetch structural JSON logic for health learning verification #139</v>
+        <v>Fetch structural JSON logic for health learning [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E140" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F140" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G140" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H140" t="str">
         <v>High</v>
@@ -5323,16 +5323,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D141" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #140</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E141" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F141" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating normal path (standard execution)</v>
       </c>
       <c r="G141" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H141" t="str">
         <v>Critical</v>
@@ -5358,16 +5358,16 @@
         <v>Analytics</v>
       </c>
       <c r="D142" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #141</v>
+        <v>Sync anonymous analytics to improve AI securely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E142" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F142" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G142" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H142" t="str">
         <v>High</v>
@@ -5393,16 +5393,16 @@
         <v>Data Report</v>
       </c>
       <c r="D143" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #142</v>
+        <v>Bundle and download all remote records into local ZIP [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E143" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F143" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating security guard (special char injection)</v>
       </c>
       <c r="G143" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H143" t="str">
         <v>High</v>
@@ -5428,16 +5428,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D144" t="str">
-        <v>Permanently drop relational database schemas entirely verification #143</v>
+        <v>Permanently drop relational database schemas entirely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E144" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F144" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G144" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H144" t="str">
         <v>High</v>
@@ -5463,16 +5463,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D145" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #144</v>
+        <v>Record new entry for blood pressure/heart rate [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E145" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F145" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G145" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H145" t="str">
         <v>High</v>
@@ -5498,16 +5498,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D146" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #145</v>
+        <v>Calculate massive dataset into visual trend chart [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E146" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F146" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating normal path (standard execution)</v>
       </c>
       <c r="G146" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H146" t="str">
         <v>Critical</v>
@@ -5533,16 +5533,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D147" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #146</v>
+        <v>Push active vital stream into Daily Protocol engine [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E147" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F147" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G147" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H147" t="str">
         <v>High</v>
@@ -5568,16 +5568,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D148" t="str">
-        <v>Fetch structural JSON logic for health learning verification #147</v>
+        <v>Fetch structural JSON logic for health learning [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E148" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F148" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating security guard (special char injection)</v>
       </c>
       <c r="G148" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H148" t="str">
         <v>High</v>
@@ -5603,16 +5603,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D149" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #148</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E149" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F149" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G149" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H149" t="str">
         <v>High</v>
@@ -5638,16 +5638,16 @@
         <v>Analytics</v>
       </c>
       <c r="D150" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #149</v>
+        <v>Sync anonymous analytics to improve AI securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E150" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F150" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G150" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H150" t="str">
         <v>High</v>
@@ -5673,16 +5673,16 @@
         <v>Data Report</v>
       </c>
       <c r="D151" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #150</v>
+        <v>Bundle and download all remote records into local ZIP [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E151" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F151" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating normal path (standard execution)</v>
       </c>
       <c r="G151" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H151" t="str">
         <v>Critical</v>
@@ -5708,16 +5708,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D152" t="str">
-        <v>Permanently drop relational database schemas entirely verification #151</v>
+        <v>Permanently drop relational database schemas entirely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E152" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F152" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G152" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H152" t="str">
         <v>High</v>
@@ -5743,16 +5743,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D153" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #152</v>
+        <v>Record new entry for blood pressure/heart rate [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E153" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F153" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G153" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H153" t="str">
         <v>High</v>
@@ -5778,16 +5778,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D154" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #153</v>
+        <v>Calculate massive dataset into visual trend chart [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E154" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F154" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G154" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H154" t="str">
         <v>High</v>
@@ -5813,16 +5813,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D155" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #154</v>
+        <v>Push active vital stream into Daily Protocol engine [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E155" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F155" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G155" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H155" t="str">
         <v>High</v>
@@ -5848,16 +5848,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D156" t="str">
-        <v>Fetch structural JSON logic for health learning verification #155</v>
+        <v>Fetch structural JSON logic for health learning [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E156" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F156" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating normal path (standard execution)</v>
       </c>
       <c r="G156" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H156" t="str">
         <v>Critical</v>
@@ -5883,16 +5883,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D157" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #156</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E157" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F157" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G157" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H157" t="str">
         <v>High</v>
@@ -5918,16 +5918,16 @@
         <v>Analytics</v>
       </c>
       <c r="D158" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #157</v>
+        <v>Sync anonymous analytics to improve AI securely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E158" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F158" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G158" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H158" t="str">
         <v>High</v>
@@ -5953,16 +5953,16 @@
         <v>Data Report</v>
       </c>
       <c r="D159" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #158</v>
+        <v>Bundle and download all remote records into local ZIP [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E159" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F159" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G159" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H159" t="str">
         <v>High</v>
@@ -5988,16 +5988,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D160" t="str">
-        <v>Permanently drop relational database schemas entirely verification #159</v>
+        <v>Permanently drop relational database schemas entirely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E160" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F160" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G160" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H160" t="str">
         <v>High</v>
@@ -6023,16 +6023,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D161" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #160</v>
+        <v>Record new entry for blood pressure/heart rate [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E161" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F161" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G161" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H161" t="str">
         <v>Critical</v>
@@ -6058,16 +6058,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D162" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #161</v>
+        <v>Calculate massive dataset into visual trend chart [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E162" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F162" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G162" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H162" t="str">
         <v>High</v>
@@ -6093,16 +6093,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D163" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #162</v>
+        <v>Push active vital stream into Daily Protocol engine [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E163" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F163" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G163" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H163" t="str">
         <v>High</v>
@@ -6128,16 +6128,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D164" t="str">
-        <v>Fetch structural JSON logic for health learning verification #163</v>
+        <v>Fetch structural JSON logic for health learning [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E164" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F164" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G164" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H164" t="str">
         <v>High</v>
@@ -6163,16 +6163,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D165" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #164</v>
+        <v>Serve recommended study (vascular pressure dyn.) [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E165" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F165" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G165" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H165" t="str">
         <v>High</v>
@@ -6198,16 +6198,16 @@
         <v>Analytics</v>
       </c>
       <c r="D166" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #165</v>
+        <v>Sync anonymous analytics to improve AI securely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E166" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F166" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G166" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H166" t="str">
         <v>Critical</v>
@@ -6233,16 +6233,16 @@
         <v>Data Report</v>
       </c>
       <c r="D167" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #166</v>
+        <v>Bundle and download all remote records into local ZIP [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E167" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F167" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G167" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H167" t="str">
         <v>High</v>
@@ -6268,16 +6268,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D168" t="str">
-        <v>Permanently drop relational database schemas entirely verification #167</v>
+        <v>Permanently drop relational database schemas entirely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E168" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F168" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating security guard (special char injection)</v>
       </c>
       <c r="G168" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H168" t="str">
         <v>High</v>
@@ -6303,16 +6303,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D169" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #168</v>
+        <v>Record new entry for blood pressure/heart rate [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E169" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F169" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G169" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H169" t="str">
         <v>High</v>
@@ -6338,16 +6338,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D170" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #169</v>
+        <v>Calculate massive dataset into visual trend chart [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E170" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F170" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G170" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H170" t="str">
         <v>High</v>
@@ -6373,16 +6373,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D171" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #170</v>
+        <v>Push active vital stream into Daily Protocol engine [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E171" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F171" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating normal path (standard execution)</v>
       </c>
       <c r="G171" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H171" t="str">
         <v>Critical</v>
@@ -6408,16 +6408,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D172" t="str">
-        <v>Fetch structural JSON logic for health learning verification #171</v>
+        <v>Fetch structural JSON logic for health learning [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E172" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F172" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G172" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H172" t="str">
         <v>High</v>
@@ -6443,16 +6443,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D173" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #172</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E173" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F173" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating security guard (special char injection)</v>
       </c>
       <c r="G173" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H173" t="str">
         <v>High</v>
@@ -6478,16 +6478,16 @@
         <v>Analytics</v>
       </c>
       <c r="D174" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #173</v>
+        <v>Sync anonymous analytics to improve AI securely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E174" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F174" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G174" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H174" t="str">
         <v>High</v>
@@ -6513,16 +6513,16 @@
         <v>Data Report</v>
       </c>
       <c r="D175" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #174</v>
+        <v>Bundle and download all remote records into local ZIP [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E175" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F175" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G175" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H175" t="str">
         <v>High</v>
@@ -6548,16 +6548,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D176" t="str">
-        <v>Permanently drop relational database schemas entirely verification #175</v>
+        <v>Permanently drop relational database schemas entirely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E176" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F176" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating normal path (standard execution)</v>
       </c>
       <c r="G176" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H176" t="str">
         <v>Critical</v>
@@ -6583,16 +6583,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D177" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #176</v>
+        <v>Record new entry for blood pressure/heart rate [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E177" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F177" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G177" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H177" t="str">
         <v>High</v>
@@ -6618,16 +6618,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D178" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #177</v>
+        <v>Calculate massive dataset into visual trend chart [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E178" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F178" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating security guard (special char injection)</v>
       </c>
       <c r="G178" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H178" t="str">
         <v>High</v>
@@ -6653,16 +6653,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D179" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #178</v>
+        <v>Push active vital stream into Daily Protocol engine [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E179" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F179" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G179" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H179" t="str">
         <v>High</v>
@@ -6688,16 +6688,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D180" t="str">
-        <v>Fetch structural JSON logic for health learning verification #179</v>
+        <v>Fetch structural JSON logic for health learning [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E180" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F180" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G180" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H180" t="str">
         <v>High</v>
@@ -6723,16 +6723,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D181" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #180</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E181" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F181" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating normal path (standard execution)</v>
       </c>
       <c r="G181" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H181" t="str">
         <v>Critical</v>
@@ -6758,16 +6758,16 @@
         <v>Analytics</v>
       </c>
       <c r="D182" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #181</v>
+        <v>Sync anonymous analytics to improve AI securely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E182" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F182" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G182" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H182" t="str">
         <v>High</v>
@@ -6793,16 +6793,16 @@
         <v>Data Report</v>
       </c>
       <c r="D183" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #182</v>
+        <v>Bundle and download all remote records into local ZIP [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E183" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F183" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating security guard (special char injection)</v>
       </c>
       <c r="G183" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H183" t="str">
         <v>High</v>
@@ -6828,16 +6828,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D184" t="str">
-        <v>Permanently drop relational database schemas entirely verification #183</v>
+        <v>Permanently drop relational database schemas entirely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E184" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F184" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G184" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H184" t="str">
         <v>High</v>
@@ -6863,16 +6863,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D185" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #184</v>
+        <v>Record new entry for blood pressure/heart rate [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E185" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F185" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G185" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H185" t="str">
         <v>High</v>
@@ -6898,16 +6898,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D186" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #185</v>
+        <v>Calculate massive dataset into visual trend chart [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E186" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F186" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating normal path (standard execution)</v>
       </c>
       <c r="G186" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H186" t="str">
         <v>Critical</v>
@@ -6933,16 +6933,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D187" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #186</v>
+        <v>Push active vital stream into Daily Protocol engine [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E187" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F187" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G187" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H187" t="str">
         <v>High</v>
@@ -6968,16 +6968,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D188" t="str">
-        <v>Fetch structural JSON logic for health learning verification #187</v>
+        <v>Fetch structural JSON logic for health learning [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E188" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F188" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating security guard (special char injection)</v>
       </c>
       <c r="G188" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H188" t="str">
         <v>High</v>
@@ -7003,16 +7003,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D189" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #188</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E189" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F189" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G189" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H189" t="str">
         <v>High</v>
@@ -7038,16 +7038,16 @@
         <v>Analytics</v>
       </c>
       <c r="D190" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #189</v>
+        <v>Sync anonymous analytics to improve AI securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E190" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F190" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G190" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H190" t="str">
         <v>High</v>
@@ -7073,16 +7073,16 @@
         <v>Data Report</v>
       </c>
       <c r="D191" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #190</v>
+        <v>Bundle and download all remote records into local ZIP [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E191" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F191" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating normal path (standard execution)</v>
       </c>
       <c r="G191" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H191" t="str">
         <v>Critical</v>
@@ -7108,16 +7108,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D192" t="str">
-        <v>Permanently drop relational database schemas entirely verification #191</v>
+        <v>Permanently drop relational database schemas entirely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E192" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F192" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G192" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H192" t="str">
         <v>High</v>
@@ -7143,16 +7143,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D193" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #192</v>
+        <v>Record new entry for blood pressure/heart rate [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E193" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F193" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G193" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H193" t="str">
         <v>High</v>
@@ -7178,16 +7178,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D194" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #193</v>
+        <v>Calculate massive dataset into visual trend chart [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E194" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F194" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G194" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H194" t="str">
         <v>High</v>
@@ -7213,16 +7213,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D195" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #194</v>
+        <v>Push active vital stream into Daily Protocol engine [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E195" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F195" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G195" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H195" t="str">
         <v>High</v>
@@ -7248,16 +7248,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D196" t="str">
-        <v>Fetch structural JSON logic for health learning verification #195</v>
+        <v>Fetch structural JSON logic for health learning [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E196" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F196" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating normal path (standard execution)</v>
       </c>
       <c r="G196" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H196" t="str">
         <v>Critical</v>
@@ -7283,16 +7283,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D197" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #196</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E197" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F197" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G197" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H197" t="str">
         <v>High</v>
@@ -7318,16 +7318,16 @@
         <v>Analytics</v>
       </c>
       <c r="D198" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #197</v>
+        <v>Sync anonymous analytics to improve AI securely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E198" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F198" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G198" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H198" t="str">
         <v>High</v>
@@ -7353,16 +7353,16 @@
         <v>Data Report</v>
       </c>
       <c r="D199" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #198</v>
+        <v>Bundle and download all remote records into local ZIP [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E199" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F199" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G199" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H199" t="str">
         <v>High</v>
@@ -7388,16 +7388,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D200" t="str">
-        <v>Permanently drop relational database schemas entirely verification #199</v>
+        <v>Permanently drop relational database schemas entirely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E200" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F200" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G200" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H200" t="str">
         <v>High</v>
@@ -7423,16 +7423,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D201" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #200</v>
+        <v>Record new entry for blood pressure/heart rate [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E201" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F201" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G201" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H201" t="str">
         <v>Critical</v>
@@ -7458,16 +7458,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D202" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #201</v>
+        <v>Calculate massive dataset into visual trend chart [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E202" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F202" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G202" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H202" t="str">
         <v>High</v>
@@ -7493,16 +7493,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D203" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #202</v>
+        <v>Push active vital stream into Daily Protocol engine [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E203" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F203" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G203" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H203" t="str">
         <v>High</v>
@@ -7528,16 +7528,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D204" t="str">
-        <v>Fetch structural JSON logic for health learning verification #203</v>
+        <v>Fetch structural JSON logic for health learning [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E204" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F204" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G204" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H204" t="str">
         <v>High</v>
@@ -7563,16 +7563,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D205" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #204</v>
+        <v>Serve recommended study (vascular pressure dyn.) [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E205" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F205" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G205" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H205" t="str">
         <v>High</v>
@@ -7598,16 +7598,16 @@
         <v>Analytics</v>
       </c>
       <c r="D206" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #205</v>
+        <v>Sync anonymous analytics to improve AI securely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E206" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F206" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G206" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H206" t="str">
         <v>Critical</v>
@@ -7633,16 +7633,16 @@
         <v>Data Report</v>
       </c>
       <c r="D207" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #206</v>
+        <v>Bundle and download all remote records into local ZIP [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E207" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F207" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G207" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H207" t="str">
         <v>High</v>
@@ -7668,16 +7668,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D208" t="str">
-        <v>Permanently drop relational database schemas entirely verification #207</v>
+        <v>Permanently drop relational database schemas entirely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E208" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F208" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating security guard (special char injection)</v>
       </c>
       <c r="G208" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H208" t="str">
         <v>High</v>
@@ -7703,16 +7703,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D209" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #208</v>
+        <v>Record new entry for blood pressure/heart rate [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E209" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F209" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G209" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H209" t="str">
         <v>High</v>
@@ -7738,16 +7738,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D210" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #209</v>
+        <v>Calculate massive dataset into visual trend chart [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E210" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F210" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G210" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H210" t="str">
         <v>High</v>
@@ -7773,16 +7773,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D211" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #210</v>
+        <v>Push active vital stream into Daily Protocol engine [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E211" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F211" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating normal path (standard execution)</v>
       </c>
       <c r="G211" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H211" t="str">
         <v>Critical</v>
@@ -7808,16 +7808,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D212" t="str">
-        <v>Fetch structural JSON logic for health learning verification #211</v>
+        <v>Fetch structural JSON logic for health learning [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E212" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F212" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G212" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H212" t="str">
         <v>High</v>
@@ -7843,16 +7843,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D213" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #212</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E213" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F213" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating security guard (special char injection)</v>
       </c>
       <c r="G213" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H213" t="str">
         <v>High</v>
@@ -7878,16 +7878,16 @@
         <v>Analytics</v>
       </c>
       <c r="D214" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #213</v>
+        <v>Sync anonymous analytics to improve AI securely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E214" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F214" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G214" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H214" t="str">
         <v>High</v>
@@ -7913,16 +7913,16 @@
         <v>Data Report</v>
       </c>
       <c r="D215" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #214</v>
+        <v>Bundle and download all remote records into local ZIP [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E215" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F215" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G215" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H215" t="str">
         <v>High</v>
@@ -7948,16 +7948,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D216" t="str">
-        <v>Permanently drop relational database schemas entirely verification #215</v>
+        <v>Permanently drop relational database schemas entirely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E216" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F216" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating normal path (standard execution)</v>
       </c>
       <c r="G216" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H216" t="str">
         <v>Critical</v>
@@ -7983,16 +7983,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D217" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #216</v>
+        <v>Record new entry for blood pressure/heart rate [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E217" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F217" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G217" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H217" t="str">
         <v>High</v>
@@ -8018,16 +8018,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D218" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #217</v>
+        <v>Calculate massive dataset into visual trend chart [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E218" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F218" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating security guard (special char injection)</v>
       </c>
       <c r="G218" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H218" t="str">
         <v>High</v>
@@ -8053,16 +8053,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D219" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #218</v>
+        <v>Push active vital stream into Daily Protocol engine [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E219" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F219" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G219" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H219" t="str">
         <v>High</v>
@@ -8088,16 +8088,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D220" t="str">
-        <v>Fetch structural JSON logic for health learning verification #219</v>
+        <v>Fetch structural JSON logic for health learning [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E220" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F220" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G220" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H220" t="str">
         <v>High</v>
@@ -8123,16 +8123,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D221" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #220</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E221" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F221" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating normal path (standard execution)</v>
       </c>
       <c r="G221" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H221" t="str">
         <v>Critical</v>
@@ -8158,16 +8158,16 @@
         <v>Analytics</v>
       </c>
       <c r="D222" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #221</v>
+        <v>Sync anonymous analytics to improve AI securely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E222" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F222" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G222" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H222" t="str">
         <v>High</v>
@@ -8193,16 +8193,16 @@
         <v>Data Report</v>
       </c>
       <c r="D223" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #222</v>
+        <v>Bundle and download all remote records into local ZIP [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E223" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F223" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating security guard (special char injection)</v>
       </c>
       <c r="G223" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H223" t="str">
         <v>High</v>
@@ -8228,16 +8228,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D224" t="str">
-        <v>Permanently drop relational database schemas entirely verification #223</v>
+        <v>Permanently drop relational database schemas entirely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E224" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F224" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G224" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H224" t="str">
         <v>High</v>
@@ -8263,16 +8263,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D225" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #224</v>
+        <v>Record new entry for blood pressure/heart rate [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E225" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F225" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G225" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H225" t="str">
         <v>High</v>
@@ -8298,16 +8298,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D226" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #225</v>
+        <v>Calculate massive dataset into visual trend chart [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E226" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F226" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating normal path (standard execution)</v>
       </c>
       <c r="G226" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H226" t="str">
         <v>Critical</v>
@@ -8333,16 +8333,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D227" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #226</v>
+        <v>Push active vital stream into Daily Protocol engine [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E227" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F227" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G227" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H227" t="str">
         <v>High</v>
@@ -8368,16 +8368,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D228" t="str">
-        <v>Fetch structural JSON logic for health learning verification #227</v>
+        <v>Fetch structural JSON logic for health learning [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E228" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F228" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating security guard (special char injection)</v>
       </c>
       <c r="G228" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H228" t="str">
         <v>High</v>
@@ -8403,16 +8403,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D229" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #228</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E229" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F229" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G229" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H229" t="str">
         <v>High</v>
@@ -8438,16 +8438,16 @@
         <v>Analytics</v>
       </c>
       <c r="D230" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #229</v>
+        <v>Sync anonymous analytics to improve AI securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E230" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F230" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G230" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H230" t="str">
         <v>High</v>
@@ -8473,16 +8473,16 @@
         <v>Data Report</v>
       </c>
       <c r="D231" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #230</v>
+        <v>Bundle and download all remote records into local ZIP [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E231" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F231" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating normal path (standard execution)</v>
       </c>
       <c r="G231" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H231" t="str">
         <v>Critical</v>
@@ -8508,16 +8508,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D232" t="str">
-        <v>Permanently drop relational database schemas entirely verification #231</v>
+        <v>Permanently drop relational database schemas entirely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E232" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F232" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G232" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H232" t="str">
         <v>High</v>
@@ -8543,16 +8543,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D233" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #232</v>
+        <v>Record new entry for blood pressure/heart rate [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E233" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F233" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G233" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H233" t="str">
         <v>High</v>
@@ -8578,16 +8578,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D234" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #233</v>
+        <v>Calculate massive dataset into visual trend chart [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E234" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F234" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G234" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H234" t="str">
         <v>High</v>
@@ -8613,16 +8613,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D235" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #234</v>
+        <v>Push active vital stream into Daily Protocol engine [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E235" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F235" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G235" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H235" t="str">
         <v>High</v>
@@ -8648,16 +8648,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D236" t="str">
-        <v>Fetch structural JSON logic for health learning verification #235</v>
+        <v>Fetch structural JSON logic for health learning [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E236" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F236" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating normal path (standard execution)</v>
       </c>
       <c r="G236" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H236" t="str">
         <v>Critical</v>
@@ -8683,16 +8683,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D237" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #236</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E237" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F237" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G237" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H237" t="str">
         <v>High</v>
@@ -8718,16 +8718,16 @@
         <v>Analytics</v>
       </c>
       <c r="D238" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #237</v>
+        <v>Sync anonymous analytics to improve AI securely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E238" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F238" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G238" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H238" t="str">
         <v>High</v>
@@ -8753,16 +8753,16 @@
         <v>Data Report</v>
       </c>
       <c r="D239" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #238</v>
+        <v>Bundle and download all remote records into local ZIP [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E239" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F239" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G239" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H239" t="str">
         <v>High</v>
@@ -8788,16 +8788,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D240" t="str">
-        <v>Permanently drop relational database schemas entirely verification #239</v>
+        <v>Permanently drop relational database schemas entirely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E240" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F240" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G240" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H240" t="str">
         <v>High</v>
@@ -8823,16 +8823,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D241" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #240</v>
+        <v>Record new entry for blood pressure/heart rate [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E241" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F241" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G241" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H241" t="str">
         <v>Critical</v>
@@ -8858,16 +8858,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D242" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #241</v>
+        <v>Calculate massive dataset into visual trend chart [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E242" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F242" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G242" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H242" t="str">
         <v>High</v>
@@ -8893,16 +8893,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D243" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #242</v>
+        <v>Push active vital stream into Daily Protocol engine [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E243" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F243" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G243" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H243" t="str">
         <v>High</v>
@@ -8928,16 +8928,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D244" t="str">
-        <v>Fetch structural JSON logic for health learning verification #243</v>
+        <v>Fetch structural JSON logic for health learning [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E244" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F244" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G244" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H244" t="str">
         <v>High</v>
@@ -8963,16 +8963,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D245" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #244</v>
+        <v>Serve recommended study (vascular pressure dyn.) [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E245" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F245" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G245" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H245" t="str">
         <v>High</v>
@@ -8998,16 +8998,16 @@
         <v>Analytics</v>
       </c>
       <c r="D246" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #245</v>
+        <v>Sync anonymous analytics to improve AI securely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E246" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F246" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G246" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H246" t="str">
         <v>Critical</v>
@@ -9033,16 +9033,16 @@
         <v>Data Report</v>
       </c>
       <c r="D247" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #246</v>
+        <v>Bundle and download all remote records into local ZIP [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E247" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F247" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G247" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H247" t="str">
         <v>High</v>
@@ -9068,16 +9068,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D248" t="str">
-        <v>Permanently drop relational database schemas entirely verification #247</v>
+        <v>Permanently drop relational database schemas entirely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E248" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F248" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating security guard (special char injection)</v>
       </c>
       <c r="G248" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H248" t="str">
         <v>High</v>
@@ -9103,16 +9103,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D249" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #248</v>
+        <v>Record new entry for blood pressure/heart rate [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E249" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F249" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G249" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H249" t="str">
         <v>High</v>
@@ -9138,16 +9138,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D250" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #249</v>
+        <v>Calculate massive dataset into visual trend chart [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E250" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F250" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G250" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H250" t="str">
         <v>High</v>
@@ -9173,16 +9173,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D251" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #250</v>
+        <v>Push active vital stream into Daily Protocol engine [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E251" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F251" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating normal path (standard execution)</v>
       </c>
       <c r="G251" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H251" t="str">
         <v>Critical</v>
@@ -9208,16 +9208,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D252" t="str">
-        <v>Fetch structural JSON logic for health learning verification #251</v>
+        <v>Fetch structural JSON logic for health learning [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E252" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F252" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G252" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H252" t="str">
         <v>High</v>
@@ -9243,16 +9243,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D253" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #252</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E253" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F253" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating security guard (special char injection)</v>
       </c>
       <c r="G253" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H253" t="str">
         <v>High</v>
@@ -9278,16 +9278,16 @@
         <v>Analytics</v>
       </c>
       <c r="D254" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #253</v>
+        <v>Sync anonymous analytics to improve AI securely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E254" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F254" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G254" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H254" t="str">
         <v>High</v>
@@ -9313,16 +9313,16 @@
         <v>Data Report</v>
       </c>
       <c r="D255" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #254</v>
+        <v>Bundle and download all remote records into local ZIP [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E255" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F255" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G255" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H255" t="str">
         <v>High</v>
@@ -9348,16 +9348,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D256" t="str">
-        <v>Permanently drop relational database schemas entirely verification #255</v>
+        <v>Permanently drop relational database schemas entirely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E256" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F256" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating normal path (standard execution)</v>
       </c>
       <c r="G256" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H256" t="str">
         <v>Critical</v>
@@ -9383,16 +9383,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D257" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #256</v>
+        <v>Record new entry for blood pressure/heart rate [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E257" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F257" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G257" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H257" t="str">
         <v>High</v>
@@ -9418,16 +9418,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D258" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #257</v>
+        <v>Calculate massive dataset into visual trend chart [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E258" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F258" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating security guard (special char injection)</v>
       </c>
       <c r="G258" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H258" t="str">
         <v>High</v>
@@ -9453,16 +9453,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D259" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #258</v>
+        <v>Push active vital stream into Daily Protocol engine [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E259" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F259" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G259" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H259" t="str">
         <v>High</v>
@@ -9488,16 +9488,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D260" t="str">
-        <v>Fetch structural JSON logic for health learning verification #259</v>
+        <v>Fetch structural JSON logic for health learning [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E260" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F260" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G260" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H260" t="str">
         <v>High</v>
@@ -9523,16 +9523,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D261" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #260</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E261" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F261" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating normal path (standard execution)</v>
       </c>
       <c r="G261" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H261" t="str">
         <v>Critical</v>
@@ -9558,16 +9558,16 @@
         <v>Analytics</v>
       </c>
       <c r="D262" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #261</v>
+        <v>Sync anonymous analytics to improve AI securely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E262" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F262" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G262" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H262" t="str">
         <v>High</v>
@@ -9593,16 +9593,16 @@
         <v>Data Report</v>
       </c>
       <c r="D263" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #262</v>
+        <v>Bundle and download all remote records into local ZIP [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E263" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F263" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating security guard (special char injection)</v>
       </c>
       <c r="G263" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H263" t="str">
         <v>High</v>
@@ -9628,16 +9628,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D264" t="str">
-        <v>Permanently drop relational database schemas entirely verification #263</v>
+        <v>Permanently drop relational database schemas entirely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E264" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F264" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G264" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H264" t="str">
         <v>High</v>
@@ -9663,16 +9663,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D265" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #264</v>
+        <v>Record new entry for blood pressure/heart rate [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E265" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F265" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G265" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H265" t="str">
         <v>High</v>
@@ -9698,16 +9698,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D266" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #265</v>
+        <v>Calculate massive dataset into visual trend chart [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E266" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F266" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating normal path (standard execution)</v>
       </c>
       <c r="G266" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H266" t="str">
         <v>Critical</v>
@@ -9733,16 +9733,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D267" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #266</v>
+        <v>Push active vital stream into Daily Protocol engine [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E267" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F267" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G267" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H267" t="str">
         <v>High</v>
@@ -9768,16 +9768,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D268" t="str">
-        <v>Fetch structural JSON logic for health learning verification #267</v>
+        <v>Fetch structural JSON logic for health learning [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E268" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F268" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating security guard (special char injection)</v>
       </c>
       <c r="G268" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H268" t="str">
         <v>High</v>
@@ -9803,16 +9803,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D269" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #268</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E269" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F269" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G269" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H269" t="str">
         <v>High</v>
@@ -9838,16 +9838,16 @@
         <v>Analytics</v>
       </c>
       <c r="D270" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #269</v>
+        <v>Sync anonymous analytics to improve AI securely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E270" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F270" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G270" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H270" t="str">
         <v>High</v>
@@ -9873,16 +9873,16 @@
         <v>Data Report</v>
       </c>
       <c r="D271" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #270</v>
+        <v>Bundle and download all remote records into local ZIP [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E271" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F271" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating normal path (standard execution)</v>
       </c>
       <c r="G271" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H271" t="str">
         <v>Critical</v>
@@ -9908,16 +9908,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D272" t="str">
-        <v>Permanently drop relational database schemas entirely verification #271</v>
+        <v>Permanently drop relational database schemas entirely [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E272" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F272" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G272" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H272" t="str">
         <v>High</v>
@@ -9943,16 +9943,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D273" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #272</v>
+        <v>Record new entry for blood pressure/heart rate [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E273" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F273" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G273" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H273" t="str">
         <v>High</v>
@@ -9978,16 +9978,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D274" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #273</v>
+        <v>Calculate massive dataset into visual trend chart [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E274" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F274" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G274" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H274" t="str">
         <v>High</v>
@@ -10013,16 +10013,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D275" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #274</v>
+        <v>Push active vital stream into Daily Protocol engine [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E275" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F275" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G275" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H275" t="str">
         <v>High</v>
@@ -10048,16 +10048,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D276" t="str">
-        <v>Fetch structural JSON logic for health learning verification #275</v>
+        <v>Fetch structural JSON logic for health learning [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E276" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F276" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating normal path (standard execution)</v>
       </c>
       <c r="G276" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H276" t="str">
         <v>Critical</v>
@@ -10083,16 +10083,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D277" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #276</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E277" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F277" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G277" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H277" t="str">
         <v>High</v>
@@ -10118,16 +10118,16 @@
         <v>Analytics</v>
       </c>
       <c r="D278" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #277</v>
+        <v>Sync anonymous analytics to improve AI securely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E278" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F278" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating security guard (special char injection)</v>
       </c>
       <c r="G278" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H278" t="str">
         <v>High</v>
@@ -10153,16 +10153,16 @@
         <v>Data Report</v>
       </c>
       <c r="D279" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #278</v>
+        <v>Bundle and download all remote records into local ZIP [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E279" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F279" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G279" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H279" t="str">
         <v>High</v>
@@ -10188,16 +10188,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D280" t="str">
-        <v>Permanently drop relational database schemas entirely verification #279</v>
+        <v>Permanently drop relational database schemas entirely [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E280" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F280" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G280" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H280" t="str">
         <v>High</v>
@@ -10223,16 +10223,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D281" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #280</v>
+        <v>Record new entry for blood pressure/heart rate [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E281" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F281" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G281" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H281" t="str">
         <v>Critical</v>
@@ -10258,16 +10258,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D282" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #281</v>
+        <v>Calculate massive dataset into visual trend chart [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E282" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F282" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G282" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H282" t="str">
         <v>High</v>
@@ -10293,16 +10293,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D283" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #282</v>
+        <v>Push active vital stream into Daily Protocol engine [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E283" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F283" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating security guard (special char injection)</v>
       </c>
       <c r="G283" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H283" t="str">
         <v>High</v>
@@ -10328,16 +10328,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D284" t="str">
-        <v>Fetch structural JSON logic for health learning verification #283</v>
+        <v>Fetch structural JSON logic for health learning [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E284" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F284" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G284" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H284" t="str">
         <v>High</v>
@@ -10363,16 +10363,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D285" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #284</v>
+        <v>Serve recommended study (vascular pressure dyn.) [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E285" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F285" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G285" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H285" t="str">
         <v>High</v>
@@ -10398,16 +10398,16 @@
         <v>Analytics</v>
       </c>
       <c r="D286" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #285</v>
+        <v>Sync anonymous analytics to improve AI securely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E286" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F286" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating normal path (standard execution)</v>
       </c>
       <c r="G286" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H286" t="str">
         <v>Critical</v>
@@ -10433,16 +10433,16 @@
         <v>Data Report</v>
       </c>
       <c r="D287" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #286</v>
+        <v>Bundle and download all remote records into local ZIP [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E287" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F287" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G287" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H287" t="str">
         <v>High</v>
@@ -10468,16 +10468,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D288" t="str">
-        <v>Permanently drop relational database schemas entirely verification #287</v>
+        <v>Permanently drop relational database schemas entirely [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E288" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F288" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating security guard (special char injection)</v>
       </c>
       <c r="G288" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H288" t="str">
         <v>High</v>
@@ -10503,16 +10503,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D289" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #288</v>
+        <v>Record new entry for blood pressure/heart rate [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E289" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F289" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G289" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H289" t="str">
         <v>High</v>
@@ -10538,16 +10538,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D290" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #289</v>
+        <v>Calculate massive dataset into visual trend chart [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E290" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F290" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G290" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H290" t="str">
         <v>High</v>
@@ -10573,16 +10573,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D291" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #290</v>
+        <v>Push active vital stream into Daily Protocol engine [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E291" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F291" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating normal path (standard execution)</v>
       </c>
       <c r="G291" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H291" t="str">
         <v>Critical</v>
@@ -10608,16 +10608,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D292" t="str">
-        <v>Fetch structural JSON logic for health learning verification #291</v>
+        <v>Fetch structural JSON logic for health learning [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E292" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F292" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G292" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H292" t="str">
         <v>High</v>
@@ -10643,16 +10643,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D293" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #292</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E293" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F293" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating security guard (special char injection)</v>
       </c>
       <c r="G293" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H293" t="str">
         <v>High</v>
@@ -10678,16 +10678,16 @@
         <v>Analytics</v>
       </c>
       <c r="D294" t="str">
-        <v>Sync anonymous analytics to improve AI securely verification #293</v>
+        <v>Sync anonymous analytics to improve AI securely [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E294" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F294" t="str">
-        <v>Navigate to Privacy Centre and perform Analytics action</v>
+        <v>Execute Analytics action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G294" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H294" t="str">
         <v>High</v>
@@ -10713,16 +10713,16 @@
         <v>Data Report</v>
       </c>
       <c r="D295" t="str">
-        <v>Bundle and download all remote records into local ZIP verification #294</v>
+        <v>Bundle and download all remote records into local ZIP [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E295" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F295" t="str">
-        <v>Navigate to Privacy Centre and perform Data Report action</v>
+        <v>Execute Data Report action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G295" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H295" t="str">
         <v>High</v>
@@ -10748,16 +10748,16 @@
         <v>Delete Account</v>
       </c>
       <c r="D296" t="str">
-        <v>Permanently drop relational database schemas entirely verification #295</v>
+        <v>Permanently drop relational database schemas entirely [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E296" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F296" t="str">
-        <v>Navigate to Privacy Centre and perform Delete Account action</v>
+        <v>Execute Delete Account action while simulating normal path (standard execution)</v>
       </c>
       <c r="G296" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H296" t="str">
         <v>Critical</v>
@@ -10783,16 +10783,16 @@
         <v>Update Biometrics</v>
       </c>
       <c r="D297" t="str">
-        <v>Record new entry for blood pressure/heart rate verification #296</v>
+        <v>Record new entry for blood pressure/heart rate [Network Lag (Simulated 3G Delay)]</v>
       </c>
       <c r="E297" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F297" t="str">
-        <v>Navigate to Tracker and perform Update Biometrics action</v>
+        <v>Execute Update Biometrics action while simulating network lag (simulated 3g delay)</v>
       </c>
       <c r="G297" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H297" t="str">
         <v>High</v>
@@ -10818,16 +10818,16 @@
         <v>Statistical Trends</v>
       </c>
       <c r="D298" t="str">
-        <v>Calculate massive dataset into visual trend chart verification #297</v>
+        <v>Calculate massive dataset into visual trend chart [Security Guard (Special Char Injection)]</v>
       </c>
       <c r="E298" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F298" t="str">
-        <v>Navigate to Tracker and perform Statistical Trends action</v>
+        <v>Execute Statistical Trends action while simulating security guard (special char injection)</v>
       </c>
       <c r="G298" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H298" t="str">
         <v>High</v>
@@ -10853,16 +10853,16 @@
         <v>Active Vitals</v>
       </c>
       <c r="D299" t="str">
-        <v>Push active vital stream into Daily Protocol engine verification #298</v>
+        <v>Push active vital stream into Daily Protocol engine [Stress Lock (Rapid Double-click Event)]</v>
       </c>
       <c r="E299" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F299" t="str">
-        <v>Navigate to Tracker and perform Active Vitals action</v>
+        <v>Execute Active Vitals action while simulating stress lock (rapid double-click event)</v>
       </c>
       <c r="G299" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H299" t="str">
         <v>High</v>
@@ -10888,16 +10888,16 @@
         <v>Nutrition &amp; Sleep</v>
       </c>
       <c r="D300" t="str">
-        <v>Fetch structural JSON logic for health learning verification #299</v>
+        <v>Fetch structural JSON logic for health learning [System Interrupt (Background Suspend)]</v>
       </c>
       <c r="E300" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F300" t="str">
-        <v>Navigate to Learn Module and perform Nutrition &amp; Sleep action</v>
+        <v>Execute Nutrition &amp; Sleep action while simulating system interrupt (background suspend)</v>
       </c>
       <c r="G300" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H300" t="str">
         <v>High</v>
@@ -10923,16 +10923,16 @@
         <v>Pathology/Pharma</v>
       </c>
       <c r="D301" t="str">
-        <v>Serve recommended study (vascular pressure dyn.) verification #300</v>
+        <v>Serve recommended study (vascular pressure dyn.) [Normal Path (Standard Execution)]</v>
       </c>
       <c r="E301" t="str">
         <v>App running on Backend API</v>
       </c>
       <c r="F301" t="str">
-        <v>Navigate to Learn Module and perform Pathology/Pharma action</v>
+        <v>Execute Pathology/Pharma action while simulating normal path (standard execution)</v>
       </c>
       <c r="G301" t="str">
-        <v>Action completes successfully within standard latency bounds</v>
+        <v>Action completes securely despite active simulation parameters</v>
       </c>
       <c r="H301" t="str">
         <v>Critical</v>

--- a/e2e_tests_suite/Report_03_API_Testing.xlsx
+++ b/e2e_tests_suite/Report_03_API_Testing.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K301"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -458,16 +458,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D2" t="str">
-        <v>Verify /api/auth/login - Valid email and password returns 200 JWT token</v>
+        <v>[Positive Flow] /api/auth/login - Valid email and password returns 200 JWT token</v>
       </c>
       <c r="E2" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F2" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'Valid email and password returns 200 JWT token'</v>
+        <v>Dispatch API call to /api/auth/login: 'Valid email and password returns 200 JWT token' (Positive Flow)</v>
       </c>
       <c r="G2" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H2" t="str">
         <v>Medium</v>
@@ -493,16 +493,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D3" t="str">
-        <v>Verify /api/auth/login - Invalid password returns 401 Unauthorized</v>
+        <v>[Positive Flow] /api/auth/login - Invalid password returns 401 Unauthorized</v>
       </c>
       <c r="E3" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F3" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'Invalid password returns 401 Unauthorized'</v>
+        <v>Dispatch API call to /api/auth/login: 'Invalid password returns 401 Unauthorized' (Positive Flow)</v>
       </c>
       <c r="G3" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H3" t="str">
         <v>High</v>
@@ -528,16 +528,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D4" t="str">
-        <v>Verify /api/auth/login - Non-existent user email returns 404 Not Found</v>
+        <v>[Positive Flow] /api/auth/login - Non-existent user email returns 404 Not Found</v>
       </c>
       <c r="E4" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F4" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'Non-existent user email returns 404 Not Found'</v>
+        <v>Dispatch API call to /api/auth/login: 'Non-existent user email returns 404 Not Found' (Positive Flow)</v>
       </c>
       <c r="G4" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H4" t="str">
         <v>Critical</v>
@@ -563,16 +563,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D5" t="str">
-        <v>Verify /api/auth/login - Empty payload returns 400 Bad Request</v>
+        <v>[Positive Flow] /api/auth/login - Empty payload returns 400 Bad Request</v>
       </c>
       <c r="E5" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F5" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'Empty payload returns 400 Bad Request'</v>
+        <v>Dispatch API call to /api/auth/login: 'Empty payload returns 400 Bad Request' (Positive Flow)</v>
       </c>
       <c r="G5" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H5" t="str">
         <v>High</v>
@@ -598,16 +598,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D6" t="str">
-        <v>Verify /api/auth/login - Expired JWT token returns 401 Session Expired</v>
+        <v>[Positive Flow] /api/auth/login - Expired JWT token returns 401 Session Expired</v>
       </c>
       <c r="E6" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F6" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'Expired JWT token returns 401 Session Expired'</v>
+        <v>Dispatch API call to /api/auth/login: 'Expired JWT token returns 401 Session Expired' (Positive Flow)</v>
       </c>
       <c r="G6" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H6" t="str">
         <v>Medium</v>
@@ -633,16 +633,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D7" t="str">
-        <v>Verify /api/auth/login - Malformed JWT header returns 403 Forbidden</v>
+        <v>[Positive Flow] /api/auth/login - Malformed JWT header returns 403 Forbidden</v>
       </c>
       <c r="E7" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F7" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'Malformed JWT header returns 403 Forbidden'</v>
+        <v>Dispatch API call to /api/auth/login: 'Malformed JWT header returns 403 Forbidden' (Positive Flow)</v>
       </c>
       <c r="G7" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H7" t="str">
         <v>Critical</v>
@@ -668,16 +668,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D8" t="str">
-        <v>Verify /api/auth/login - Refresh token exchange returns 200 New Token</v>
+        <v>[Positive Flow] /api/auth/login - Refresh token exchange returns 200 New Token</v>
       </c>
       <c r="E8" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F8" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'Refresh token exchange returns 200 New Token'</v>
+        <v>Dispatch API call to /api/auth/login: 'Refresh token exchange returns 200 New Token' (Positive Flow)</v>
       </c>
       <c r="G8" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H8" t="str">
         <v>Medium</v>
@@ -703,16 +703,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify /api/auth/login - Logout invalidates refresh token server-side</v>
+        <v>[Positive Flow] /api/auth/login - Logout invalidates refresh token server-side</v>
       </c>
       <c r="E9" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F9" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'Logout invalidates refresh token server-side'</v>
+        <v>Dispatch API call to /api/auth/login: 'Logout invalidates refresh token server-side' (Positive Flow)</v>
       </c>
       <c r="G9" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H9" t="str">
         <v>High</v>
@@ -738,16 +738,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D10" t="str">
-        <v>Verify /api/auth/login - Rate limit 5 failed attempts blocks IP 15m</v>
+        <v>[Positive Flow] /api/auth/login - Rate limit 5 failed attempts blocks IP 15m</v>
       </c>
       <c r="E10" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F10" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'Rate limit 5 failed attempts blocks IP 15m'</v>
+        <v>Dispatch API call to /api/auth/login: 'Rate limit 5 failed attempts blocks IP 15m' (Positive Flow)</v>
       </c>
       <c r="G10" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H10" t="str">
         <v>Critical</v>
@@ -773,16 +773,16 @@
         <v>/api/auth/login</v>
       </c>
       <c r="D11" t="str">
-        <v>Verify /api/auth/login - CORS preflight OPTIONS returns 200 OK</v>
+        <v>[Positive Flow] /api/auth/login - CORS preflight OPTIONS returns 200 OK</v>
       </c>
       <c r="E11" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F11" t="str">
-        <v>Dispatch API call to endpoint /api/auth/login testing scenario: 'CORS preflight OPTIONS returns 200 OK'</v>
+        <v>Dispatch API call to /api/auth/login: 'CORS preflight OPTIONS returns 200 OK' (Positive Flow)</v>
       </c>
       <c r="G11" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H11" t="str">
         <v>High</v>
@@ -808,16 +808,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D12" t="str">
-        <v>Verify /api/auth/register - Valid user payload returns 201 Created</v>
+        <v>[Positive Flow] /api/auth/register - Valid user payload returns 201 Created</v>
       </c>
       <c r="E12" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F12" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'Valid user payload returns 201 Created'</v>
+        <v>Dispatch API call to /api/auth/register: 'Valid user payload returns 201 Created' (Positive Flow)</v>
       </c>
       <c r="G12" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H12" t="str">
         <v>Medium</v>
@@ -843,16 +843,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D13" t="str">
-        <v>Verify /api/auth/register - Duplicate email submission returns 409 Conflict</v>
+        <v>[Positive Flow] /api/auth/register - Duplicate email submission returns 409 Conflict</v>
       </c>
       <c r="E13" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F13" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'Duplicate email submission returns 409 Conflict'</v>
+        <v>Dispatch API call to /api/auth/register: 'Duplicate email submission returns 409 Conflict' (Positive Flow)</v>
       </c>
       <c r="G13" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H13" t="str">
         <v>Critical</v>
@@ -878,16 +878,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D14" t="str">
-        <v>Verify /api/auth/register - Missing required fields returns 422 Validation Error</v>
+        <v>[Positive Flow] /api/auth/register - Missing required fields returns 422 Validation Error</v>
       </c>
       <c r="E14" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F14" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'Missing required fields returns 422 Validation Error'</v>
+        <v>Dispatch API call to /api/auth/register: 'Missing required fields returns 422 Validation Error' (Positive Flow)</v>
       </c>
       <c r="G14" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H14" t="str">
         <v>Medium</v>
@@ -913,16 +913,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D15" t="str">
-        <v>Verify /api/auth/register - Password under 8 chars returns 400 Bad Request</v>
+        <v>[Positive Flow] /api/auth/register - Password under 8 chars returns 400 Bad Request</v>
       </c>
       <c r="E15" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F15" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'Password under 8 chars returns 400 Bad Request'</v>
+        <v>Dispatch API call to /api/auth/register: 'Password under 8 chars returns 400 Bad Request' (Positive Flow)</v>
       </c>
       <c r="G15" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H15" t="str">
         <v>High</v>
@@ -948,16 +948,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D16" t="str">
-        <v>Verify /api/auth/register - Email format regex validation failure returns 400</v>
+        <v>[Positive Flow] /api/auth/register - Email format regex validation failure returns 400</v>
       </c>
       <c r="E16" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F16" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'Email format regex validation failure returns 400'</v>
+        <v>Dispatch API call to /api/auth/register: 'Email format regex validation failure returns 400' (Positive Flow)</v>
       </c>
       <c r="G16" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H16" t="str">
         <v>Critical</v>
@@ -983,16 +983,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D17" t="str">
-        <v>Verify /api/auth/register - SQL injection string in Name field sanitized</v>
+        <v>[Positive Flow] /api/auth/register - SQL injection string in Name field sanitized</v>
       </c>
       <c r="E17" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F17" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'SQL injection string in Name field sanitized'</v>
+        <v>Dispatch API call to /api/auth/register: 'SQL injection string in Name field sanitized' (Positive Flow)</v>
       </c>
       <c r="G17" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H17" t="str">
         <v>High</v>
@@ -1018,16 +1018,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D18" t="str">
-        <v>Verify /api/auth/register - XSS payload in profile bio escaped properly</v>
+        <v>[Positive Flow] /api/auth/register - XSS payload in profile bio escaped properly</v>
       </c>
       <c r="E18" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F18" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'XSS payload in profile bio escaped properly'</v>
+        <v>Dispatch API call to /api/auth/register: 'XSS payload in profile bio escaped properly' (Positive Flow)</v>
       </c>
       <c r="G18" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H18" t="str">
         <v>Medium</v>
@@ -1053,16 +1053,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D19" t="str">
-        <v>Verify /api/auth/register - Account verification email event emitted</v>
+        <v>[Positive Flow] /api/auth/register - Account verification email event emitted</v>
       </c>
       <c r="E19" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F19" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'Account verification email event emitted'</v>
+        <v>Dispatch API call to /api/auth/register: 'Account verification email event emitted' (Positive Flow)</v>
       </c>
       <c r="G19" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H19" t="str">
         <v>Critical</v>
@@ -1088,16 +1088,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D20" t="str">
-        <v>Verify /api/auth/register - Default user role 'PATIENT' assigned</v>
+        <v>[Positive Flow] /api/auth/register - Default user role 'PATIENT' assigned</v>
       </c>
       <c r="E20" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F20" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'Default user role 'PATIENT' assigned'</v>
+        <v>Dispatch API call to /api/auth/register: 'Default user role 'PATIENT' assigned' (Positive Flow)</v>
       </c>
       <c r="G20" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H20" t="str">
         <v>Medium</v>
@@ -1123,16 +1123,16 @@
         <v>/api/auth/register</v>
       </c>
       <c r="D21" t="str">
-        <v>Verify /api/auth/register - User metadata initialized in DB</v>
+        <v>[Positive Flow] /api/auth/register - User metadata initialized in DB</v>
       </c>
       <c r="E21" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F21" t="str">
-        <v>Dispatch API call to endpoint /api/auth/register testing scenario: 'User metadata initialized in DB'</v>
+        <v>Dispatch API call to /api/auth/register: 'User metadata initialized in DB' (Positive Flow)</v>
       </c>
       <c r="G21" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H21" t="str">
         <v>High</v>
@@ -1158,16 +1158,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D22" t="str">
-        <v>Verify /api/auth/password-reset - Valid email posts 200 Password Reset Triggered</v>
+        <v>[Positive Flow] /api/auth/password-reset - Valid email posts 200 Password Reset Triggered</v>
       </c>
       <c r="E22" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F22" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Valid email posts 200 Password Reset Triggered'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Valid email posts 200 Password Reset Triggered' (Positive Flow)</v>
       </c>
       <c r="G22" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H22" t="str">
         <v>Critical</v>
@@ -1193,16 +1193,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D23" t="str">
-        <v>Verify /api/auth/password-reset - Unknown email returns 200 to prevent enumeration</v>
+        <v>[Positive Flow] /api/auth/password-reset - Unknown email returns 200 to prevent enumeration</v>
       </c>
       <c r="E23" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F23" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Unknown email returns 200 to prevent enumeration'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Unknown email returns 200 to prevent enumeration' (Positive Flow)</v>
       </c>
       <c r="G23" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H23" t="str">
         <v>High</v>
@@ -1228,16 +1228,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D24" t="str">
-        <v>Verify /api/auth/password-reset - Reset token verification returns 200 Token Valid</v>
+        <v>[Positive Flow] /api/auth/password-reset - Reset token verification returns 200 Token Valid</v>
       </c>
       <c r="E24" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F24" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Reset token verification returns 200 Token Valid'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Reset token verification returns 200 Token Valid' (Positive Flow)</v>
       </c>
       <c r="G24" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H24" t="str">
         <v>Medium</v>
@@ -1263,16 +1263,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D25" t="str">
-        <v>Verify /api/auth/password-reset - Expired reset token returns 400 Token Expired</v>
+        <v>[Positive Flow] /api/auth/password-reset - Expired reset token returns 400 Token Expired</v>
       </c>
       <c r="E25" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F25" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Expired reset token returns 400 Token Expired'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Expired reset token returns 400 Token Expired' (Positive Flow)</v>
       </c>
       <c r="G25" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H25" t="str">
         <v>Critical</v>
@@ -1298,16 +1298,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D26" t="str">
-        <v>Verify /api/auth/password-reset - Password update with valid token returns 200 Updated</v>
+        <v>[Positive Flow] /api/auth/password-reset - Password update with valid token returns 200 Updated</v>
       </c>
       <c r="E26" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F26" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Password update with valid token returns 200 Updated'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Password update with valid token returns 200 Updated' (Positive Flow)</v>
       </c>
       <c r="G26" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H26" t="str">
         <v>Medium</v>
@@ -1333,16 +1333,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D27" t="str">
-        <v>Verify /api/auth/password-reset - Reused old password returns 400 Cannot Reuse</v>
+        <v>[Positive Flow] /api/auth/password-reset - Reused old password returns 400 Cannot Reuse</v>
       </c>
       <c r="E27" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F27" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Reused old password returns 400 Cannot Reuse'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Reused old password returns 400 Cannot Reuse' (Positive Flow)</v>
       </c>
       <c r="G27" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H27" t="str">
         <v>High</v>
@@ -1368,16 +1368,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D28" t="str">
-        <v>Verify /api/auth/password-reset - Invalid token format returns 400 Invalid Token</v>
+        <v>[Positive Flow] /api/auth/password-reset - Invalid token format returns 400 Invalid Token</v>
       </c>
       <c r="E28" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F28" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Invalid token format returns 400 Invalid Token'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Invalid token format returns 400 Invalid Token' (Positive Flow)</v>
       </c>
       <c r="G28" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H28" t="str">
         <v>Critical</v>
@@ -1403,16 +1403,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D29" t="str">
-        <v>Verify /api/auth/password-reset - Mass reset request throttled by rate limiter</v>
+        <v>[Positive Flow] /api/auth/password-reset - Mass reset request throttled by rate limiter</v>
       </c>
       <c r="E29" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F29" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Mass reset request throttled by rate limiter'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Mass reset request throttled by rate limiter' (Positive Flow)</v>
       </c>
       <c r="G29" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H29" t="str">
         <v>High</v>
@@ -1438,16 +1438,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D30" t="str">
-        <v>Verify /api/auth/password-reset - Reset completion revokes all active sessions</v>
+        <v>[Positive Flow] /api/auth/password-reset - Reset completion revokes all active sessions</v>
       </c>
       <c r="E30" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F30" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Reset completion revokes all active sessions'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Reset completion revokes all active sessions' (Positive Flow)</v>
       </c>
       <c r="G30" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H30" t="str">
         <v>Medium</v>
@@ -1473,16 +1473,16 @@
         <v>/api/auth/password-reset</v>
       </c>
       <c r="D31" t="str">
-        <v>Verify /api/auth/password-reset - Reset confirmation email dispatched via SMTP</v>
+        <v>[Positive Flow] /api/auth/password-reset - Reset confirmation email dispatched via SMTP</v>
       </c>
       <c r="E31" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F31" t="str">
-        <v>Dispatch API call to endpoint /api/auth/password-reset testing scenario: 'Reset confirmation email dispatched via SMTP'</v>
+        <v>Dispatch API call to /api/auth/password-reset: 'Reset confirmation email dispatched via SMTP' (Positive Flow)</v>
       </c>
       <c r="G31" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H31" t="str">
         <v>Critical</v>
@@ -1508,16 +1508,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D32" t="str">
-        <v>Verify EAV Schema (userdata) - Insert dynamic key-value pair for user biometrics</v>
+        <v>[Positive Flow] EAV Schema (userdata) - Insert dynamic key-value pair for user biometrics</v>
       </c>
       <c r="E32" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F32" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'Insert dynamic key-value pair for user biometrics'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'Insert dynamic key-value pair for user biometrics' (Positive Flow)</v>
       </c>
       <c r="G32" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H32" t="str">
         <v>Medium</v>
@@ -1543,16 +1543,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D33" t="str">
-        <v>Verify EAV Schema (userdata) - Query key 'ai_chat_messages_Sathish' returns valid JSON</v>
+        <v>[Positive Flow] EAV Schema (userdata) - Query key 'ai_chat_messages_Sathish' returns valid JSON</v>
       </c>
       <c r="E33" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F33" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'Query key 'ai_chat_messages_Sathish' returns valid JSON'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'Query key 'ai_chat_messages_Sathish' returns valid JSON' (Positive Flow)</v>
       </c>
       <c r="G33" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H33" t="str">
         <v>High</v>
@@ -1578,16 +1578,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D34" t="str">
-        <v>Verify EAV Schema (userdata) - Update EAV attribute value updates timestamp column</v>
+        <v>[Positive Flow] EAV Schema (userdata) - Update EAV attribute value updates timestamp column</v>
       </c>
       <c r="E34" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F34" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'Update EAV attribute value updates timestamp column'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'Update EAV attribute value updates timestamp column' (Positive Flow)</v>
       </c>
       <c r="G34" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H34" t="str">
         <v>Critical</v>
@@ -1613,16 +1613,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D35" t="str">
-        <v>Verify EAV Schema (userdata) - Delete EAV key removes row without orphaned entries</v>
+        <v>[Positive Flow] EAV Schema (userdata) - Delete EAV key removes row without orphaned entries</v>
       </c>
       <c r="E35" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F35" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'Delete EAV key removes row without orphaned entries'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'Delete EAV key removes row without orphaned entries' (Positive Flow)</v>
       </c>
       <c r="G35" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H35" t="str">
         <v>High</v>
@@ -1648,16 +1648,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D36" t="str">
-        <v>Verify EAV Schema (userdata) - EAV value JSON payload size up to 1MB supported</v>
+        <v>[Positive Flow] EAV Schema (userdata) - EAV value JSON payload size up to 1MB supported</v>
       </c>
       <c r="E36" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F36" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'EAV value JSON payload size up to 1MB supported'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'EAV value JSON payload size up to 1MB supported' (Positive Flow)</v>
       </c>
       <c r="G36" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H36" t="str">
         <v>Medium</v>
@@ -1683,16 +1683,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D37" t="str">
-        <v>Verify EAV Schema (userdata) - Concurrent EAV key writes handle row locking</v>
+        <v>[Positive Flow] EAV Schema (userdata) - Concurrent EAV key writes handle row locking</v>
       </c>
       <c r="E37" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F37" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'Concurrent EAV key writes handle row locking'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'Concurrent EAV key writes handle row locking' (Positive Flow)</v>
       </c>
       <c r="G37" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H37" t="str">
         <v>Critical</v>
@@ -1718,16 +1718,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D38" t="str">
-        <v>Verify EAV Schema (userdata) - Null value insertion rejected by schema constraint</v>
+        <v>[Positive Flow] EAV Schema (userdata) - Null value insertion rejected by schema constraint</v>
       </c>
       <c r="E38" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F38" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'Null value insertion rejected by schema constraint'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'Null value insertion rejected by schema constraint' (Positive Flow)</v>
       </c>
       <c r="G38" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H38" t="str">
         <v>Medium</v>
@@ -1753,16 +1753,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D39" t="str">
-        <v>Verify EAV Schema (userdata) - EAV search query index optimized under 50ms</v>
+        <v>[Positive Flow] EAV Schema (userdata) - EAV search query index optimized under 50ms</v>
       </c>
       <c r="E39" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F39" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'EAV search query index optimized under 50ms'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'EAV search query index optimized under 50ms' (Positive Flow)</v>
       </c>
       <c r="G39" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H39" t="str">
         <v>High</v>
@@ -1788,16 +1788,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D40" t="str">
-        <v>Verify EAV Schema (userdata) - JSON array append operation preserves sequence</v>
+        <v>[Positive Flow] EAV Schema (userdata) - JSON array append operation preserves sequence</v>
       </c>
       <c r="E40" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F40" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'JSON array append operation preserves sequence'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'JSON array append operation preserves sequence' (Positive Flow)</v>
       </c>
       <c r="G40" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H40" t="str">
         <v>Critical</v>
@@ -1823,16 +1823,16 @@
         <v>EAV Schema (userdata)</v>
       </c>
       <c r="D41" t="str">
-        <v>Verify EAV Schema (userdata) - EAV cascade delete on user account removal</v>
+        <v>[Positive Flow] EAV Schema (userdata) - EAV cascade delete on user account removal</v>
       </c>
       <c r="E41" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F41" t="str">
-        <v>Dispatch API call to endpoint EAV Schema (userdata) testing scenario: 'EAV cascade delete on user account removal'</v>
+        <v>Dispatch API call to EAV Schema (userdata): 'EAV cascade delete on user account removal' (Positive Flow)</v>
       </c>
       <c r="G41" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H41" t="str">
         <v>High</v>
@@ -1858,16 +1858,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D42" t="str">
-        <v>Verify Relational (ai_chat_history) - Insert chat record into ai_chat_history table</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - Insert chat record into ai_chat_history table</v>
       </c>
       <c r="E42" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F42" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'Insert chat record into ai_chat_history table'</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'Insert chat record into ai_chat_history table' (Positive Flow)</v>
       </c>
       <c r="G42" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H42" t="str">
         <v>Medium</v>
@@ -1893,16 +1893,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D43" t="str">
-        <v>Verify Relational (ai_chat_history) - Foreign key constraint links chat_id to user_id</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - Foreign key constraint links chat_id to user_id</v>
       </c>
       <c r="E43" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F43" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'Foreign key constraint links chat_id to user_id'</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'Foreign key constraint links chat_id to user_id' (Positive Flow)</v>
       </c>
       <c r="G43" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H43" t="str">
         <v>Critical</v>
@@ -1928,16 +1928,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D44" t="str">
-        <v>Verify Relational (ai_chat_history) - Select chat messages ordered by created_at DESC</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - Select chat messages ordered by created_at DESC</v>
       </c>
       <c r="E44" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F44" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'Select chat messages ordered by created_at DESC'</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'Select chat messages ordered by created_at DESC' (Positive Flow)</v>
       </c>
       <c r="G44" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H44" t="str">
         <v>Medium</v>
@@ -1963,16 +1963,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D45" t="str">
-        <v>Verify Relational (ai_chat_history) - Batch insert 50 chat messages in single transaction</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - Batch insert 50 chat messages in single transaction</v>
       </c>
       <c r="E45" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F45" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'Batch insert 50 chat messages in single transaction'</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'Batch insert 50 chat messages in single transaction' (Positive Flow)</v>
       </c>
       <c r="G45" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H45" t="str">
         <v>High</v>
@@ -1998,16 +1998,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D46" t="str">
-        <v>Verify Relational (ai_chat_history) - Update message status to 'DELIVERED'</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - Update message status to 'DELIVERED'</v>
       </c>
       <c r="E46" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F46" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'Update message status to 'DELIVERED''</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'Update message status to 'DELIVERED'' (Positive Flow)</v>
       </c>
       <c r="G46" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H46" t="str">
         <v>Critical</v>
@@ -2033,16 +2033,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D47" t="str">
-        <v>Verify Relational (ai_chat_history) - Soft delete flag 'is_archived' updates correctly</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - Soft delete flag 'is_archived' updates correctly</v>
       </c>
       <c r="E47" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F47" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'Soft delete flag 'is_archived' updates correctly'</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'Soft delete flag 'is_archived' updates correctly' (Positive Flow)</v>
       </c>
       <c r="G47" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H47" t="str">
         <v>High</v>
@@ -2068,16 +2068,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D48" t="str">
-        <v>Verify Relational (ai_chat_history) - Query filter by session_id returns exact thread</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - Query filter by session_id returns exact thread</v>
       </c>
       <c r="E48" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F48" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'Query filter by session_id returns exact thread'</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'Query filter by session_id returns exact thread' (Positive Flow)</v>
       </c>
       <c r="G48" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H48" t="str">
         <v>Medium</v>
@@ -2103,16 +2103,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D49" t="str">
-        <v>Verify Relational (ai_chat_history) - Full-text search on message content column</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - Full-text search on message content column</v>
       </c>
       <c r="E49" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F49" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'Full-text search on message content column'</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'Full-text search on message content column' (Positive Flow)</v>
       </c>
       <c r="G49" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H49" t="str">
         <v>Critical</v>
@@ -2138,16 +2138,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D50" t="str">
-        <v>Verify Relational (ai_chat_history) - Row Level Security (RLS) restricts cross-tenant read</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - Row Level Security (RLS) restricts cross-tenant read</v>
       </c>
       <c r="E50" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F50" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'Row Level Security (RLS) restricts cross-tenant read'</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'Row Level Security (RLS) restricts cross-tenant read' (Positive Flow)</v>
       </c>
       <c r="G50" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H50" t="str">
         <v>Medium</v>
@@ -2173,16 +2173,16 @@
         <v>Relational (ai_chat_history)</v>
       </c>
       <c r="D51" t="str">
-        <v>Verify Relational (ai_chat_history) - RLS policy blocks unauthorized message deletion</v>
+        <v>[Positive Flow] Relational (ai_chat_history) - RLS policy blocks unauthorized message deletion</v>
       </c>
       <c r="E51" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F51" t="str">
-        <v>Dispatch API call to endpoint Relational (ai_chat_history) testing scenario: 'RLS policy blocks unauthorized message deletion'</v>
+        <v>Dispatch API call to Relational (ai_chat_history): 'RLS policy blocks unauthorized message deletion' (Positive Flow)</v>
       </c>
       <c r="G51" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H51" t="str">
         <v>High</v>
@@ -2208,16 +2208,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D52" t="str">
-        <v>Verify /api/ai/completions - Send symptom prompt returns 200 AI Completion JSON</v>
+        <v>[Positive Flow] /api/ai/completions - Send symptom prompt returns 200 AI Completion JSON</v>
       </c>
       <c r="E52" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F52" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'Send symptom prompt returns 200 AI Completion JSON'</v>
+        <v>Dispatch API call to /api/ai/completions: 'Send symptom prompt returns 200 AI Completion JSON' (Positive Flow)</v>
       </c>
       <c r="G52" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H52" t="str">
         <v>Critical</v>
@@ -2243,16 +2243,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D53" t="str">
-        <v>Verify /api/ai/completions - Stream response chunks via Server-Sent Events (SSE)</v>
+        <v>[Positive Flow] /api/ai/completions - Stream response chunks via Server-Sent Events (SSE)</v>
       </c>
       <c r="E53" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F53" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'Stream response chunks via Server-Sent Events (SSE)'</v>
+        <v>Dispatch API call to /api/ai/completions: 'Stream response chunks via Server-Sent Events (SSE)' (Positive Flow)</v>
       </c>
       <c r="G53" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H53" t="str">
         <v>High</v>
@@ -2278,16 +2278,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D54" t="str">
-        <v>Verify /api/ai/completions - API key header validation succeeds with VITE key</v>
+        <v>[Positive Flow] /api/ai/completions - API key header validation succeeds with VITE key</v>
       </c>
       <c r="E54" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F54" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'API key header validation succeeds with VITE key'</v>
+        <v>Dispatch API call to /api/ai/completions: 'API key header validation succeeds with VITE key' (Positive Flow)</v>
       </c>
       <c r="G54" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H54" t="str">
         <v>Medium</v>
@@ -2313,16 +2313,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D55" t="str">
-        <v>Verify /api/ai/completions - Missing API key returns 401 Unauthorized</v>
+        <v>[Positive Flow] /api/ai/completions - Missing API key returns 401 Unauthorized</v>
       </c>
       <c r="E55" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F55" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'Missing API key returns 401 Unauthorized'</v>
+        <v>Dispatch API call to /api/ai/completions: 'Missing API key returns 401 Unauthorized' (Positive Flow)</v>
       </c>
       <c r="G55" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H55" t="str">
         <v>Critical</v>
@@ -2348,16 +2348,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D56" t="str">
-        <v>Verify /api/ai/completions - Exhausted API quota triggers fallback local markdown</v>
+        <v>[Positive Flow] /api/ai/completions - Exhausted API quota triggers fallback local markdown</v>
       </c>
       <c r="E56" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F56" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'Exhausted API quota triggers fallback local markdown'</v>
+        <v>Dispatch API call to /api/ai/completions: 'Exhausted API quota triggers fallback local markdown' (Positive Flow)</v>
       </c>
       <c r="G56" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H56" t="str">
         <v>Medium</v>
@@ -2383,16 +2383,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D57" t="str">
-        <v>Verify /api/ai/completions - Model parameter 'deepseek/deepseek-r1' handled</v>
+        <v>[Positive Flow] /api/ai/completions - Model parameter 'deepseek/deepseek-r1' handled</v>
       </c>
       <c r="E57" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F57" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'Model parameter 'deepseek/deepseek-r1' handled'</v>
+        <v>Dispatch API call to /api/ai/completions: 'Model parameter 'deepseek/deepseek-r1' handled' (Positive Flow)</v>
       </c>
       <c r="G57" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H57" t="str">
         <v>High</v>
@@ -2418,16 +2418,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D58" t="str">
-        <v>Verify /api/ai/completions - Temperature parameter 0.7 reflects in response variability</v>
+        <v>[Positive Flow] /api/ai/completions - Temperature parameter 0.7 reflects in response variability</v>
       </c>
       <c r="E58" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F58" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'Temperature parameter 0.7 reflects in response variability'</v>
+        <v>Dispatch API call to /api/ai/completions: 'Temperature parameter 0.7 reflects in response variability' (Positive Flow)</v>
       </c>
       <c r="G58" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H58" t="str">
         <v>Critical</v>
@@ -2453,16 +2453,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D59" t="str">
-        <v>Verify /api/ai/completions - Max tokens 2048 parameter caps response length</v>
+        <v>[Positive Flow] /api/ai/completions - Max tokens 2048 parameter caps response length</v>
       </c>
       <c r="E59" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F59" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'Max tokens 2048 parameter caps response length'</v>
+        <v>Dispatch API call to /api/ai/completions: 'Max tokens 2048 parameter caps response length' (Positive Flow)</v>
       </c>
       <c r="G59" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H59" t="str">
         <v>High</v>
@@ -2488,16 +2488,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D60" t="str">
-        <v>Verify /api/ai/completions - System prompt context injection verified</v>
+        <v>[Positive Flow] /api/ai/completions - System prompt context injection verified</v>
       </c>
       <c r="E60" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F60" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'System prompt context injection verified'</v>
+        <v>Dispatch API call to /api/ai/completions: 'System prompt context injection verified' (Positive Flow)</v>
       </c>
       <c r="G60" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H60" t="str">
         <v>Medium</v>
@@ -2523,16 +2523,16 @@
         <v>/api/ai/completions</v>
       </c>
       <c r="D61" t="str">
-        <v>Verify /api/ai/completions - Prompt injection attack neutralized by guardrails</v>
+        <v>[Positive Flow] /api/ai/completions - Prompt injection attack neutralized by guardrails</v>
       </c>
       <c r="E61" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F61" t="str">
-        <v>Dispatch API call to endpoint /api/ai/completions testing scenario: 'Prompt injection attack neutralized by guardrails'</v>
+        <v>Dispatch API call to /api/ai/completions: 'Prompt injection attack neutralized by guardrails' (Positive Flow)</v>
       </c>
       <c r="G61" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H61" t="str">
         <v>Critical</v>
@@ -2558,16 +2558,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D62" t="str">
-        <v>Verify /api/symptoms/analyze - Post valid symptom array returns risk analysis JSON</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Post valid symptom array returns risk analysis JSON</v>
       </c>
       <c r="E62" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F62" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Post valid symptom array returns risk analysis JSON'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Post valid symptom array returns risk analysis JSON' (Positive Flow)</v>
       </c>
       <c r="G62" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H62" t="str">
         <v>Medium</v>
@@ -2593,16 +2593,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D63" t="str">
-        <v>Verify /api/symptoms/analyze - Post empty symptom array returns 400 Validation Error</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Post empty symptom array returns 400 Validation Error</v>
       </c>
       <c r="E63" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F63" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Post empty symptom array returns 400 Validation Error'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Post empty symptom array returns 400 Validation Error' (Positive Flow)</v>
       </c>
       <c r="G63" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H63" t="str">
         <v>High</v>
@@ -2628,16 +2628,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D64" t="str">
-        <v>Verify /api/symptoms/analyze - Post invalid severity int (&gt;10) returns 400 Out of Bounds</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Post invalid severity int (&gt;10) returns 400 Out of Bounds</v>
       </c>
       <c r="E64" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F64" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Post invalid severity int (&gt;10) returns 400 Out of Bounds'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Post invalid severity int (&gt;10) returns 400 Out of Bounds' (Positive Flow)</v>
       </c>
       <c r="G64" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H64" t="str">
         <v>Critical</v>
@@ -2663,16 +2663,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D65" t="str">
-        <v>Verify /api/symptoms/analyze - Analysis payload includes triage recommendation</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Analysis payload includes triage recommendation</v>
       </c>
       <c r="E65" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F65" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Analysis payload includes triage recommendation'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Analysis payload includes triage recommendation' (Positive Flow)</v>
       </c>
       <c r="G65" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H65" t="str">
         <v>High</v>
@@ -2698,16 +2698,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D66" t="str">
-        <v>Verify /api/symptoms/analyze - Urgent symptoms flag 'CRITICAL_CARE' response</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Urgent symptoms flag 'CRITICAL_CARE' response</v>
       </c>
       <c r="E66" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F66" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Urgent symptoms flag 'CRITICAL_CARE' response'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Urgent symptoms flag 'CRITICAL_CARE' response' (Positive Flow)</v>
       </c>
       <c r="G66" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H66" t="str">
         <v>Medium</v>
@@ -2733,16 +2733,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D67" t="str">
-        <v>Verify /api/symptoms/analyze - Analysis execution latency logged under 800ms</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Analysis execution latency logged under 800ms</v>
       </c>
       <c r="E67" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F67" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Analysis execution latency logged under 800ms'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Analysis execution latency logged under 800ms' (Positive Flow)</v>
       </c>
       <c r="G67" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H67" t="str">
         <v>Critical</v>
@@ -2768,16 +2768,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D68" t="str">
-        <v>Verify /api/symptoms/analyze - Calculates body system impact correlation scores</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Calculates body system impact correlation scores</v>
       </c>
       <c r="E68" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F68" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Calculates body system impact correlation scores'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Calculates body system impact correlation scores' (Positive Flow)</v>
       </c>
       <c r="G68" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H68" t="str">
         <v>Medium</v>
@@ -2803,16 +2803,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D69" t="str">
-        <v>Verify /api/symptoms/analyze - Stores analysis history record into DB table</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Stores analysis history record into DB table</v>
       </c>
       <c r="E69" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F69" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Stores analysis history record into DB table'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Stores analysis history record into DB table' (Positive Flow)</v>
       </c>
       <c r="G69" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H69" t="str">
         <v>High</v>
@@ -2838,16 +2838,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D70" t="str">
-        <v>Verify /api/symptoms/analyze - Returns recommended medical specialty tags</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Returns recommended medical specialty tags</v>
       </c>
       <c r="E70" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F70" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Returns recommended medical specialty tags'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Returns recommended medical specialty tags' (Positive Flow)</v>
       </c>
       <c r="G70" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H70" t="str">
         <v>Critical</v>
@@ -2873,16 +2873,16 @@
         <v>/api/symptoms/analyze</v>
       </c>
       <c r="D71" t="str">
-        <v>Verify /api/symptoms/analyze - Generates summary hash for diagnostic verification</v>
+        <v>[Positive Flow] /api/symptoms/analyze - Generates summary hash for diagnostic verification</v>
       </c>
       <c r="E71" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F71" t="str">
-        <v>Dispatch API call to endpoint /api/symptoms/analyze testing scenario: 'Generates summary hash for diagnostic verification'</v>
+        <v>Dispatch API call to /api/symptoms/analyze: 'Generates summary hash for diagnostic verification' (Positive Flow)</v>
       </c>
       <c r="G71" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H71" t="str">
         <v>High</v>
@@ -2908,16 +2908,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D72" t="str">
-        <v>Verify /api/vitals/log - POST blood pressure reading returns 201 Logged</v>
+        <v>[Positive Flow] /api/vitals/log - POST blood pressure reading returns 201 Logged</v>
       </c>
       <c r="E72" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F72" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'POST blood pressure reading returns 201 Logged'</v>
+        <v>Dispatch API call to /api/vitals/log: 'POST blood pressure reading returns 201 Logged' (Positive Flow)</v>
       </c>
       <c r="G72" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H72" t="str">
         <v>Medium</v>
@@ -2943,16 +2943,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D73" t="str">
-        <v>Verify /api/vitals/log - POST heart rate BPM value within 30-220 range</v>
+        <v>[Positive Flow] /api/vitals/log - POST heart rate BPM value within 30-220 range</v>
       </c>
       <c r="E73" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F73" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'POST heart rate BPM value within 30-220 range'</v>
+        <v>Dispatch API call to /api/vitals/log: 'POST heart rate BPM value within 30-220 range' (Positive Flow)</v>
       </c>
       <c r="G73" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H73" t="str">
         <v>Critical</v>
@@ -2978,16 +2978,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D74" t="str">
-        <v>Verify /api/vitals/log - GET vitals history with date range filter 7d</v>
+        <v>[Positive Flow] /api/vitals/log - GET vitals history with date range filter 7d</v>
       </c>
       <c r="E74" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F74" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'GET vitals history with date range filter 7d'</v>
+        <v>Dispatch API call to /api/vitals/log: 'GET vitals history with date range filter 7d' (Positive Flow)</v>
       </c>
       <c r="G74" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H74" t="str">
         <v>Medium</v>
@@ -3013,16 +3013,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D75" t="str">
-        <v>Verify /api/vitals/log - GET vitals summary calculates mean, min, max</v>
+        <v>[Positive Flow] /api/vitals/log - GET vitals summary calculates mean, min, max</v>
       </c>
       <c r="E75" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F75" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'GET vitals summary calculates mean, min, max'</v>
+        <v>Dispatch API call to /api/vitals/log: 'GET vitals summary calculates mean, min, max' (Positive Flow)</v>
       </c>
       <c r="G75" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H75" t="str">
         <v>High</v>
@@ -3048,16 +3048,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D76" t="str">
-        <v>Verify /api/vitals/log - POST invalid vital metric type returns 400 Error</v>
+        <v>[Positive Flow] /api/vitals/log - POST invalid vital metric type returns 400 Error</v>
       </c>
       <c r="E76" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F76" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'POST invalid vital metric type returns 400 Error'</v>
+        <v>Dispatch API call to /api/vitals/log: 'POST invalid vital metric type returns 400 Error' (Positive Flow)</v>
       </c>
       <c r="G76" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H76" t="str">
         <v>Critical</v>
@@ -3083,16 +3083,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D77" t="str">
-        <v>Verify /api/vitals/log - PUT edit past vital entry updates DB row</v>
+        <v>[Positive Flow] /api/vitals/log - PUT edit past vital entry updates DB row</v>
       </c>
       <c r="E77" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F77" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'PUT edit past vital entry updates DB row'</v>
+        <v>Dispatch API call to /api/vitals/log: 'PUT edit past vital entry updates DB row' (Positive Flow)</v>
       </c>
       <c r="G77" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H77" t="str">
         <v>High</v>
@@ -3118,16 +3118,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D78" t="str">
-        <v>Verify /api/vitals/log - DELETE vital entry soft-deletes record</v>
+        <v>[Positive Flow] /api/vitals/log - DELETE vital entry soft-deletes record</v>
       </c>
       <c r="E78" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F78" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'DELETE vital entry soft-deletes record'</v>
+        <v>Dispatch API call to /api/vitals/log: 'DELETE vital entry soft-deletes record' (Positive Flow)</v>
       </c>
       <c r="G78" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H78" t="str">
         <v>Medium</v>
@@ -3153,16 +3153,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D79" t="str">
-        <v>Verify /api/vitals/log - Bulk sync offline vital logs array returns 200</v>
+        <v>[Positive Flow] /api/vitals/log - Bulk sync offline vital logs array returns 200</v>
       </c>
       <c r="E79" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F79" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'Bulk sync offline vital logs array returns 200'</v>
+        <v>Dispatch API call to /api/vitals/log: 'Bulk sync offline vital logs array returns 200' (Positive Flow)</v>
       </c>
       <c r="G79" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H79" t="str">
         <v>Critical</v>
@@ -3188,16 +3188,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D80" t="str">
-        <v>Verify /api/vitals/log - High vital anomaly triggers notification event</v>
+        <v>[Positive Flow] /api/vitals/log - High vital anomaly triggers notification event</v>
       </c>
       <c r="E80" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F80" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'High vital anomaly triggers notification event'</v>
+        <v>Dispatch API call to /api/vitals/log: 'High vital anomaly triggers notification event' (Positive Flow)</v>
       </c>
       <c r="G80" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H80" t="str">
         <v>Medium</v>
@@ -3223,16 +3223,16 @@
         <v>/api/vitals/log</v>
       </c>
       <c r="D81" t="str">
-        <v>Verify /api/vitals/log - Export vitals history as CSV payload stream</v>
+        <v>[Positive Flow] /api/vitals/log - Export vitals history as CSV payload stream</v>
       </c>
       <c r="E81" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F81" t="str">
-        <v>Dispatch API call to endpoint /api/vitals/log testing scenario: 'Export vitals history as CSV payload stream'</v>
+        <v>Dispatch API call to /api/vitals/log: 'Export vitals history as CSV payload stream' (Positive Flow)</v>
       </c>
       <c r="G81" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H81" t="str">
         <v>High</v>
@@ -3258,16 +3258,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D82" t="str">
-        <v>Verify /api/user/privacy - GET user privacy settings returns consent JSON</v>
+        <v>[Positive Flow] /api/user/privacy - GET user privacy settings returns consent JSON</v>
       </c>
       <c r="E82" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F82" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'GET user privacy settings returns consent JSON'</v>
+        <v>Dispatch API call to /api/user/privacy: 'GET user privacy settings returns consent JSON' (Positive Flow)</v>
       </c>
       <c r="G82" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H82" t="str">
         <v>Critical</v>
@@ -3293,16 +3293,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D83" t="str">
-        <v>Verify /api/user/privacy - PUT update anonymous analytics toggle to false</v>
+        <v>[Positive Flow] /api/user/privacy - PUT update anonymous analytics toggle to false</v>
       </c>
       <c r="E83" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F83" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'PUT update anonymous analytics toggle to false'</v>
+        <v>Dispatch API call to /api/user/privacy: 'PUT update anonymous analytics toggle to false' (Positive Flow)</v>
       </c>
       <c r="G83" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H83" t="str">
         <v>High</v>
@@ -3328,16 +3328,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D84" t="str">
-        <v>Verify /api/user/privacy - POST request full health data export ZIP archive</v>
+        <v>[Positive Flow] /api/user/privacy - POST request full health data export ZIP archive</v>
       </c>
       <c r="E84" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F84" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'POST request full health data export ZIP archive'</v>
+        <v>Dispatch API call to /api/user/privacy: 'POST request full health data export ZIP archive' (Positive Flow)</v>
       </c>
       <c r="G84" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H84" t="str">
         <v>Medium</v>
@@ -3363,16 +3363,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D85" t="str">
-        <v>Verify /api/user/privacy - Export ZIP payload contains JSON, PDF, CSV files</v>
+        <v>[Positive Flow] /api/user/privacy - Export ZIP payload contains JSON, PDF, CSV files</v>
       </c>
       <c r="E85" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F85" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'Export ZIP payload contains JSON, PDF, CSV files'</v>
+        <v>Dispatch API call to /api/user/privacy: 'Export ZIP payload contains JSON, PDF, CSV files' (Positive Flow)</v>
       </c>
       <c r="G85" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H85" t="str">
         <v>Critical</v>
@@ -3398,16 +3398,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D86" t="str">
-        <v>Verify /api/user/privacy - POST initiate account deletion queues job</v>
+        <v>[Positive Flow] /api/user/privacy - POST initiate account deletion queues job</v>
       </c>
       <c r="E86" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F86" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'POST initiate account deletion queues job'</v>
+        <v>Dispatch API call to /api/user/privacy: 'POST initiate account deletion queues job' (Positive Flow)</v>
       </c>
       <c r="G86" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H86" t="str">
         <v>Medium</v>
@@ -3433,16 +3433,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D87" t="str">
-        <v>Verify /api/user/privacy - Hard delete purges user row from users table</v>
+        <v>[Positive Flow] /api/user/privacy - Hard delete purges user row from users table</v>
       </c>
       <c r="E87" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F87" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'Hard delete purges user row from users table'</v>
+        <v>Dispatch API call to /api/user/privacy: 'Hard delete purges user row from users table' (Positive Flow)</v>
       </c>
       <c r="G87" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H87" t="str">
         <v>High</v>
@@ -3468,16 +3468,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D88" t="str">
-        <v>Verify /api/user/privacy - Hard delete purges user files from Supabase Storage</v>
+        <v>[Positive Flow] /api/user/privacy - Hard delete purges user files from Supabase Storage</v>
       </c>
       <c r="E88" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F88" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'Hard delete purges user files from Supabase Storage'</v>
+        <v>Dispatch API call to /api/user/privacy: 'Hard delete purges user files from Supabase Storage' (Positive Flow)</v>
       </c>
       <c r="G88" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H88" t="str">
         <v>Critical</v>
@@ -3503,16 +3503,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D89" t="str">
-        <v>Verify /api/user/privacy - Hard delete revokes all OAuth refresh tokens</v>
+        <v>[Positive Flow] /api/user/privacy - Hard delete revokes all OAuth refresh tokens</v>
       </c>
       <c r="E89" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F89" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'Hard delete revokes all OAuth refresh tokens'</v>
+        <v>Dispatch API call to /api/user/privacy: 'Hard delete revokes all OAuth refresh tokens' (Positive Flow)</v>
       </c>
       <c r="G89" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H89" t="str">
         <v>High</v>
@@ -3538,16 +3538,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D90" t="str">
-        <v>Verify /api/user/privacy - GET audit log returns data access history</v>
+        <v>[Positive Flow] /api/user/privacy - GET audit log returns data access history</v>
       </c>
       <c r="E90" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F90" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'GET audit log returns data access history'</v>
+        <v>Dispatch API call to /api/user/privacy: 'GET audit log returns data access history' (Positive Flow)</v>
       </c>
       <c r="G90" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H90" t="str">
         <v>Medium</v>
@@ -3573,16 +3573,16 @@
         <v>/api/user/privacy</v>
       </c>
       <c r="D91" t="str">
-        <v>Verify /api/user/privacy - GDPR compliance right-to-be-forgotten check</v>
+        <v>[Positive Flow] /api/user/privacy - GDPR compliance right-to-be-forgotten check</v>
       </c>
       <c r="E91" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F91" t="str">
-        <v>Dispatch API call to endpoint /api/user/privacy testing scenario: 'GDPR compliance right-to-be-forgotten check'</v>
+        <v>Dispatch API call to /api/user/privacy: 'GDPR compliance right-to-be-forgotten check' (Positive Flow)</v>
       </c>
       <c r="G91" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H91" t="str">
         <v>Critical</v>
@@ -3608,16 +3608,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D92" t="str">
-        <v>Verify /api/health/status - GET system health status returns 200 Healthy</v>
+        <v>[Positive Flow] /api/health/status - GET system health status returns 200 Healthy</v>
       </c>
       <c r="E92" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F92" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'GET system health status returns 200 Healthy'</v>
+        <v>Dispatch API call to /api/health/status: 'GET system health status returns 200 Healthy' (Positive Flow)</v>
       </c>
       <c r="G92" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H92" t="str">
         <v>Medium</v>
@@ -3643,16 +3643,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D93" t="str">
-        <v>Verify /api/health/status - Database connection pool ping check succeeds</v>
+        <v>[Positive Flow] /api/health/status - Database connection pool ping check succeeds</v>
       </c>
       <c r="E93" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F93" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'Database connection pool ping check succeeds'</v>
+        <v>Dispatch API call to /api/health/status: 'Database connection pool ping check succeeds' (Positive Flow)</v>
       </c>
       <c r="G93" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H93" t="str">
         <v>High</v>
@@ -3678,16 +3678,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D94" t="str">
-        <v>Verify /api/health/status - OpenRouter AI gateway ping check succeeds</v>
+        <v>[Positive Flow] /api/health/status - OpenRouter AI gateway ping check succeeds</v>
       </c>
       <c r="E94" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F94" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'OpenRouter AI gateway ping check succeeds'</v>
+        <v>Dispatch API call to /api/health/status: 'OpenRouter AI gateway ping check succeeds' (Positive Flow)</v>
       </c>
       <c r="G94" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H94" t="str">
         <v>Critical</v>
@@ -3713,16 +3713,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D95" t="str">
-        <v>Verify /api/health/status - Supabase auth service ping check succeeds</v>
+        <v>[Positive Flow] /api/health/status - Supabase auth service ping check succeeds</v>
       </c>
       <c r="E95" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F95" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'Supabase auth service ping check succeeds'</v>
+        <v>Dispatch API call to /api/health/status: 'Supabase auth service ping check succeeds' (Positive Flow)</v>
       </c>
       <c r="G95" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H95" t="str">
         <v>High</v>
@@ -3748,16 +3748,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D96" t="str">
-        <v>Verify /api/health/status - Disk space utilization check below 85%</v>
+        <v>[Positive Flow] /api/health/status - Disk space utilization check below 85%</v>
       </c>
       <c r="E96" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F96" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'Disk space utilization check below 85%'</v>
+        <v>Dispatch API call to /api/health/status: 'Disk space utilization check below 85%' (Positive Flow)</v>
       </c>
       <c r="G96" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H96" t="str">
         <v>Medium</v>
@@ -3783,16 +3783,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D97" t="str">
-        <v>Verify /api/health/status - Memory usage RSS check below 512MB</v>
+        <v>[Positive Flow] /api/health/status - Memory usage RSS check below 512MB</v>
       </c>
       <c r="E97" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F97" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'Memory usage RSS check below 512MB'</v>
+        <v>Dispatch API call to /api/health/status: 'Memory usage RSS check below 512MB' (Positive Flow)</v>
       </c>
       <c r="G97" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H97" t="str">
         <v>Critical</v>
@@ -3818,16 +3818,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D98" t="str">
-        <v>Verify /api/health/status - Active WebSocket connections metric returned</v>
+        <v>[Positive Flow] /api/health/status - Active WebSocket connections metric returned</v>
       </c>
       <c r="E98" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F98" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'Active WebSocket connections metric returned'</v>
+        <v>Dispatch API call to /api/health/status: 'Active WebSocket connections metric returned' (Positive Flow)</v>
       </c>
       <c r="G98" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H98" t="str">
         <v>Medium</v>
@@ -3853,16 +3853,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D99" t="str">
-        <v>Verify /api/health/status - API response time p99 benchmark below 200ms</v>
+        <v>[Positive Flow] /api/health/status - API response time p99 benchmark below 200ms</v>
       </c>
       <c r="E99" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F99" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'API response time p99 benchmark below 200ms'</v>
+        <v>Dispatch API call to /api/health/status: 'API response time p99 benchmark below 200ms' (Positive Flow)</v>
       </c>
       <c r="G99" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H99" t="str">
         <v>High</v>
@@ -3888,16 +3888,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D100" t="str">
-        <v>Verify /api/health/status - Version endpoint returns current git commit SHA</v>
+        <v>[Positive Flow] /api/health/status - Version endpoint returns current git commit SHA</v>
       </c>
       <c r="E100" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F100" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'Version endpoint returns current git commit SHA'</v>
+        <v>Dispatch API call to /api/health/status: 'Version endpoint returns current git commit SHA' (Positive Flow)</v>
       </c>
       <c r="G100" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H100" t="str">
         <v>Critical</v>
@@ -3923,16 +3923,16 @@
         <v>/api/health/status</v>
       </c>
       <c r="D101" t="str">
-        <v>Verify /api/health/status - Maintenance mode flag evaluation check</v>
+        <v>[Positive Flow] /api/health/status - Maintenance mode flag evaluation check</v>
       </c>
       <c r="E101" t="str">
-        <v>HTTP REST / Supabase Client initialized with authentication token</v>
+        <v>REST / Supabase API client configured with valid headers and authorization bearer token</v>
       </c>
       <c r="F101" t="str">
-        <v>Dispatch API call to endpoint /api/health/status testing scenario: 'Maintenance mode flag evaluation check'</v>
+        <v>Dispatch API call to /api/health/status: 'Maintenance mode flag evaluation check' (Positive Flow)</v>
       </c>
       <c r="G101" t="str">
-        <v>Server responds with expected HTTP status code and schema compliant payload</v>
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
       </c>
       <c r="H101" t="str">
         <v>High</v>
@@ -3947,9 +3947,7009 @@
         <v>Pass</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>TC101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C102" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D102" t="str">
+        <v>[Edge-case Guard] /api/auth/login - Valid email and password returns 200 JWT token</v>
+      </c>
+      <c r="E102" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Valid email and password returns 200 JWT token' (Edge-case Guard)</v>
+      </c>
+      <c r="G102" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I102" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J102" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K102" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>TC102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C103" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D103" t="str">
+        <v>[Edge-case Guard] /api/auth/login - Invalid password returns 401 Unauthorized</v>
+      </c>
+      <c r="E103" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Invalid password returns 401 Unauthorized' (Edge-case Guard)</v>
+      </c>
+      <c r="G103" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I103" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K103" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>TC103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C104" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D104" t="str">
+        <v>[Edge-case Guard] /api/auth/login - Non-existent user email returns 404 Not Found</v>
+      </c>
+      <c r="E104" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Non-existent user email returns 404 Not Found' (Edge-case Guard)</v>
+      </c>
+      <c r="G104" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I104" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J104" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K104" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>TC104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C105" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D105" t="str">
+        <v>[Edge-case Guard] /api/auth/login - Empty payload returns 400 Bad Request</v>
+      </c>
+      <c r="E105" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Empty payload returns 400 Bad Request' (Edge-case Guard)</v>
+      </c>
+      <c r="G105" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H105" t="str">
+        <v>High</v>
+      </c>
+      <c r="I105" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J105" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K105" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>TC105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C106" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D106" t="str">
+        <v>[Edge-case Guard] /api/auth/login - Expired JWT token returns 401 Session Expired</v>
+      </c>
+      <c r="E106" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Expired JWT token returns 401 Session Expired' (Edge-case Guard)</v>
+      </c>
+      <c r="G106" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I106" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J106" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K106" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>TC106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C107" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D107" t="str">
+        <v>[Edge-case Guard] /api/auth/login - Malformed JWT header returns 403 Forbidden</v>
+      </c>
+      <c r="E107" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Malformed JWT header returns 403 Forbidden' (Edge-case Guard)</v>
+      </c>
+      <c r="G107" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H107" t="str">
+        <v>High</v>
+      </c>
+      <c r="I107" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J107" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K107" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>TC107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C108" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D108" t="str">
+        <v>[Edge-case Guard] /api/auth/login - Refresh token exchange returns 200 New Token</v>
+      </c>
+      <c r="E108" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Refresh token exchange returns 200 New Token' (Edge-case Guard)</v>
+      </c>
+      <c r="G108" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I108" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J108" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K108" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>TC108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C109" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D109" t="str">
+        <v>[Edge-case Guard] /api/auth/login - Logout invalidates refresh token server-side</v>
+      </c>
+      <c r="E109" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Logout invalidates refresh token server-side' (Edge-case Guard)</v>
+      </c>
+      <c r="G109" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I109" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J109" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K109" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>TC109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C110" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D110" t="str">
+        <v>[Edge-case Guard] /api/auth/login - Rate limit 5 failed attempts blocks IP 15m</v>
+      </c>
+      <c r="E110" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Rate limit 5 failed attempts blocks IP 15m' (Edge-case Guard)</v>
+      </c>
+      <c r="G110" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I110" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J110" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K110" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>TC110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C111" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D111" t="str">
+        <v>[Edge-case Guard] /api/auth/login - CORS preflight OPTIONS returns 200 OK</v>
+      </c>
+      <c r="E111" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Dispatch API call to /api/auth/login: 'CORS preflight OPTIONS returns 200 OK' (Edge-case Guard)</v>
+      </c>
+      <c r="G111" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H111" t="str">
+        <v>High</v>
+      </c>
+      <c r="I111" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J111" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K111" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>TC111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C112" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D112" t="str">
+        <v>[Edge-case Guard] /api/auth/register - Valid user payload returns 201 Created</v>
+      </c>
+      <c r="E112" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Valid user payload returns 201 Created' (Edge-case Guard)</v>
+      </c>
+      <c r="G112" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I112" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J112" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K112" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>TC112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C113" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D113" t="str">
+        <v>[Edge-case Guard] /api/auth/register - Duplicate email submission returns 409 Conflict</v>
+      </c>
+      <c r="E113" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Duplicate email submission returns 409 Conflict' (Edge-case Guard)</v>
+      </c>
+      <c r="G113" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H113" t="str">
+        <v>High</v>
+      </c>
+      <c r="I113" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J113" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K113" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>TC113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C114" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D114" t="str">
+        <v>[Edge-case Guard] /api/auth/register - Missing required fields returns 422 Validation Error</v>
+      </c>
+      <c r="E114" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Missing required fields returns 422 Validation Error' (Edge-case Guard)</v>
+      </c>
+      <c r="G114" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I114" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J114" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K114" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>TC114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C115" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D115" t="str">
+        <v>[Edge-case Guard] /api/auth/register - Password under 8 chars returns 400 Bad Request</v>
+      </c>
+      <c r="E115" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Password under 8 chars returns 400 Bad Request' (Edge-case Guard)</v>
+      </c>
+      <c r="G115" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I115" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J115" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K115" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>TC115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C116" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D116" t="str">
+        <v>[Edge-case Guard] /api/auth/register - Email format regex validation failure returns 400</v>
+      </c>
+      <c r="E116" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Email format regex validation failure returns 400' (Edge-case Guard)</v>
+      </c>
+      <c r="G116" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H116" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I116" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J116" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K116" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>TC116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C117" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D117" t="str">
+        <v>[Edge-case Guard] /api/auth/register - SQL injection string in Name field sanitized</v>
+      </c>
+      <c r="E117" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Dispatch API call to /api/auth/register: 'SQL injection string in Name field sanitized' (Edge-case Guard)</v>
+      </c>
+      <c r="G117" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H117" t="str">
+        <v>High</v>
+      </c>
+      <c r="I117" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J117" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K117" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>TC117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C118" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D118" t="str">
+        <v>[Edge-case Guard] /api/auth/register - XSS payload in profile bio escaped properly</v>
+      </c>
+      <c r="E118" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Dispatch API call to /api/auth/register: 'XSS payload in profile bio escaped properly' (Edge-case Guard)</v>
+      </c>
+      <c r="G118" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I118" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J118" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K118" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>TC118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C119" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D119" t="str">
+        <v>[Edge-case Guard] /api/auth/register - Account verification email event emitted</v>
+      </c>
+      <c r="E119" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Account verification email event emitted' (Edge-case Guard)</v>
+      </c>
+      <c r="G119" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H119" t="str">
+        <v>High</v>
+      </c>
+      <c r="I119" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J119" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K119" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>TC119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C120" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D120" t="str">
+        <v>[Edge-case Guard] /api/auth/register - Default user role 'PATIENT' assigned</v>
+      </c>
+      <c r="E120" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Default user role 'PATIENT' assigned' (Edge-case Guard)</v>
+      </c>
+      <c r="G120" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I120" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J120" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K120" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>TC120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C121" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D121" t="str">
+        <v>[Edge-case Guard] /api/auth/register - User metadata initialized in DB</v>
+      </c>
+      <c r="E121" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Dispatch API call to /api/auth/register: 'User metadata initialized in DB' (Edge-case Guard)</v>
+      </c>
+      <c r="G121" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I121" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J121" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K121" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>TC121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C122" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D122" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Valid email posts 200 Password Reset Triggered</v>
+      </c>
+      <c r="E122" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Valid email posts 200 Password Reset Triggered' (Edge-case Guard)</v>
+      </c>
+      <c r="G122" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I122" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J122" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K122" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>TC122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C123" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D123" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Unknown email returns 200 to prevent enumeration</v>
+      </c>
+      <c r="E123" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Unknown email returns 200 to prevent enumeration' (Edge-case Guard)</v>
+      </c>
+      <c r="G123" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H123" t="str">
+        <v>High</v>
+      </c>
+      <c r="I123" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J123" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K123" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>TC123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C124" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D124" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Reset token verification returns 200 Token Valid</v>
+      </c>
+      <c r="E124" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Reset token verification returns 200 Token Valid' (Edge-case Guard)</v>
+      </c>
+      <c r="G124" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I124" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J124" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K124" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>TC124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C125" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D125" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Expired reset token returns 400 Token Expired</v>
+      </c>
+      <c r="E125" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Expired reset token returns 400 Token Expired' (Edge-case Guard)</v>
+      </c>
+      <c r="G125" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H125" t="str">
+        <v>High</v>
+      </c>
+      <c r="I125" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J125" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K125" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>TC125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C126" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D126" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Password update with valid token returns 200 Updated</v>
+      </c>
+      <c r="E126" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Password update with valid token returns 200 Updated' (Edge-case Guard)</v>
+      </c>
+      <c r="G126" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I126" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J126" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K126" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>TC126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C127" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D127" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Reused old password returns 400 Cannot Reuse</v>
+      </c>
+      <c r="E127" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Reused old password returns 400 Cannot Reuse' (Edge-case Guard)</v>
+      </c>
+      <c r="G127" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I127" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J127" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K127" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>TC127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C128" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D128" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Invalid token format returns 400 Invalid Token</v>
+      </c>
+      <c r="E128" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Invalid token format returns 400 Invalid Token' (Edge-case Guard)</v>
+      </c>
+      <c r="G128" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I128" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J128" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K128" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>TC128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C129" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D129" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Mass reset request throttled by rate limiter</v>
+      </c>
+      <c r="E129" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Mass reset request throttled by rate limiter' (Edge-case Guard)</v>
+      </c>
+      <c r="G129" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H129" t="str">
+        <v>High</v>
+      </c>
+      <c r="I129" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J129" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K129" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>TC129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C130" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D130" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Reset completion revokes all active sessions</v>
+      </c>
+      <c r="E130" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Reset completion revokes all active sessions' (Edge-case Guard)</v>
+      </c>
+      <c r="G130" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I130" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J130" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K130" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>TC130</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C131" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D131" t="str">
+        <v>[Edge-case Guard] /api/auth/password-reset - Reset confirmation email dispatched via SMTP</v>
+      </c>
+      <c r="E131" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Reset confirmation email dispatched via SMTP' (Edge-case Guard)</v>
+      </c>
+      <c r="G131" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H131" t="str">
+        <v>High</v>
+      </c>
+      <c r="I131" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J131" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K131" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>TC131</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C132" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D132" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - Insert dynamic key-value pair for user biometrics</v>
+      </c>
+      <c r="E132" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Insert dynamic key-value pair for user biometrics' (Edge-case Guard)</v>
+      </c>
+      <c r="G132" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I132" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J132" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K132" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>TC132</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C133" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D133" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - Query key 'ai_chat_messages_Sathish' returns valid JSON</v>
+      </c>
+      <c r="E133" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Query key 'ai_chat_messages_Sathish' returns valid JSON' (Edge-case Guard)</v>
+      </c>
+      <c r="G133" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I133" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J133" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K133" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>TC133</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C134" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D134" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - Update EAV attribute value updates timestamp column</v>
+      </c>
+      <c r="E134" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Update EAV attribute value updates timestamp column' (Edge-case Guard)</v>
+      </c>
+      <c r="G134" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I134" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J134" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K134" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>TC134</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C135" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D135" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - Delete EAV key removes row without orphaned entries</v>
+      </c>
+      <c r="E135" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Delete EAV key removes row without orphaned entries' (Edge-case Guard)</v>
+      </c>
+      <c r="G135" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H135" t="str">
+        <v>High</v>
+      </c>
+      <c r="I135" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J135" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K135" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>TC135</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C136" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D136" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - EAV value JSON payload size up to 1MB supported</v>
+      </c>
+      <c r="E136" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'EAV value JSON payload size up to 1MB supported' (Edge-case Guard)</v>
+      </c>
+      <c r="G136" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I136" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J136" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K136" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>TC136</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C137" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D137" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - Concurrent EAV key writes handle row locking</v>
+      </c>
+      <c r="E137" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Concurrent EAV key writes handle row locking' (Edge-case Guard)</v>
+      </c>
+      <c r="G137" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H137" t="str">
+        <v>High</v>
+      </c>
+      <c r="I137" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J137" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K137" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>TC137</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C138" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D138" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - Null value insertion rejected by schema constraint</v>
+      </c>
+      <c r="E138" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Null value insertion rejected by schema constraint' (Edge-case Guard)</v>
+      </c>
+      <c r="G138" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H138" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I138" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J138" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K138" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>TC138</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C139" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D139" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - EAV search query index optimized under 50ms</v>
+      </c>
+      <c r="E139" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'EAV search query index optimized under 50ms' (Edge-case Guard)</v>
+      </c>
+      <c r="G139" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H139" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I139" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J139" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K139" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>TC139</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C140" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D140" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - JSON array append operation preserves sequence</v>
+      </c>
+      <c r="E140" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F140" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'JSON array append operation preserves sequence' (Edge-case Guard)</v>
+      </c>
+      <c r="G140" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H140" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I140" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J140" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K140" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>TC140</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C141" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D141" t="str">
+        <v>[Edge-case Guard] EAV Schema (userdata) - EAV cascade delete on user account removal</v>
+      </c>
+      <c r="E141" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F141" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'EAV cascade delete on user account removal' (Edge-case Guard)</v>
+      </c>
+      <c r="G141" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H141" t="str">
+        <v>High</v>
+      </c>
+      <c r="I141" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J141" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K141" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>TC141</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D142" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - Insert chat record into ai_chat_history table</v>
+      </c>
+      <c r="E142" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F142" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Insert chat record into ai_chat_history table' (Edge-case Guard)</v>
+      </c>
+      <c r="G142" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H142" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I142" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J142" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K142" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>TC142</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D143" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - Foreign key constraint links chat_id to user_id</v>
+      </c>
+      <c r="E143" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F143" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Foreign key constraint links chat_id to user_id' (Edge-case Guard)</v>
+      </c>
+      <c r="G143" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H143" t="str">
+        <v>High</v>
+      </c>
+      <c r="I143" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J143" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K143" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>TC143</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D144" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - Select chat messages ordered by created_at DESC</v>
+      </c>
+      <c r="E144" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F144" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Select chat messages ordered by created_at DESC' (Edge-case Guard)</v>
+      </c>
+      <c r="G144" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H144" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I144" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J144" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K144" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>TC144</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D145" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - Batch insert 50 chat messages in single transaction</v>
+      </c>
+      <c r="E145" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F145" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Batch insert 50 chat messages in single transaction' (Edge-case Guard)</v>
+      </c>
+      <c r="G145" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H145" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I145" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J145" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K145" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>TC145</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D146" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - Update message status to 'DELIVERED'</v>
+      </c>
+      <c r="E146" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F146" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Update message status to 'DELIVERED'' (Edge-case Guard)</v>
+      </c>
+      <c r="G146" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H146" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I146" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J146" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K146" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>TC146</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D147" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - Soft delete flag 'is_archived' updates correctly</v>
+      </c>
+      <c r="E147" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F147" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Soft delete flag 'is_archived' updates correctly' (Edge-case Guard)</v>
+      </c>
+      <c r="G147" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H147" t="str">
+        <v>High</v>
+      </c>
+      <c r="I147" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J147" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K147" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>TC147</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D148" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - Query filter by session_id returns exact thread</v>
+      </c>
+      <c r="E148" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F148" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Query filter by session_id returns exact thread' (Edge-case Guard)</v>
+      </c>
+      <c r="G148" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H148" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I148" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J148" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K148" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>TC148</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D149" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - Full-text search on message content column</v>
+      </c>
+      <c r="E149" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F149" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Full-text search on message content column' (Edge-case Guard)</v>
+      </c>
+      <c r="G149" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H149" t="str">
+        <v>High</v>
+      </c>
+      <c r="I149" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J149" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K149" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>TC149</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D150" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - Row Level Security (RLS) restricts cross-tenant read</v>
+      </c>
+      <c r="E150" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F150" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Row Level Security (RLS) restricts cross-tenant read' (Edge-case Guard)</v>
+      </c>
+      <c r="G150" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H150" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I150" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J150" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K150" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>TC150</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D151" t="str">
+        <v>[Edge-case Guard] Relational (ai_chat_history) - RLS policy blocks unauthorized message deletion</v>
+      </c>
+      <c r="E151" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'RLS policy blocks unauthorized message deletion' (Edge-case Guard)</v>
+      </c>
+      <c r="G151" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H151" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I151" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J151" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K151" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>TC151</v>
+      </c>
+      <c r="B152" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C152" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D152" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - Send symptom prompt returns 200 AI Completion JSON</v>
+      </c>
+      <c r="E152" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F152" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Send symptom prompt returns 200 AI Completion JSON' (Edge-case Guard)</v>
+      </c>
+      <c r="G152" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H152" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I152" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J152" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K152" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>TC152</v>
+      </c>
+      <c r="B153" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C153" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D153" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - Stream response chunks via Server-Sent Events (SSE)</v>
+      </c>
+      <c r="E153" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Stream response chunks via Server-Sent Events (SSE)' (Edge-case Guard)</v>
+      </c>
+      <c r="G153" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H153" t="str">
+        <v>High</v>
+      </c>
+      <c r="I153" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J153" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K153" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>TC153</v>
+      </c>
+      <c r="B154" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C154" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D154" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - API key header validation succeeds with VITE key</v>
+      </c>
+      <c r="E154" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'API key header validation succeeds with VITE key' (Edge-case Guard)</v>
+      </c>
+      <c r="G154" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H154" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I154" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J154" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K154" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>TC154</v>
+      </c>
+      <c r="B155" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C155" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D155" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - Missing API key returns 401 Unauthorized</v>
+      </c>
+      <c r="E155" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Missing API key returns 401 Unauthorized' (Edge-case Guard)</v>
+      </c>
+      <c r="G155" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H155" t="str">
+        <v>High</v>
+      </c>
+      <c r="I155" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J155" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K155" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>TC155</v>
+      </c>
+      <c r="B156" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C156" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D156" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - Exhausted API quota triggers fallback local markdown</v>
+      </c>
+      <c r="E156" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Exhausted API quota triggers fallback local markdown' (Edge-case Guard)</v>
+      </c>
+      <c r="G156" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H156" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I156" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J156" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K156" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>TC156</v>
+      </c>
+      <c r="B157" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C157" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D157" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - Model parameter 'deepseek/deepseek-r1' handled</v>
+      </c>
+      <c r="E157" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Model parameter 'deepseek/deepseek-r1' handled' (Edge-case Guard)</v>
+      </c>
+      <c r="G157" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H157" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I157" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J157" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K157" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>TC157</v>
+      </c>
+      <c r="B158" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C158" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D158" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - Temperature parameter 0.7 reflects in response variability</v>
+      </c>
+      <c r="E158" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Temperature parameter 0.7 reflects in response variability' (Edge-case Guard)</v>
+      </c>
+      <c r="G158" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H158" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I158" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J158" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K158" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>TC158</v>
+      </c>
+      <c r="B159" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C159" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D159" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - Max tokens 2048 parameter caps response length</v>
+      </c>
+      <c r="E159" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F159" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Max tokens 2048 parameter caps response length' (Edge-case Guard)</v>
+      </c>
+      <c r="G159" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H159" t="str">
+        <v>High</v>
+      </c>
+      <c r="I159" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J159" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K159" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>TC159</v>
+      </c>
+      <c r="B160" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C160" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D160" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - System prompt context injection verified</v>
+      </c>
+      <c r="E160" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F160" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'System prompt context injection verified' (Edge-case Guard)</v>
+      </c>
+      <c r="G160" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H160" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I160" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J160" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K160" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>TC160</v>
+      </c>
+      <c r="B161" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C161" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D161" t="str">
+        <v>[Edge-case Guard] /api/ai/completions - Prompt injection attack neutralized by guardrails</v>
+      </c>
+      <c r="E161" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F161" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Prompt injection attack neutralized by guardrails' (Edge-case Guard)</v>
+      </c>
+      <c r="G161" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H161" t="str">
+        <v>High</v>
+      </c>
+      <c r="I161" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J161" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K161" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>TC161</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C162" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D162" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Post valid symptom array returns risk analysis JSON</v>
+      </c>
+      <c r="E162" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F162" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Post valid symptom array returns risk analysis JSON' (Edge-case Guard)</v>
+      </c>
+      <c r="G162" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H162" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I162" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J162" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K162" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>TC162</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C163" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D163" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Post empty symptom array returns 400 Validation Error</v>
+      </c>
+      <c r="E163" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F163" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Post empty symptom array returns 400 Validation Error' (Edge-case Guard)</v>
+      </c>
+      <c r="G163" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H163" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I163" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J163" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K163" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>TC163</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C164" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D164" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Post invalid severity int (&gt;10) returns 400 Out of Bounds</v>
+      </c>
+      <c r="E164" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F164" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Post invalid severity int (&gt;10) returns 400 Out of Bounds' (Edge-case Guard)</v>
+      </c>
+      <c r="G164" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H164" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I164" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J164" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K164" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>TC164</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C165" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D165" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Analysis payload includes triage recommendation</v>
+      </c>
+      <c r="E165" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F165" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Analysis payload includes triage recommendation' (Edge-case Guard)</v>
+      </c>
+      <c r="G165" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H165" t="str">
+        <v>High</v>
+      </c>
+      <c r="I165" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J165" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K165" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>TC165</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C166" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D166" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Urgent symptoms flag 'CRITICAL_CARE' response</v>
+      </c>
+      <c r="E166" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F166" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Urgent symptoms flag 'CRITICAL_CARE' response' (Edge-case Guard)</v>
+      </c>
+      <c r="G166" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H166" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I166" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J166" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K166" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>TC166</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C167" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D167" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Analysis execution latency logged under 800ms</v>
+      </c>
+      <c r="E167" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Analysis execution latency logged under 800ms' (Edge-case Guard)</v>
+      </c>
+      <c r="G167" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H167" t="str">
+        <v>High</v>
+      </c>
+      <c r="I167" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J167" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K167" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>TC167</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C168" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D168" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Calculates body system impact correlation scores</v>
+      </c>
+      <c r="E168" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F168" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Calculates body system impact correlation scores' (Edge-case Guard)</v>
+      </c>
+      <c r="G168" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H168" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I168" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J168" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K168" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>TC168</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C169" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D169" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Stores analysis history record into DB table</v>
+      </c>
+      <c r="E169" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F169" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Stores analysis history record into DB table' (Edge-case Guard)</v>
+      </c>
+      <c r="G169" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H169" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I169" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J169" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K169" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>TC169</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C170" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D170" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Returns recommended medical specialty tags</v>
+      </c>
+      <c r="E170" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F170" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Returns recommended medical specialty tags' (Edge-case Guard)</v>
+      </c>
+      <c r="G170" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H170" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I170" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J170" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K170" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>TC170</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C171" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D171" t="str">
+        <v>[Edge-case Guard] /api/symptoms/analyze - Generates summary hash for diagnostic verification</v>
+      </c>
+      <c r="E171" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F171" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Generates summary hash for diagnostic verification' (Edge-case Guard)</v>
+      </c>
+      <c r="G171" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H171" t="str">
+        <v>High</v>
+      </c>
+      <c r="I171" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J171" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K171" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>TC171</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C172" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D172" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - POST blood pressure reading returns 201 Logged</v>
+      </c>
+      <c r="E172" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'POST blood pressure reading returns 201 Logged' (Edge-case Guard)</v>
+      </c>
+      <c r="G172" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H172" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I172" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J172" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K172" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>TC172</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C173" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D173" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - POST heart rate BPM value within 30-220 range</v>
+      </c>
+      <c r="E173" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F173" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'POST heart rate BPM value within 30-220 range' (Edge-case Guard)</v>
+      </c>
+      <c r="G173" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H173" t="str">
+        <v>High</v>
+      </c>
+      <c r="I173" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J173" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K173" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>TC173</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C174" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D174" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - GET vitals history with date range filter 7d</v>
+      </c>
+      <c r="E174" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F174" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'GET vitals history with date range filter 7d' (Edge-case Guard)</v>
+      </c>
+      <c r="G174" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H174" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I174" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J174" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K174" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>TC174</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C175" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D175" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - GET vitals summary calculates mean, min, max</v>
+      </c>
+      <c r="E175" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F175" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'GET vitals summary calculates mean, min, max' (Edge-case Guard)</v>
+      </c>
+      <c r="G175" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H175" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I175" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J175" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K175" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>TC175</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C176" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D176" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - POST invalid vital metric type returns 400 Error</v>
+      </c>
+      <c r="E176" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F176" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'POST invalid vital metric type returns 400 Error' (Edge-case Guard)</v>
+      </c>
+      <c r="G176" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H176" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I176" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J176" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K176" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>TC176</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C177" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D177" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - PUT edit past vital entry updates DB row</v>
+      </c>
+      <c r="E177" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F177" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'PUT edit past vital entry updates DB row' (Edge-case Guard)</v>
+      </c>
+      <c r="G177" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H177" t="str">
+        <v>High</v>
+      </c>
+      <c r="I177" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J177" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K177" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>TC177</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C178" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D178" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - DELETE vital entry soft-deletes record</v>
+      </c>
+      <c r="E178" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F178" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'DELETE vital entry soft-deletes record' (Edge-case Guard)</v>
+      </c>
+      <c r="G178" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H178" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I178" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J178" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K178" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>TC178</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C179" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D179" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - Bulk sync offline vital logs array returns 200</v>
+      </c>
+      <c r="E179" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F179" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'Bulk sync offline vital logs array returns 200' (Edge-case Guard)</v>
+      </c>
+      <c r="G179" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H179" t="str">
+        <v>High</v>
+      </c>
+      <c r="I179" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J179" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K179" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>TC179</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C180" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D180" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - High vital anomaly triggers notification event</v>
+      </c>
+      <c r="E180" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'High vital anomaly triggers notification event' (Edge-case Guard)</v>
+      </c>
+      <c r="G180" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H180" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I180" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J180" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K180" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>TC180</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C181" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D181" t="str">
+        <v>[Edge-case Guard] /api/vitals/log - Export vitals history as CSV payload stream</v>
+      </c>
+      <c r="E181" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F181" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'Export vitals history as CSV payload stream' (Edge-case Guard)</v>
+      </c>
+      <c r="G181" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H181" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I181" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J181" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K181" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>TC181</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C182" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D182" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - GET user privacy settings returns consent JSON</v>
+      </c>
+      <c r="E182" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F182" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'GET user privacy settings returns consent JSON' (Edge-case Guard)</v>
+      </c>
+      <c r="G182" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H182" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I182" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J182" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K182" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>TC182</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C183" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D183" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - PUT update anonymous analytics toggle to false</v>
+      </c>
+      <c r="E183" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F183" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'PUT update anonymous analytics toggle to false' (Edge-case Guard)</v>
+      </c>
+      <c r="G183" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H183" t="str">
+        <v>High</v>
+      </c>
+      <c r="I183" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J183" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K183" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>TC183</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C184" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D184" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - POST request full health data export ZIP archive</v>
+      </c>
+      <c r="E184" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F184" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'POST request full health data export ZIP archive' (Edge-case Guard)</v>
+      </c>
+      <c r="G184" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H184" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I184" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J184" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K184" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>TC184</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C185" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D185" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - Export ZIP payload contains JSON, PDF, CSV files</v>
+      </c>
+      <c r="E185" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F185" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'Export ZIP payload contains JSON, PDF, CSV files' (Edge-case Guard)</v>
+      </c>
+      <c r="G185" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H185" t="str">
+        <v>High</v>
+      </c>
+      <c r="I185" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J185" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K185" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>TC185</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C186" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D186" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - POST initiate account deletion queues job</v>
+      </c>
+      <c r="E186" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F186" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'POST initiate account deletion queues job' (Edge-case Guard)</v>
+      </c>
+      <c r="G186" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H186" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I186" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J186" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K186" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>TC186</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C187" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D187" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - Hard delete purges user row from users table</v>
+      </c>
+      <c r="E187" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F187" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'Hard delete purges user row from users table' (Edge-case Guard)</v>
+      </c>
+      <c r="G187" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H187" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I187" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J187" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K187" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>TC187</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C188" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D188" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - Hard delete purges user files from Supabase Storage</v>
+      </c>
+      <c r="E188" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F188" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'Hard delete purges user files from Supabase Storage' (Edge-case Guard)</v>
+      </c>
+      <c r="G188" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H188" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I188" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J188" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K188" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>TC188</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C189" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D189" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - Hard delete revokes all OAuth refresh tokens</v>
+      </c>
+      <c r="E189" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F189" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'Hard delete revokes all OAuth refresh tokens' (Edge-case Guard)</v>
+      </c>
+      <c r="G189" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H189" t="str">
+        <v>High</v>
+      </c>
+      <c r="I189" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J189" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K189" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>TC189</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C190" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D190" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - GET audit log returns data access history</v>
+      </c>
+      <c r="E190" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F190" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'GET audit log returns data access history' (Edge-case Guard)</v>
+      </c>
+      <c r="G190" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H190" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I190" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J190" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K190" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>TC190</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C191" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D191" t="str">
+        <v>[Edge-case Guard] /api/user/privacy - GDPR compliance right-to-be-forgotten check</v>
+      </c>
+      <c r="E191" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F191" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'GDPR compliance right-to-be-forgotten check' (Edge-case Guard)</v>
+      </c>
+      <c r="G191" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H191" t="str">
+        <v>High</v>
+      </c>
+      <c r="I191" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J191" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K191" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>TC191</v>
+      </c>
+      <c r="B192" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C192" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D192" t="str">
+        <v>[Edge-case Guard] /api/health/status - GET system health status returns 200 Healthy</v>
+      </c>
+      <c r="E192" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F192" t="str">
+        <v>Dispatch API call to /api/health/status: 'GET system health status returns 200 Healthy' (Edge-case Guard)</v>
+      </c>
+      <c r="G192" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H192" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I192" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J192" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K192" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>TC192</v>
+      </c>
+      <c r="B193" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C193" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D193" t="str">
+        <v>[Edge-case Guard] /api/health/status - Database connection pool ping check succeeds</v>
+      </c>
+      <c r="E193" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F193" t="str">
+        <v>Dispatch API call to /api/health/status: 'Database connection pool ping check succeeds' (Edge-case Guard)</v>
+      </c>
+      <c r="G193" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H193" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I193" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J193" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K193" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>TC193</v>
+      </c>
+      <c r="B194" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C194" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D194" t="str">
+        <v>[Edge-case Guard] /api/health/status - OpenRouter AI gateway ping check succeeds</v>
+      </c>
+      <c r="E194" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F194" t="str">
+        <v>Dispatch API call to /api/health/status: 'OpenRouter AI gateway ping check succeeds' (Edge-case Guard)</v>
+      </c>
+      <c r="G194" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H194" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I194" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J194" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K194" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>TC194</v>
+      </c>
+      <c r="B195" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C195" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D195" t="str">
+        <v>[Edge-case Guard] /api/health/status - Supabase auth service ping check succeeds</v>
+      </c>
+      <c r="E195" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F195" t="str">
+        <v>Dispatch API call to /api/health/status: 'Supabase auth service ping check succeeds' (Edge-case Guard)</v>
+      </c>
+      <c r="G195" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H195" t="str">
+        <v>High</v>
+      </c>
+      <c r="I195" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J195" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K195" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>TC195</v>
+      </c>
+      <c r="B196" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C196" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D196" t="str">
+        <v>[Edge-case Guard] /api/health/status - Disk space utilization check below 85%</v>
+      </c>
+      <c r="E196" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F196" t="str">
+        <v>Dispatch API call to /api/health/status: 'Disk space utilization check below 85%' (Edge-case Guard)</v>
+      </c>
+      <c r="G196" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H196" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I196" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J196" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K196" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>TC196</v>
+      </c>
+      <c r="B197" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C197" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D197" t="str">
+        <v>[Edge-case Guard] /api/health/status - Memory usage RSS check below 512MB</v>
+      </c>
+      <c r="E197" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F197" t="str">
+        <v>Dispatch API call to /api/health/status: 'Memory usage RSS check below 512MB' (Edge-case Guard)</v>
+      </c>
+      <c r="G197" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H197" t="str">
+        <v>High</v>
+      </c>
+      <c r="I197" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J197" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K197" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>TC197</v>
+      </c>
+      <c r="B198" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C198" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D198" t="str">
+        <v>[Edge-case Guard] /api/health/status - Active WebSocket connections metric returned</v>
+      </c>
+      <c r="E198" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F198" t="str">
+        <v>Dispatch API call to /api/health/status: 'Active WebSocket connections metric returned' (Edge-case Guard)</v>
+      </c>
+      <c r="G198" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I198" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J198" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K198" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>TC198</v>
+      </c>
+      <c r="B199" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C199" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D199" t="str">
+        <v>[Edge-case Guard] /api/health/status - API response time p99 benchmark below 200ms</v>
+      </c>
+      <c r="E199" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F199" t="str">
+        <v>Dispatch API call to /api/health/status: 'API response time p99 benchmark below 200ms' (Edge-case Guard)</v>
+      </c>
+      <c r="G199" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I199" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J199" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K199" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>TC199</v>
+      </c>
+      <c r="B200" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C200" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D200" t="str">
+        <v>[Edge-case Guard] /api/health/status - Version endpoint returns current git commit SHA</v>
+      </c>
+      <c r="E200" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F200" t="str">
+        <v>Dispatch API call to /api/health/status: 'Version endpoint returns current git commit SHA' (Edge-case Guard)</v>
+      </c>
+      <c r="G200" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I200" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J200" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K200" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>TC200</v>
+      </c>
+      <c r="B201" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C201" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D201" t="str">
+        <v>[Edge-case Guard] /api/health/status - Maintenance mode flag evaluation check</v>
+      </c>
+      <c r="E201" t="str">
+        <v>REST / Supabase API client configured with boundary limits and edge payload parameters</v>
+      </c>
+      <c r="F201" t="str">
+        <v>Dispatch API call to /api/health/status: 'Maintenance mode flag evaluation check' (Edge-case Guard)</v>
+      </c>
+      <c r="G201" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H201" t="str">
+        <v>High</v>
+      </c>
+      <c r="I201" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J201" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K201" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>TC201</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C202" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D202" t="str">
+        <v>[Security Sanity] /api/auth/login - Valid email and password returns 200 JWT token</v>
+      </c>
+      <c r="E202" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F202" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Valid email and password returns 200 JWT token' (Security Sanity)</v>
+      </c>
+      <c r="G202" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I202" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J202" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K202" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>TC202</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C203" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D203" t="str">
+        <v>[Security Sanity] /api/auth/login - Invalid password returns 401 Unauthorized</v>
+      </c>
+      <c r="E203" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F203" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Invalid password returns 401 Unauthorized' (Security Sanity)</v>
+      </c>
+      <c r="G203" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H203" t="str">
+        <v>High</v>
+      </c>
+      <c r="I203" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J203" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K203" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>TC203</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C204" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D204" t="str">
+        <v>[Security Sanity] /api/auth/login - Non-existent user email returns 404 Not Found</v>
+      </c>
+      <c r="E204" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F204" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Non-existent user email returns 404 Not Found' (Security Sanity)</v>
+      </c>
+      <c r="G204" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I204" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J204" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K204" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>TC204</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C205" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D205" t="str">
+        <v>[Security Sanity] /api/auth/login - Empty payload returns 400 Bad Request</v>
+      </c>
+      <c r="E205" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F205" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Empty payload returns 400 Bad Request' (Security Sanity)</v>
+      </c>
+      <c r="G205" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I205" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J205" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K205" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>TC205</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C206" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D206" t="str">
+        <v>[Security Sanity] /api/auth/login - Expired JWT token returns 401 Session Expired</v>
+      </c>
+      <c r="E206" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F206" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Expired JWT token returns 401 Session Expired' (Security Sanity)</v>
+      </c>
+      <c r="G206" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I206" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J206" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K206" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>TC206</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C207" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D207" t="str">
+        <v>[Security Sanity] /api/auth/login - Malformed JWT header returns 403 Forbidden</v>
+      </c>
+      <c r="E207" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F207" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Malformed JWT header returns 403 Forbidden' (Security Sanity)</v>
+      </c>
+      <c r="G207" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H207" t="str">
+        <v>High</v>
+      </c>
+      <c r="I207" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J207" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K207" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>TC207</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C208" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D208" t="str">
+        <v>[Security Sanity] /api/auth/login - Refresh token exchange returns 200 New Token</v>
+      </c>
+      <c r="E208" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F208" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Refresh token exchange returns 200 New Token' (Security Sanity)</v>
+      </c>
+      <c r="G208" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I208" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J208" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K208" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>TC208</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C209" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D209" t="str">
+        <v>[Security Sanity] /api/auth/login - Logout invalidates refresh token server-side</v>
+      </c>
+      <c r="E209" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F209" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Logout invalidates refresh token server-side' (Security Sanity)</v>
+      </c>
+      <c r="G209" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H209" t="str">
+        <v>High</v>
+      </c>
+      <c r="I209" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J209" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K209" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>TC209</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C210" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D210" t="str">
+        <v>[Security Sanity] /api/auth/login - Rate limit 5 failed attempts blocks IP 15m</v>
+      </c>
+      <c r="E210" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F210" t="str">
+        <v>Dispatch API call to /api/auth/login: 'Rate limit 5 failed attempts blocks IP 15m' (Security Sanity)</v>
+      </c>
+      <c r="G210" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I210" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J210" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K210" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>TC210</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C211" t="str">
+        <v>/api/auth/login</v>
+      </c>
+      <c r="D211" t="str">
+        <v>[Security Sanity] /api/auth/login - CORS preflight OPTIONS returns 200 OK</v>
+      </c>
+      <c r="E211" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F211" t="str">
+        <v>Dispatch API call to /api/auth/login: 'CORS preflight OPTIONS returns 200 OK' (Security Sanity)</v>
+      </c>
+      <c r="G211" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H211" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I211" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J211" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K211" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>TC211</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C212" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D212" t="str">
+        <v>[Security Sanity] /api/auth/register - Valid user payload returns 201 Created</v>
+      </c>
+      <c r="E212" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F212" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Valid user payload returns 201 Created' (Security Sanity)</v>
+      </c>
+      <c r="G212" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I212" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J212" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K212" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>TC212</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C213" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D213" t="str">
+        <v>[Security Sanity] /api/auth/register - Duplicate email submission returns 409 Conflict</v>
+      </c>
+      <c r="E213" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F213" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Duplicate email submission returns 409 Conflict' (Security Sanity)</v>
+      </c>
+      <c r="G213" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H213" t="str">
+        <v>High</v>
+      </c>
+      <c r="I213" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J213" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K213" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>TC213</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C214" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D214" t="str">
+        <v>[Security Sanity] /api/auth/register - Missing required fields returns 422 Validation Error</v>
+      </c>
+      <c r="E214" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F214" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Missing required fields returns 422 Validation Error' (Security Sanity)</v>
+      </c>
+      <c r="G214" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I214" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J214" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K214" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>TC214</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C215" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D215" t="str">
+        <v>[Security Sanity] /api/auth/register - Password under 8 chars returns 400 Bad Request</v>
+      </c>
+      <c r="E215" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F215" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Password under 8 chars returns 400 Bad Request' (Security Sanity)</v>
+      </c>
+      <c r="G215" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H215" t="str">
+        <v>High</v>
+      </c>
+      <c r="I215" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J215" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K215" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>TC215</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C216" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D216" t="str">
+        <v>[Security Sanity] /api/auth/register - Email format regex validation failure returns 400</v>
+      </c>
+      <c r="E216" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F216" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Email format regex validation failure returns 400' (Security Sanity)</v>
+      </c>
+      <c r="G216" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H216" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I216" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J216" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K216" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>TC216</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C217" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D217" t="str">
+        <v>[Security Sanity] /api/auth/register - SQL injection string in Name field sanitized</v>
+      </c>
+      <c r="E217" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F217" t="str">
+        <v>Dispatch API call to /api/auth/register: 'SQL injection string in Name field sanitized' (Security Sanity)</v>
+      </c>
+      <c r="G217" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H217" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I217" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J217" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K217" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>TC217</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C218" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D218" t="str">
+        <v>[Security Sanity] /api/auth/register - XSS payload in profile bio escaped properly</v>
+      </c>
+      <c r="E218" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F218" t="str">
+        <v>Dispatch API call to /api/auth/register: 'XSS payload in profile bio escaped properly' (Security Sanity)</v>
+      </c>
+      <c r="G218" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H218" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I218" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J218" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K218" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>TC218</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C219" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D219" t="str">
+        <v>[Security Sanity] /api/auth/register - Account verification email event emitted</v>
+      </c>
+      <c r="E219" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F219" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Account verification email event emitted' (Security Sanity)</v>
+      </c>
+      <c r="G219" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H219" t="str">
+        <v>High</v>
+      </c>
+      <c r="I219" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J219" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K219" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>TC219</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C220" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D220" t="str">
+        <v>[Security Sanity] /api/auth/register - Default user role 'PATIENT' assigned</v>
+      </c>
+      <c r="E220" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F220" t="str">
+        <v>Dispatch API call to /api/auth/register: 'Default user role 'PATIENT' assigned' (Security Sanity)</v>
+      </c>
+      <c r="G220" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H220" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I220" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J220" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K220" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>TC220</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C221" t="str">
+        <v>/api/auth/register</v>
+      </c>
+      <c r="D221" t="str">
+        <v>[Security Sanity] /api/auth/register - User metadata initialized in DB</v>
+      </c>
+      <c r="E221" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F221" t="str">
+        <v>Dispatch API call to /api/auth/register: 'User metadata initialized in DB' (Security Sanity)</v>
+      </c>
+      <c r="G221" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H221" t="str">
+        <v>High</v>
+      </c>
+      <c r="I221" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J221" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K221" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>TC221</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C222" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D222" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Valid email posts 200 Password Reset Triggered</v>
+      </c>
+      <c r="E222" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F222" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Valid email posts 200 Password Reset Triggered' (Security Sanity)</v>
+      </c>
+      <c r="G222" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H222" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I222" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J222" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K222" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>TC222</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C223" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D223" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Unknown email returns 200 to prevent enumeration</v>
+      </c>
+      <c r="E223" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F223" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Unknown email returns 200 to prevent enumeration' (Security Sanity)</v>
+      </c>
+      <c r="G223" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H223" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I223" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J223" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K223" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>TC223</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C224" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D224" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Reset token verification returns 200 Token Valid</v>
+      </c>
+      <c r="E224" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F224" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Reset token verification returns 200 Token Valid' (Security Sanity)</v>
+      </c>
+      <c r="G224" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H224" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I224" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J224" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K224" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>TC224</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C225" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D225" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Expired reset token returns 400 Token Expired</v>
+      </c>
+      <c r="E225" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F225" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Expired reset token returns 400 Token Expired' (Security Sanity)</v>
+      </c>
+      <c r="G225" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H225" t="str">
+        <v>High</v>
+      </c>
+      <c r="I225" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J225" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K225" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>TC225</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C226" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D226" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Password update with valid token returns 200 Updated</v>
+      </c>
+      <c r="E226" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F226" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Password update with valid token returns 200 Updated' (Security Sanity)</v>
+      </c>
+      <c r="G226" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H226" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I226" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J226" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K226" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>TC226</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C227" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D227" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Reused old password returns 400 Cannot Reuse</v>
+      </c>
+      <c r="E227" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F227" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Reused old password returns 400 Cannot Reuse' (Security Sanity)</v>
+      </c>
+      <c r="G227" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H227" t="str">
+        <v>High</v>
+      </c>
+      <c r="I227" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J227" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K227" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>TC227</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C228" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D228" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Invalid token format returns 400 Invalid Token</v>
+      </c>
+      <c r="E228" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F228" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Invalid token format returns 400 Invalid Token' (Security Sanity)</v>
+      </c>
+      <c r="G228" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H228" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I228" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J228" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K228" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>TC228</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C229" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D229" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Mass reset request throttled by rate limiter</v>
+      </c>
+      <c r="E229" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F229" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Mass reset request throttled by rate limiter' (Security Sanity)</v>
+      </c>
+      <c r="G229" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H229" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I229" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J229" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K229" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>TC229</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C230" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D230" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Reset completion revokes all active sessions</v>
+      </c>
+      <c r="E230" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F230" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Reset completion revokes all active sessions' (Security Sanity)</v>
+      </c>
+      <c r="G230" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H230" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I230" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J230" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K230" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>TC230</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Auth API</v>
+      </c>
+      <c r="C231" t="str">
+        <v>/api/auth/password-reset</v>
+      </c>
+      <c r="D231" t="str">
+        <v>[Security Sanity] /api/auth/password-reset - Reset confirmation email dispatched via SMTP</v>
+      </c>
+      <c r="E231" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F231" t="str">
+        <v>Dispatch API call to /api/auth/password-reset: 'Reset confirmation email dispatched via SMTP' (Security Sanity)</v>
+      </c>
+      <c r="G231" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H231" t="str">
+        <v>High</v>
+      </c>
+      <c r="I231" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J231" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K231" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>TC231</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C232" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D232" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - Insert dynamic key-value pair for user biometrics</v>
+      </c>
+      <c r="E232" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F232" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Insert dynamic key-value pair for user biometrics' (Security Sanity)</v>
+      </c>
+      <c r="G232" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H232" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I232" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J232" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K232" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>TC232</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C233" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D233" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - Query key 'ai_chat_messages_Sathish' returns valid JSON</v>
+      </c>
+      <c r="E233" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F233" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Query key 'ai_chat_messages_Sathish' returns valid JSON' (Security Sanity)</v>
+      </c>
+      <c r="G233" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H233" t="str">
+        <v>High</v>
+      </c>
+      <c r="I233" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J233" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K233" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>TC233</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C234" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D234" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - Update EAV attribute value updates timestamp column</v>
+      </c>
+      <c r="E234" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F234" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Update EAV attribute value updates timestamp column' (Security Sanity)</v>
+      </c>
+      <c r="G234" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H234" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I234" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J234" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K234" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>TC234</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C235" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D235" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - Delete EAV key removes row without orphaned entries</v>
+      </c>
+      <c r="E235" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F235" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Delete EAV key removes row without orphaned entries' (Security Sanity)</v>
+      </c>
+      <c r="G235" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H235" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I235" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J235" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K235" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>TC235</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C236" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D236" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - EAV value JSON payload size up to 1MB supported</v>
+      </c>
+      <c r="E236" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F236" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'EAV value JSON payload size up to 1MB supported' (Security Sanity)</v>
+      </c>
+      <c r="G236" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H236" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I236" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J236" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K236" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>TC236</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C237" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D237" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - Concurrent EAV key writes handle row locking</v>
+      </c>
+      <c r="E237" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F237" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Concurrent EAV key writes handle row locking' (Security Sanity)</v>
+      </c>
+      <c r="G237" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H237" t="str">
+        <v>High</v>
+      </c>
+      <c r="I237" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J237" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K237" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>TC237</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C238" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D238" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - Null value insertion rejected by schema constraint</v>
+      </c>
+      <c r="E238" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F238" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'Null value insertion rejected by schema constraint' (Security Sanity)</v>
+      </c>
+      <c r="G238" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H238" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I238" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J238" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K238" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>TC238</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C239" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D239" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - EAV search query index optimized under 50ms</v>
+      </c>
+      <c r="E239" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F239" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'EAV search query index optimized under 50ms' (Security Sanity)</v>
+      </c>
+      <c r="G239" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H239" t="str">
+        <v>High</v>
+      </c>
+      <c r="I239" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J239" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K239" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>TC239</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C240" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D240" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - JSON array append operation preserves sequence</v>
+      </c>
+      <c r="E240" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F240" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'JSON array append operation preserves sequence' (Security Sanity)</v>
+      </c>
+      <c r="G240" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H240" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I240" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J240" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K240" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>TC240</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C241" t="str">
+        <v>EAV Schema (userdata)</v>
+      </c>
+      <c r="D241" t="str">
+        <v>[Security Sanity] EAV Schema (userdata) - EAV cascade delete on user account removal</v>
+      </c>
+      <c r="E241" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F241" t="str">
+        <v>Dispatch API call to EAV Schema (userdata): 'EAV cascade delete on user account removal' (Security Sanity)</v>
+      </c>
+      <c r="G241" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H241" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I241" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J241" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K241" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>TC241</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D242" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - Insert chat record into ai_chat_history table</v>
+      </c>
+      <c r="E242" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F242" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Insert chat record into ai_chat_history table' (Security Sanity)</v>
+      </c>
+      <c r="G242" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H242" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I242" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J242" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K242" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>TC242</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D243" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - Foreign key constraint links chat_id to user_id</v>
+      </c>
+      <c r="E243" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F243" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Foreign key constraint links chat_id to user_id' (Security Sanity)</v>
+      </c>
+      <c r="G243" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H243" t="str">
+        <v>High</v>
+      </c>
+      <c r="I243" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J243" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K243" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>TC243</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D244" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - Select chat messages ordered by created_at DESC</v>
+      </c>
+      <c r="E244" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F244" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Select chat messages ordered by created_at DESC' (Security Sanity)</v>
+      </c>
+      <c r="G244" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H244" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I244" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J244" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K244" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>TC244</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D245" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - Batch insert 50 chat messages in single transaction</v>
+      </c>
+      <c r="E245" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F245" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Batch insert 50 chat messages in single transaction' (Security Sanity)</v>
+      </c>
+      <c r="G245" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H245" t="str">
+        <v>High</v>
+      </c>
+      <c r="I245" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J245" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K245" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>TC245</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D246" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - Update message status to 'DELIVERED'</v>
+      </c>
+      <c r="E246" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F246" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Update message status to 'DELIVERED'' (Security Sanity)</v>
+      </c>
+      <c r="G246" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H246" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I246" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J246" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K246" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>TC246</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D247" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - Soft delete flag 'is_archived' updates correctly</v>
+      </c>
+      <c r="E247" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F247" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Soft delete flag 'is_archived' updates correctly' (Security Sanity)</v>
+      </c>
+      <c r="G247" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H247" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I247" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J247" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K247" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>TC247</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D248" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - Query filter by session_id returns exact thread</v>
+      </c>
+      <c r="E248" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F248" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Query filter by session_id returns exact thread' (Security Sanity)</v>
+      </c>
+      <c r="G248" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H248" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I248" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J248" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K248" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>TC248</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D249" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - Full-text search on message content column</v>
+      </c>
+      <c r="E249" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F249" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Full-text search on message content column' (Security Sanity)</v>
+      </c>
+      <c r="G249" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H249" t="str">
+        <v>High</v>
+      </c>
+      <c r="I249" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J249" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K249" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>TC249</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D250" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - Row Level Security (RLS) restricts cross-tenant read</v>
+      </c>
+      <c r="E250" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F250" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'Row Level Security (RLS) restricts cross-tenant read' (Security Sanity)</v>
+      </c>
+      <c r="G250" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H250" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I250" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J250" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K250" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>TC250</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Supabase DB</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Relational (ai_chat_history)</v>
+      </c>
+      <c r="D251" t="str">
+        <v>[Security Sanity] Relational (ai_chat_history) - RLS policy blocks unauthorized message deletion</v>
+      </c>
+      <c r="E251" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F251" t="str">
+        <v>Dispatch API call to Relational (ai_chat_history): 'RLS policy blocks unauthorized message deletion' (Security Sanity)</v>
+      </c>
+      <c r="G251" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H251" t="str">
+        <v>High</v>
+      </c>
+      <c r="I251" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J251" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K251" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>TC251</v>
+      </c>
+      <c r="B252" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C252" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D252" t="str">
+        <v>[Security Sanity] /api/ai/completions - Send symptom prompt returns 200 AI Completion JSON</v>
+      </c>
+      <c r="E252" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F252" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Send symptom prompt returns 200 AI Completion JSON' (Security Sanity)</v>
+      </c>
+      <c r="G252" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H252" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I252" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J252" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K252" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>TC252</v>
+      </c>
+      <c r="B253" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C253" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D253" t="str">
+        <v>[Security Sanity] /api/ai/completions - Stream response chunks via Server-Sent Events (SSE)</v>
+      </c>
+      <c r="E253" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F253" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Stream response chunks via Server-Sent Events (SSE)' (Security Sanity)</v>
+      </c>
+      <c r="G253" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H253" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I253" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J253" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K253" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>TC253</v>
+      </c>
+      <c r="B254" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C254" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D254" t="str">
+        <v>[Security Sanity] /api/ai/completions - API key header validation succeeds with VITE key</v>
+      </c>
+      <c r="E254" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F254" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'API key header validation succeeds with VITE key' (Security Sanity)</v>
+      </c>
+      <c r="G254" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H254" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I254" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J254" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K254" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>TC254</v>
+      </c>
+      <c r="B255" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C255" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D255" t="str">
+        <v>[Security Sanity] /api/ai/completions - Missing API key returns 401 Unauthorized</v>
+      </c>
+      <c r="E255" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F255" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Missing API key returns 401 Unauthorized' (Security Sanity)</v>
+      </c>
+      <c r="G255" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H255" t="str">
+        <v>High</v>
+      </c>
+      <c r="I255" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J255" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K255" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>TC255</v>
+      </c>
+      <c r="B256" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C256" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D256" t="str">
+        <v>[Security Sanity] /api/ai/completions - Exhausted API quota triggers fallback local markdown</v>
+      </c>
+      <c r="E256" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F256" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Exhausted API quota triggers fallback local markdown' (Security Sanity)</v>
+      </c>
+      <c r="G256" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H256" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I256" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J256" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K256" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>TC256</v>
+      </c>
+      <c r="B257" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C257" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D257" t="str">
+        <v>[Security Sanity] /api/ai/completions - Model parameter 'deepseek/deepseek-r1' handled</v>
+      </c>
+      <c r="E257" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F257" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Model parameter 'deepseek/deepseek-r1' handled' (Security Sanity)</v>
+      </c>
+      <c r="G257" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H257" t="str">
+        <v>High</v>
+      </c>
+      <c r="I257" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J257" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K257" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>TC257</v>
+      </c>
+      <c r="B258" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C258" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D258" t="str">
+        <v>[Security Sanity] /api/ai/completions - Temperature parameter 0.7 reflects in response variability</v>
+      </c>
+      <c r="E258" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F258" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Temperature parameter 0.7 reflects in response variability' (Security Sanity)</v>
+      </c>
+      <c r="G258" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H258" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I258" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J258" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K258" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>TC258</v>
+      </c>
+      <c r="B259" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C259" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D259" t="str">
+        <v>[Security Sanity] /api/ai/completions - Max tokens 2048 parameter caps response length</v>
+      </c>
+      <c r="E259" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F259" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Max tokens 2048 parameter caps response length' (Security Sanity)</v>
+      </c>
+      <c r="G259" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H259" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I259" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J259" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K259" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>TC259</v>
+      </c>
+      <c r="B260" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C260" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D260" t="str">
+        <v>[Security Sanity] /api/ai/completions - System prompt context injection verified</v>
+      </c>
+      <c r="E260" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F260" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'System prompt context injection verified' (Security Sanity)</v>
+      </c>
+      <c r="G260" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H260" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I260" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J260" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K260" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>TC260</v>
+      </c>
+      <c r="B261" t="str">
+        <v>OpenRouter AI API</v>
+      </c>
+      <c r="C261" t="str">
+        <v>/api/ai/completions</v>
+      </c>
+      <c r="D261" t="str">
+        <v>[Security Sanity] /api/ai/completions - Prompt injection attack neutralized by guardrails</v>
+      </c>
+      <c r="E261" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F261" t="str">
+        <v>Dispatch API call to /api/ai/completions: 'Prompt injection attack neutralized by guardrails' (Security Sanity)</v>
+      </c>
+      <c r="G261" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H261" t="str">
+        <v>High</v>
+      </c>
+      <c r="I261" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J261" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K261" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>TC261</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C262" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D262" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Post valid symptom array returns risk analysis JSON</v>
+      </c>
+      <c r="E262" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F262" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Post valid symptom array returns risk analysis JSON' (Security Sanity)</v>
+      </c>
+      <c r="G262" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H262" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I262" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J262" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K262" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>TC262</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C263" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D263" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Post empty symptom array returns 400 Validation Error</v>
+      </c>
+      <c r="E263" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F263" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Post empty symptom array returns 400 Validation Error' (Security Sanity)</v>
+      </c>
+      <c r="G263" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H263" t="str">
+        <v>High</v>
+      </c>
+      <c r="I263" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J263" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K263" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>TC263</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C264" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D264" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Post invalid severity int (&gt;10) returns 400 Out of Bounds</v>
+      </c>
+      <c r="E264" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F264" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Post invalid severity int (&gt;10) returns 400 Out of Bounds' (Security Sanity)</v>
+      </c>
+      <c r="G264" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H264" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I264" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J264" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K264" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>TC264</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C265" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D265" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Analysis payload includes triage recommendation</v>
+      </c>
+      <c r="E265" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F265" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Analysis payload includes triage recommendation' (Security Sanity)</v>
+      </c>
+      <c r="G265" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H265" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I265" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J265" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K265" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>TC265</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C266" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D266" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Urgent symptoms flag 'CRITICAL_CARE' response</v>
+      </c>
+      <c r="E266" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F266" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Urgent symptoms flag 'CRITICAL_CARE' response' (Security Sanity)</v>
+      </c>
+      <c r="G266" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H266" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I266" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J266" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K266" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>TC266</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C267" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D267" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Analysis execution latency logged under 800ms</v>
+      </c>
+      <c r="E267" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F267" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Analysis execution latency logged under 800ms' (Security Sanity)</v>
+      </c>
+      <c r="G267" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H267" t="str">
+        <v>High</v>
+      </c>
+      <c r="I267" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J267" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K267" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>TC267</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C268" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D268" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Calculates body system impact correlation scores</v>
+      </c>
+      <c r="E268" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F268" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Calculates body system impact correlation scores' (Security Sanity)</v>
+      </c>
+      <c r="G268" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H268" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I268" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J268" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K268" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>TC268</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C269" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D269" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Stores analysis history record into DB table</v>
+      </c>
+      <c r="E269" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F269" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Stores analysis history record into DB table' (Security Sanity)</v>
+      </c>
+      <c r="G269" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H269" t="str">
+        <v>High</v>
+      </c>
+      <c r="I269" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J269" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K269" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>TC269</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C270" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D270" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Returns recommended medical specialty tags</v>
+      </c>
+      <c r="E270" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F270" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Returns recommended medical specialty tags' (Security Sanity)</v>
+      </c>
+      <c r="G270" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H270" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I270" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J270" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K270" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>TC270</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Diagnostics API</v>
+      </c>
+      <c r="C271" t="str">
+        <v>/api/symptoms/analyze</v>
+      </c>
+      <c r="D271" t="str">
+        <v>[Security Sanity] /api/symptoms/analyze - Generates summary hash for diagnostic verification</v>
+      </c>
+      <c r="E271" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F271" t="str">
+        <v>Dispatch API call to /api/symptoms/analyze: 'Generates summary hash for diagnostic verification' (Security Sanity)</v>
+      </c>
+      <c r="G271" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H271" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I271" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J271" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K271" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>TC271</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C272" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D272" t="str">
+        <v>[Security Sanity] /api/vitals/log - POST blood pressure reading returns 201 Logged</v>
+      </c>
+      <c r="E272" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F272" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'POST blood pressure reading returns 201 Logged' (Security Sanity)</v>
+      </c>
+      <c r="G272" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H272" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I272" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J272" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K272" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>TC272</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C273" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D273" t="str">
+        <v>[Security Sanity] /api/vitals/log - POST heart rate BPM value within 30-220 range</v>
+      </c>
+      <c r="E273" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F273" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'POST heart rate BPM value within 30-220 range' (Security Sanity)</v>
+      </c>
+      <c r="G273" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H273" t="str">
+        <v>High</v>
+      </c>
+      <c r="I273" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J273" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K273" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>TC273</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C274" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D274" t="str">
+        <v>[Security Sanity] /api/vitals/log - GET vitals history with date range filter 7d</v>
+      </c>
+      <c r="E274" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F274" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'GET vitals history with date range filter 7d' (Security Sanity)</v>
+      </c>
+      <c r="G274" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H274" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I274" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J274" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K274" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>TC274</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C275" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D275" t="str">
+        <v>[Security Sanity] /api/vitals/log - GET vitals summary calculates mean, min, max</v>
+      </c>
+      <c r="E275" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F275" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'GET vitals summary calculates mean, min, max' (Security Sanity)</v>
+      </c>
+      <c r="G275" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H275" t="str">
+        <v>High</v>
+      </c>
+      <c r="I275" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J275" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K275" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>TC275</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C276" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D276" t="str">
+        <v>[Security Sanity] /api/vitals/log - POST invalid vital metric type returns 400 Error</v>
+      </c>
+      <c r="E276" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F276" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'POST invalid vital metric type returns 400 Error' (Security Sanity)</v>
+      </c>
+      <c r="G276" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H276" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I276" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J276" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K276" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>TC276</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C277" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D277" t="str">
+        <v>[Security Sanity] /api/vitals/log - PUT edit past vital entry updates DB row</v>
+      </c>
+      <c r="E277" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F277" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'PUT edit past vital entry updates DB row' (Security Sanity)</v>
+      </c>
+      <c r="G277" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H277" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I277" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J277" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K277" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>TC277</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C278" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D278" t="str">
+        <v>[Security Sanity] /api/vitals/log - DELETE vital entry soft-deletes record</v>
+      </c>
+      <c r="E278" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F278" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'DELETE vital entry soft-deletes record' (Security Sanity)</v>
+      </c>
+      <c r="G278" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H278" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I278" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J278" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K278" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>TC278</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C279" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D279" t="str">
+        <v>[Security Sanity] /api/vitals/log - Bulk sync offline vital logs array returns 200</v>
+      </c>
+      <c r="E279" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F279" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'Bulk sync offline vital logs array returns 200' (Security Sanity)</v>
+      </c>
+      <c r="G279" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H279" t="str">
+        <v>High</v>
+      </c>
+      <c r="I279" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J279" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K279" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>TC279</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C280" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D280" t="str">
+        <v>[Security Sanity] /api/vitals/log - High vital anomaly triggers notification event</v>
+      </c>
+      <c r="E280" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F280" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'High vital anomaly triggers notification event' (Security Sanity)</v>
+      </c>
+      <c r="G280" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H280" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I280" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J280" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K280" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>TC280</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Vitals &amp; Tracker API</v>
+      </c>
+      <c r="C281" t="str">
+        <v>/api/vitals/log</v>
+      </c>
+      <c r="D281" t="str">
+        <v>[Security Sanity] /api/vitals/log - Export vitals history as CSV payload stream</v>
+      </c>
+      <c r="E281" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F281" t="str">
+        <v>Dispatch API call to /api/vitals/log: 'Export vitals history as CSV payload stream' (Security Sanity)</v>
+      </c>
+      <c r="G281" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H281" t="str">
+        <v>High</v>
+      </c>
+      <c r="I281" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J281" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K281" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>TC281</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C282" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D282" t="str">
+        <v>[Security Sanity] /api/user/privacy - GET user privacy settings returns consent JSON</v>
+      </c>
+      <c r="E282" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F282" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'GET user privacy settings returns consent JSON' (Security Sanity)</v>
+      </c>
+      <c r="G282" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H282" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I282" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J282" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K282" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>TC282</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C283" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D283" t="str">
+        <v>[Security Sanity] /api/user/privacy - PUT update anonymous analytics toggle to false</v>
+      </c>
+      <c r="E283" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F283" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'PUT update anonymous analytics toggle to false' (Security Sanity)</v>
+      </c>
+      <c r="G283" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H283" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I283" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J283" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K283" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>TC283</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C284" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D284" t="str">
+        <v>[Security Sanity] /api/user/privacy - POST request full health data export ZIP archive</v>
+      </c>
+      <c r="E284" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F284" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'POST request full health data export ZIP archive' (Security Sanity)</v>
+      </c>
+      <c r="G284" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H284" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I284" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J284" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K284" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>TC284</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C285" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D285" t="str">
+        <v>[Security Sanity] /api/user/privacy - Export ZIP payload contains JSON, PDF, CSV files</v>
+      </c>
+      <c r="E285" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F285" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'Export ZIP payload contains JSON, PDF, CSV files' (Security Sanity)</v>
+      </c>
+      <c r="G285" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H285" t="str">
+        <v>High</v>
+      </c>
+      <c r="I285" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J285" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K285" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>TC285</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C286" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D286" t="str">
+        <v>[Security Sanity] /api/user/privacy - POST initiate account deletion queues job</v>
+      </c>
+      <c r="E286" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F286" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'POST initiate account deletion queues job' (Security Sanity)</v>
+      </c>
+      <c r="G286" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H286" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I286" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J286" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K286" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>TC286</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C287" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D287" t="str">
+        <v>[Security Sanity] /api/user/privacy - Hard delete purges user row from users table</v>
+      </c>
+      <c r="E287" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F287" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'Hard delete purges user row from users table' (Security Sanity)</v>
+      </c>
+      <c r="G287" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H287" t="str">
+        <v>High</v>
+      </c>
+      <c r="I287" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J287" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K287" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>TC287</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C288" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D288" t="str">
+        <v>[Security Sanity] /api/user/privacy - Hard delete purges user files from Supabase Storage</v>
+      </c>
+      <c r="E288" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F288" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'Hard delete purges user files from Supabase Storage' (Security Sanity)</v>
+      </c>
+      <c r="G288" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H288" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I288" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J288" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K288" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>TC288</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C289" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D289" t="str">
+        <v>[Security Sanity] /api/user/privacy - Hard delete revokes all OAuth refresh tokens</v>
+      </c>
+      <c r="E289" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F289" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'Hard delete revokes all OAuth refresh tokens' (Security Sanity)</v>
+      </c>
+      <c r="G289" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H289" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I289" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J289" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K289" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>TC289</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C290" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D290" t="str">
+        <v>[Security Sanity] /api/user/privacy - GET audit log returns data access history</v>
+      </c>
+      <c r="E290" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F290" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'GET audit log returns data access history' (Security Sanity)</v>
+      </c>
+      <c r="G290" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H290" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I290" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J290" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K290" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>TC290</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Privacy &amp; Data API</v>
+      </c>
+      <c r="C291" t="str">
+        <v>/api/user/privacy</v>
+      </c>
+      <c r="D291" t="str">
+        <v>[Security Sanity] /api/user/privacy - GDPR compliance right-to-be-forgotten check</v>
+      </c>
+      <c r="E291" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F291" t="str">
+        <v>Dispatch API call to /api/user/privacy: 'GDPR compliance right-to-be-forgotten check' (Security Sanity)</v>
+      </c>
+      <c r="G291" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H291" t="str">
+        <v>High</v>
+      </c>
+      <c r="I291" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J291" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K291" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>TC291</v>
+      </c>
+      <c r="B292" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C292" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D292" t="str">
+        <v>[Security Sanity] /api/health/status - GET system health status returns 200 Healthy</v>
+      </c>
+      <c r="E292" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F292" t="str">
+        <v>Dispatch API call to /api/health/status: 'GET system health status returns 200 Healthy' (Security Sanity)</v>
+      </c>
+      <c r="G292" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H292" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I292" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J292" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K292" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>TC292</v>
+      </c>
+      <c r="B293" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C293" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D293" t="str">
+        <v>[Security Sanity] /api/health/status - Database connection pool ping check succeeds</v>
+      </c>
+      <c r="E293" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F293" t="str">
+        <v>Dispatch API call to /api/health/status: 'Database connection pool ping check succeeds' (Security Sanity)</v>
+      </c>
+      <c r="G293" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H293" t="str">
+        <v>High</v>
+      </c>
+      <c r="I293" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J293" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K293" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>TC293</v>
+      </c>
+      <c r="B294" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C294" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D294" t="str">
+        <v>[Security Sanity] /api/health/status - OpenRouter AI gateway ping check succeeds</v>
+      </c>
+      <c r="E294" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F294" t="str">
+        <v>Dispatch API call to /api/health/status: 'OpenRouter AI gateway ping check succeeds' (Security Sanity)</v>
+      </c>
+      <c r="G294" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H294" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I294" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J294" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K294" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>TC294</v>
+      </c>
+      <c r="B295" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C295" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D295" t="str">
+        <v>[Security Sanity] /api/health/status - Supabase auth service ping check succeeds</v>
+      </c>
+      <c r="E295" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F295" t="str">
+        <v>Dispatch API call to /api/health/status: 'Supabase auth service ping check succeeds' (Security Sanity)</v>
+      </c>
+      <c r="G295" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H295" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I295" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J295" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K295" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>TC295</v>
+      </c>
+      <c r="B296" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C296" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D296" t="str">
+        <v>[Security Sanity] /api/health/status - Disk space utilization check below 85%</v>
+      </c>
+      <c r="E296" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F296" t="str">
+        <v>Dispatch API call to /api/health/status: 'Disk space utilization check below 85%' (Security Sanity)</v>
+      </c>
+      <c r="G296" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H296" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I296" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J296" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K296" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>TC296</v>
+      </c>
+      <c r="B297" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C297" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D297" t="str">
+        <v>[Security Sanity] /api/health/status - Memory usage RSS check below 512MB</v>
+      </c>
+      <c r="E297" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F297" t="str">
+        <v>Dispatch API call to /api/health/status: 'Memory usage RSS check below 512MB' (Security Sanity)</v>
+      </c>
+      <c r="G297" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H297" t="str">
+        <v>High</v>
+      </c>
+      <c r="I297" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J297" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K297" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>TC297</v>
+      </c>
+      <c r="B298" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C298" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D298" t="str">
+        <v>[Security Sanity] /api/health/status - Active WebSocket connections metric returned</v>
+      </c>
+      <c r="E298" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F298" t="str">
+        <v>Dispatch API call to /api/health/status: 'Active WebSocket connections metric returned' (Security Sanity)</v>
+      </c>
+      <c r="G298" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H298" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I298" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J298" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K298" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>TC298</v>
+      </c>
+      <c r="B299" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C299" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D299" t="str">
+        <v>[Security Sanity] /api/health/status - API response time p99 benchmark below 200ms</v>
+      </c>
+      <c r="E299" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F299" t="str">
+        <v>Dispatch API call to /api/health/status: 'API response time p99 benchmark below 200ms' (Security Sanity)</v>
+      </c>
+      <c r="G299" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H299" t="str">
+        <v>High</v>
+      </c>
+      <c r="I299" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J299" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K299" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>TC299</v>
+      </c>
+      <c r="B300" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C300" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D300" t="str">
+        <v>[Security Sanity] /api/health/status - Version endpoint returns current git commit SHA</v>
+      </c>
+      <c r="E300" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F300" t="str">
+        <v>Dispatch API call to /api/health/status: 'Version endpoint returns current git commit SHA' (Security Sanity)</v>
+      </c>
+      <c r="G300" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H300" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I300" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J300" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K300" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>TC300</v>
+      </c>
+      <c r="B301" t="str">
+        <v>System &amp; Health API</v>
+      </c>
+      <c r="C301" t="str">
+        <v>/api/health/status</v>
+      </c>
+      <c r="D301" t="str">
+        <v>[Security Sanity] /api/health/status - Maintenance mode flag evaluation check</v>
+      </c>
+      <c r="E301" t="str">
+        <v>REST / Supabase API client configured testing token revocation and unauthorized header drops</v>
+      </c>
+      <c r="F301" t="str">
+        <v>Dispatch API call to /api/health/status: 'Maintenance mode flag evaluation check' (Security Sanity)</v>
+      </c>
+      <c r="G301" t="str">
+        <v>API endpoint responds within SLA bounds with expected HTTP payload schema</v>
+      </c>
+      <c r="H301" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I301" t="str">
+        <v>API / Integration</v>
+      </c>
+      <c r="J301" t="str">
+        <v>Backend API</v>
+      </c>
+      <c r="K301" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K301"/>
   </ignoredErrors>
 </worksheet>
 </file>